--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>Prepare for the CA and build some logic.</t>
+  </si>
+  <si>
+    <t>Prepare for the CA and Practice.</t>
   </si>
 </sst>
 </file>
@@ -1048,12 +1051,6 @@
     <xf numFmtId="1" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1062,6 +1059,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1091,7 +1094,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1628,7 +1631,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" ht="19.5" customHeight="1" spans="1:7">
+    <row r="2" ht="19.5" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -1645,7 +1648,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" ht="19.5" customHeight="1" spans="1:7">
+    <row r="3" ht="19.5" customHeight="1" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -1749,50 +1752,50 @@
       <c r="H6" s="7">
         <v>30</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="8">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="8">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="10" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="8">
+      <c r="A7" s="11">
         <v>46247</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="12">
         <v>360</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="12">
         <v>60</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="12">
         <v>60</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="12">
         <v>0</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="12">
         <v>400</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="12">
         <v>8</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="12">
         <v>300</v>
       </c>
       <c r="I7" s="13">
@@ -1817,28 +1820,28 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="8">
+      <c r="A8" s="11">
         <v>46248</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="12">
         <v>420</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="12">
         <v>60</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="12">
         <v>60</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="12">
         <v>45</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="12">
         <v>350</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="12">
         <v>7</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="12">
         <v>350</v>
       </c>
       <c r="I8" s="13">
@@ -1863,28 +1866,28 @@
       </c>
     </row>
     <row r="9" ht="43.2" spans="1:14">
-      <c r="A9" s="8">
+      <c r="A9" s="11">
         <v>46249</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="12">
         <v>480</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="12">
         <v>60</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="12">
         <v>60</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="12">
         <v>30</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="12">
         <v>0</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="12">
         <v>0</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="12">
         <v>360</v>
       </c>
       <c r="I9" s="13">
@@ -1909,28 +1912,28 @@
       </c>
     </row>
     <row r="10" ht="43.2" spans="1:14">
-      <c r="A10" s="8">
+      <c r="A10" s="11">
         <v>46250</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="12">
         <v>480</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="12">
         <v>60</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="12">
         <v>60</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="12">
         <v>0</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="12">
         <v>0</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="12">
         <v>0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="12">
         <v>400</v>
       </c>
       <c r="I10" s="13">
@@ -1955,28 +1958,28 @@
       </c>
     </row>
     <row r="11" ht="43.2" spans="1:14">
-      <c r="A11" s="8">
+      <c r="A11" s="11">
         <v>46251</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="12">
         <v>480</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="12">
         <v>60</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="12">
         <v>60</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="12">
         <v>45</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="12">
         <v>0</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="12">
         <v>0</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="12">
         <v>400</v>
       </c>
       <c r="I11" s="13">
@@ -2001,28 +2004,28 @@
       </c>
     </row>
     <row r="12" ht="28.8" spans="1:14">
-      <c r="A12" s="8">
+      <c r="A12" s="11">
         <v>46252</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="12">
         <v>420</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="12">
         <v>60</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="12">
         <v>90</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="12">
         <v>30</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="12">
         <v>400</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="12">
         <v>8</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="12">
         <v>240</v>
       </c>
       <c r="I12" s="13">
@@ -2047,28 +2050,28 @@
       </c>
     </row>
     <row r="13" ht="43.2" spans="1:14">
-      <c r="A13" s="8">
+      <c r="A13" s="11">
         <v>46253</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="12">
         <v>420</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="12">
         <v>60</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="12">
         <v>120</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="12">
         <v>30</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="12">
         <v>200</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="12">
         <v>4</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="12">
         <v>240</v>
       </c>
       <c r="I13" s="13">
@@ -2093,28 +2096,28 @@
       </c>
     </row>
     <row r="14" ht="43.2" spans="1:14">
-      <c r="A14" s="8">
+      <c r="A14" s="11">
         <v>46254</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="12">
         <v>480</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="12">
         <v>60</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="12">
         <v>120</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="12">
         <v>30</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="12">
         <v>350</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="12">
         <v>7</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="12">
         <v>300</v>
       </c>
       <c r="I14" s="13">
@@ -2139,28 +2142,28 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="8">
+      <c r="A15" s="11">
         <v>46255</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="12">
         <v>300</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="12">
         <v>60</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="12">
         <v>180</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="12">
         <v>30</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="12">
         <v>300</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="12">
         <v>6</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="12">
         <v>350</v>
       </c>
       <c r="I15" s="13">
@@ -2185,28 +2188,28 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="8">
+      <c r="A16" s="11">
         <v>46256</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="12">
         <v>300</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="12">
         <v>0</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="12">
         <v>240</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="12">
         <v>120</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="12">
         <v>0</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="12">
         <v>0</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="12">
         <v>240</v>
       </c>
       <c r="I16" s="13">
@@ -2231,28 +2234,28 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="8">
+      <c r="A17" s="11">
         <v>46257</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="12">
         <v>480</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="12">
         <v>0</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="12">
         <v>120</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="12">
         <v>120</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="12">
         <v>0</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="12">
         <v>0</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="12">
         <v>240</v>
       </c>
       <c r="I17" s="13">
@@ -2277,28 +2280,28 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="8">
+      <c r="A18" s="11">
         <v>46258</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="12">
         <v>300</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="12">
         <v>60</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="12">
         <v>120</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="12">
         <v>120</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="12">
         <v>150</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="12">
         <v>3</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="12">
         <v>120</v>
       </c>
       <c r="I18" s="13">
@@ -2323,28 +2326,28 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="8">
+      <c r="A19" s="11">
         <v>46259</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="12">
         <v>420</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="12">
         <v>60</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="12">
         <v>120</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="12">
         <v>60</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="12">
         <v>350</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="12">
         <v>7</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="12">
         <v>180</v>
       </c>
       <c r="I19" s="13">
@@ -2369,28 +2372,28 @@
       </c>
     </row>
     <row r="20" ht="28.8" spans="1:14">
-      <c r="A20" s="8">
+      <c r="A20" s="11">
         <v>46260</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="12">
         <v>480</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="12">
         <v>60</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="12">
         <v>180</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="12">
         <v>180</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="12">
         <v>200</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="12">
         <v>4</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="12">
         <v>180</v>
       </c>
       <c r="I20" s="13">
@@ -2415,28 +2418,28 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="8">
+      <c r="A21" s="11">
         <v>46261</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="12">
         <v>420</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="12">
         <v>60</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="12">
         <v>120</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="12">
         <v>0</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="12">
         <v>350</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="12">
         <v>7</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="12">
         <v>60</v>
       </c>
       <c r="I21" s="13">
@@ -2461,28 +2464,28 @@
       </c>
     </row>
     <row r="22" ht="43.2" spans="1:14">
-      <c r="A22" s="8">
+      <c r="A22" s="11">
         <v>46262</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="12">
         <v>540</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="12">
         <v>60</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="12">
         <v>30</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="12">
         <v>0</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="12">
         <v>300</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="12">
         <v>6</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="12">
         <v>120</v>
       </c>
       <c r="I22" s="13">
@@ -2507,28 +2510,28 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="8">
+      <c r="A23" s="11">
         <v>46263</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="12">
         <v>480</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="12">
         <v>0</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="12">
         <v>60</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="12">
         <v>120</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="12">
         <v>0</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="12">
         <v>0</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="12">
         <v>120</v>
       </c>
       <c r="I23" s="13">
@@ -2553,28 +2556,28 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="8">
+      <c r="A24" s="11">
         <v>46264</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="12">
         <v>420</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="12">
         <v>0</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="12">
         <v>180</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="12">
         <v>60</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="12">
         <v>0</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="12">
         <v>0</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="12">
         <v>180</v>
       </c>
       <c r="I24" s="13">
@@ -2599,28 +2602,28 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="8">
+      <c r="A25" s="11">
         <v>46266</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="12">
         <v>540</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="12">
         <v>60</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="12">
         <v>120</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="12">
         <v>30</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="12">
         <v>350</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="12">
         <v>7</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="12">
         <v>180</v>
       </c>
       <c r="I25" s="13">
@@ -2645,28 +2648,28 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="8">
+      <c r="A26" s="11">
         <v>46267</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="12">
         <v>540</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="12">
         <v>60</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="12">
         <v>300</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="12">
         <v>30</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="12">
         <v>200</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="12">
         <v>4</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="12">
         <v>120</v>
       </c>
       <c r="I26" s="13">
@@ -2691,28 +2694,28 @@
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:14">
-      <c r="A27" s="8">
+      <c r="A27" s="11">
         <v>46268</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="12">
         <v>480</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="12">
         <v>60</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="12">
         <v>180</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="12">
         <v>30</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="12">
         <v>350</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="12">
         <v>7</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="12">
         <v>120</v>
       </c>
       <c r="I27" s="13">
@@ -2737,28 +2740,28 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="8">
+      <c r="A28" s="11">
         <v>46269</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="12">
         <v>420</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="12">
         <v>60</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="12">
         <v>180</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="12">
         <v>30</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="12">
         <v>300</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="12">
         <v>6</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="12">
         <v>120</v>
       </c>
       <c r="I28" s="13">
@@ -2783,28 +2786,28 @@
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="8">
+      <c r="A29" s="11">
         <v>46270</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="12">
         <v>120</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="12">
         <v>0</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="12">
         <v>240</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="12">
         <v>0</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="12">
         <v>0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="12">
         <v>0</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="12">
         <v>120</v>
       </c>
       <c r="I29" s="13">
@@ -2829,28 +2832,28 @@
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="8">
+      <c r="A30" s="11">
         <v>46271</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="12">
         <v>360</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="12">
         <v>60</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="12">
         <v>120</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="12">
         <v>0</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="12">
         <v>150</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="12">
         <v>3</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="12">
         <v>120</v>
       </c>
       <c r="I30" s="13">
@@ -2875,28 +2878,28 @@
       </c>
     </row>
     <row r="31" ht="28.8" spans="1:14">
-      <c r="A31" s="8">
+      <c r="A31" s="11">
         <v>46272</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="12">
         <v>360</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="12">
         <v>60</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="12">
         <v>240</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="12">
         <v>0</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="12">
         <v>200</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="12">
         <v>4</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="12">
         <v>180</v>
       </c>
       <c r="I31" s="13">
@@ -2921,28 +2924,28 @@
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="8">
+      <c r="A32" s="11">
         <v>46273</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="12">
         <v>300</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="12">
         <v>60</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="12">
         <v>180</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="12">
         <v>0</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="12">
         <v>350</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="12">
         <v>7</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="12">
         <v>180</v>
       </c>
       <c r="I32" s="13">
@@ -2967,28 +2970,28 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="8">
+      <c r="A33" s="11">
         <v>46274</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="12">
         <v>300</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="12">
         <v>60</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="12">
         <v>120</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="12">
         <v>0</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="12">
         <v>200</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="12">
         <v>4</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="12">
         <v>180</v>
       </c>
       <c r="I33" s="13">
@@ -3013,28 +3016,28 @@
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="8">
+      <c r="A34" s="11">
         <v>46275</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="12">
         <v>420</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="12">
         <v>60</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="12">
         <v>180</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="12">
         <v>0</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="12">
         <v>350</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="12">
         <v>7</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="12">
         <v>180</v>
       </c>
       <c r="I34" s="13">
@@ -3059,28 +3062,28 @@
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="8">
+      <c r="A35" s="11">
         <v>46276</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="12">
         <v>480</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="12">
         <v>60</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="12">
         <v>120</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="12">
         <v>0</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="12">
         <v>300</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="12">
         <v>6</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="12">
         <v>180</v>
       </c>
       <c r="I35" s="13">
@@ -3105,28 +3108,28 @@
       </c>
     </row>
     <row r="36" ht="28.8" spans="1:14">
-      <c r="A36" s="8">
+      <c r="A36" s="11">
         <v>46277</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="12">
         <v>480</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="12">
         <v>0</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="12">
         <v>180</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="12">
         <v>60</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="12">
         <v>0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="12">
         <v>0</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="12">
         <v>180</v>
       </c>
       <c r="I36" s="13">
@@ -3151,28 +3154,28 @@
       </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="8">
+      <c r="A37" s="11">
         <v>46278</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="12">
         <v>540</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="12">
         <v>0</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="12">
         <v>120</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="12">
         <v>60</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="12">
         <v>0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="12">
         <v>0</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="12">
         <v>240</v>
       </c>
       <c r="I37" s="13">
@@ -3197,28 +3200,28 @@
       </c>
     </row>
     <row r="38" ht="28.8" spans="1:14">
-      <c r="A38" s="8">
+      <c r="A38" s="11">
         <v>46279</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="12">
         <v>480</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="12">
         <v>60</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="12">
         <v>120</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="12">
         <v>0</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="12">
         <v>150</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="12">
         <v>3</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="12">
         <v>240</v>
       </c>
       <c r="I38" s="13">
@@ -3243,28 +3246,28 @@
       </c>
     </row>
     <row r="39" ht="28.8" spans="1:14">
-      <c r="A39" s="8">
+      <c r="A39" s="11">
         <v>46280</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="12">
         <v>360</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="12">
         <v>60</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="12">
         <v>60</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="12">
         <v>0</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="12">
         <v>350</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="12">
         <v>7</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="12">
         <v>240</v>
       </c>
       <c r="I39" s="13">
@@ -3289,28 +3292,28 @@
       </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="8">
+      <c r="A40" s="11">
         <v>46281</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="12">
         <v>300</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="12">
         <v>60</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="12">
         <v>120</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="12">
         <v>60</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="12">
         <v>200</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="12">
         <v>4</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="12">
         <v>240</v>
       </c>
       <c r="I40" s="13">
@@ -3335,28 +3338,28 @@
       </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="8">
+      <c r="A41" s="11">
         <v>46282</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="12">
         <v>480</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="12">
         <v>60</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="12">
         <v>60</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="12">
         <v>0</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="12">
         <v>350</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="12">
         <v>7</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="12">
         <v>240</v>
       </c>
       <c r="I41" s="13">
@@ -3381,28 +3384,28 @@
       </c>
     </row>
     <row r="42" ht="43.2" spans="1:14">
-      <c r="A42" s="8">
+      <c r="A42" s="11">
         <v>46283</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="12">
         <v>240</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="12">
         <v>60</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="12">
         <v>60</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="12">
         <v>60</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="12">
         <v>300</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="12">
         <v>6</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="12">
         <v>240</v>
       </c>
       <c r="I42" s="13">
@@ -3427,28 +3430,28 @@
       </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="8">
+      <c r="A43" s="11">
         <v>46284</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="12">
         <v>600</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="12">
         <v>0</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="12">
         <v>0</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="12">
         <v>30</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="12">
         <v>100</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="12">
         <v>2</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="12">
         <v>240</v>
       </c>
       <c r="I43" s="13">
@@ -3473,28 +3476,28 @@
       </c>
     </row>
     <row r="44" ht="28.8" spans="1:14">
-      <c r="A44" s="8">
+      <c r="A44" s="11">
         <v>46285</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="12">
         <v>240</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="12">
         <v>0</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="12">
         <v>30</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="12">
         <v>120</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="12">
         <v>0</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="12">
         <v>0</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="12">
         <v>240</v>
       </c>
       <c r="I44" s="13">
@@ -3519,28 +3522,28 @@
       </c>
     </row>
     <row r="45" ht="28.8" spans="1:14">
-      <c r="A45" s="8">
+      <c r="A45" s="11">
         <v>46286</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="12">
         <v>420</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="12">
         <v>60</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="12">
         <v>60</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="12">
         <v>120</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="12">
         <v>150</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="12">
         <v>3</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="12">
         <v>240</v>
       </c>
       <c r="I45" s="13">
@@ -3565,28 +3568,28 @@
       </c>
     </row>
     <row r="46" ht="28.8" spans="1:14">
-      <c r="A46" s="8">
+      <c r="A46" s="11">
         <v>46287</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="12">
         <v>360</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="12">
         <v>60</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="12">
         <v>60</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="12">
         <v>30</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="12">
         <v>350</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="12">
         <v>7</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="12">
         <v>240</v>
       </c>
       <c r="I46" s="13">
@@ -3611,28 +3614,28 @@
       </c>
     </row>
     <row r="47" ht="28.8" spans="1:14">
-      <c r="A47" s="8">
+      <c r="A47" s="11">
         <v>46288</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="12">
         <v>450</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="12">
         <v>60</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="12">
         <v>120</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="12">
         <v>60</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="12">
         <v>200</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="12">
         <v>4</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="12">
         <v>120</v>
       </c>
       <c r="I47" s="13">
@@ -3657,36 +3660,60 @@
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="13" t="str">
+      <c r="A48" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B48" s="12">
+        <v>240</v>
+      </c>
+      <c r="C48" s="12">
+        <v>60</v>
+      </c>
+      <c r="D48" s="12">
+        <v>120</v>
+      </c>
+      <c r="E48" s="12">
+        <v>120</v>
+      </c>
+      <c r="F48" s="12">
+        <v>350</v>
+      </c>
+      <c r="G48" s="12">
+        <v>7</v>
+      </c>
+      <c r="H48" s="12">
+        <v>300</v>
+      </c>
+      <c r="I48" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="13" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J48" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L48" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M48" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N48" s="16" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
       <c r="I49" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3701,14 +3728,14 @@
       <c r="N49" s="16"/>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
       <c r="I50" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3723,14 +3750,14 @@
       <c r="N50" s="16"/>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
       <c r="I51" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3745,14 +3772,14 @@
       <c r="N51" s="16"/>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
       <c r="I52" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3767,14 +3794,14 @@
       <c r="N52" s="16"/>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
       <c r="I53" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3789,14 +3816,14 @@
       <c r="N53" s="16"/>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
+      <c r="A54" s="11"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
       <c r="I54" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3811,14 +3838,14 @@
       <c r="N54" s="16"/>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
       <c r="I55" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3833,14 +3860,14 @@
       <c r="N55" s="16"/>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
       <c r="I56" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3855,14 +3882,14 @@
       <c r="N56" s="16"/>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
       <c r="I57" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3877,14 +3904,14 @@
       <c r="N57" s="16"/>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
+      <c r="A58" s="11"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
       <c r="I58" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3899,14 +3926,14 @@
       <c r="N58" s="16"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
       <c r="I59" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3921,14 +3948,14 @@
       <c r="N59" s="16"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
       <c r="I60" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3943,14 +3970,14 @@
       <c r="N60" s="16"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
+      <c r="A61" s="11"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
       <c r="I61" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3965,14 +3992,14 @@
       <c r="N61" s="16"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
+      <c r="A62" s="11"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
       <c r="I62" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3987,14 +4014,14 @@
       <c r="N62" s="16"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
       <c r="I63" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4009,14 +4036,14 @@
       <c r="N63" s="16"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
+      <c r="A64" s="11"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
       <c r="I64" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4031,14 +4058,14 @@
       <c r="N64" s="16"/>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
       <c r="I65" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4053,14 +4080,14 @@
       <c r="N65" s="16"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
+      <c r="A66" s="11"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
       <c r="I66" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4075,14 +4102,14 @@
       <c r="N66" s="16"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
       <c r="I67" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4097,14 +4124,14 @@
       <c r="N67" s="16"/>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
+      <c r="A68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
       <c r="I68" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4119,14 +4146,14 @@
       <c r="N68" s="16"/>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
       <c r="I69" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4141,14 +4168,14 @@
       <c r="N69" s="16"/>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
       <c r="I70" s="13" t="str">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
@@ -4163,14 +4190,14 @@
       <c r="N70" s="16"/>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
       <c r="I71" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4185,14 +4212,14 @@
       <c r="N71" s="16"/>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
       <c r="I72" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4207,14 +4234,14 @@
       <c r="N72" s="16"/>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
       <c r="I73" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4229,14 +4256,14 @@
       <c r="N73" s="16"/>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
       <c r="I74" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4251,14 +4278,14 @@
       <c r="N74" s="16"/>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
       <c r="I75" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4273,14 +4300,14 @@
       <c r="N75" s="16"/>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
       <c r="I76" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4295,14 +4322,14 @@
       <c r="N76" s="16"/>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
+      <c r="A77" s="11"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
       <c r="I77" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4317,14 +4344,14 @@
       <c r="N77" s="16"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
+      <c r="A78" s="11"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
       <c r="I78" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4339,14 +4366,14 @@
       <c r="N78" s="16"/>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
+      <c r="A79" s="11"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
       <c r="I79" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4361,14 +4388,14 @@
       <c r="N79" s="16"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
       <c r="I80" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4383,14 +4410,14 @@
       <c r="N80" s="16"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
       <c r="I81" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4405,14 +4432,14 @@
       <c r="N81" s="16"/>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="8"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
+      <c r="A82" s="11"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
+      <c r="H82" s="12"/>
       <c r="I82" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4427,14 +4454,14 @@
       <c r="N82" s="16"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="8"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-      <c r="H83" s="9"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
+      <c r="H83" s="12"/>
       <c r="I83" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4449,14 +4476,14 @@
       <c r="N83" s="16"/>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="8"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
       <c r="I84" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4471,14 +4498,14 @@
       <c r="N84" s="16"/>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="8"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="9"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
+      <c r="H85" s="12"/>
       <c r="I85" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4493,14 +4520,14 @@
       <c r="N85" s="16"/>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
+      <c r="A86" s="11"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
       <c r="I86" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4515,14 +4542,14 @@
       <c r="N86" s="16"/>
     </row>
     <row r="87" spans="1:14">
-      <c r="A87" s="8"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="9"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="12"/>
       <c r="I87" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4537,14 +4564,14 @@
       <c r="N87" s="16"/>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="8"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="12"/>
       <c r="I88" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4559,14 +4586,14 @@
       <c r="N88" s="16"/>
     </row>
     <row r="89" spans="1:14">
-      <c r="A89" s="8"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="9"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
+      <c r="H89" s="12"/>
       <c r="I89" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4581,14 +4608,14 @@
       <c r="N89" s="16"/>
     </row>
     <row r="90" spans="1:14">
-      <c r="A90" s="8"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
+      <c r="A90" s="11"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
+      <c r="H90" s="12"/>
       <c r="I90" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4603,14 +4630,14 @@
       <c r="N90" s="16"/>
     </row>
     <row r="91" spans="1:14">
-      <c r="A91" s="8"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
+      <c r="A91" s="11"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
       <c r="I91" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4625,14 +4652,14 @@
       <c r="N91" s="16"/>
     </row>
     <row r="92" spans="1:14">
-      <c r="A92" s="8"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
+      <c r="H92" s="12"/>
       <c r="I92" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4647,14 +4674,14 @@
       <c r="N92" s="16"/>
     </row>
     <row r="93" spans="1:14">
-      <c r="A93" s="8"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
+      <c r="A93" s="11"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="12"/>
       <c r="I93" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4669,14 +4696,14 @@
       <c r="N93" s="16"/>
     </row>
     <row r="94" spans="1:14">
-      <c r="A94" s="8"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
+      <c r="A94" s="11"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
       <c r="I94" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4691,14 +4718,14 @@
       <c r="N94" s="16"/>
     </row>
     <row r="95" spans="1:14">
-      <c r="A95" s="8"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
+      <c r="A95" s="11"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
       <c r="I95" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4713,14 +4740,14 @@
       <c r="N95" s="16"/>
     </row>
     <row r="96" spans="1:14">
-      <c r="A96" s="8"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
+      <c r="A96" s="11"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
       <c r="I96" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4735,14 +4762,14 @@
       <c r="N96" s="16"/>
     </row>
     <row r="97" spans="1:14">
-      <c r="A97" s="8"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
+      <c r="A97" s="11"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
       <c r="I97" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4757,14 +4784,14 @@
       <c r="N97" s="16"/>
     </row>
     <row r="98" spans="1:14">
-      <c r="A98" s="8"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
+      <c r="A98" s="11"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
       <c r="I98" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4779,14 +4806,14 @@
       <c r="N98" s="16"/>
     </row>
     <row r="99" spans="1:14">
-      <c r="A99" s="8"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
+      <c r="A99" s="11"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="12"/>
       <c r="I99" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4801,14 +4828,14 @@
       <c r="N99" s="16"/>
     </row>
     <row r="100" spans="1:14">
-      <c r="A100" s="8"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
+      <c r="A100" s="11"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
       <c r="I100" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4823,14 +4850,14 @@
       <c r="N100" s="16"/>
     </row>
     <row r="101" spans="1:14">
-      <c r="A101" s="8"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
+      <c r="A101" s="11"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
+      <c r="H101" s="12"/>
       <c r="I101" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4845,14 +4872,14 @@
       <c r="N101" s="16"/>
     </row>
     <row r="102" spans="1:14">
-      <c r="A102" s="8"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="9"/>
-      <c r="D102" s="9"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="9"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
+      <c r="A102" s="11"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12"/>
       <c r="I102" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4867,14 +4894,14 @@
       <c r="N102" s="16"/>
     </row>
     <row r="103" spans="1:14">
-      <c r="A103" s="8"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
+      <c r="A103" s="11"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+      <c r="H103" s="12"/>
       <c r="I103" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4889,14 +4916,14 @@
       <c r="N103" s="16"/>
     </row>
     <row r="104" spans="1:14">
-      <c r="A104" s="8"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
+      <c r="A104" s="11"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
+      <c r="H104" s="12"/>
       <c r="I104" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4911,14 +4938,14 @@
       <c r="N104" s="16"/>
     </row>
     <row r="105" spans="1:14">
-      <c r="A105" s="8"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
-      <c r="E105" s="9"/>
-      <c r="F105" s="9"/>
-      <c r="G105" s="9"/>
-      <c r="H105" s="9"/>
+      <c r="A105" s="11"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
+      <c r="H105" s="12"/>
       <c r="I105" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4933,14 +4960,14 @@
       <c r="N105" s="16"/>
     </row>
     <row r="106" spans="1:14">
-      <c r="A106" s="8"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
+      <c r="A106" s="11"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="12"/>
       <c r="I106" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4955,14 +4982,14 @@
       <c r="N106" s="16"/>
     </row>
     <row r="107" spans="1:14">
-      <c r="A107" s="8"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="9"/>
-      <c r="D107" s="9"/>
-      <c r="E107" s="9"/>
-      <c r="F107" s="9"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
+      <c r="A107" s="11"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="12"/>
       <c r="I107" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4977,14 +5004,14 @@
       <c r="N107" s="16"/>
     </row>
     <row r="108" spans="1:14">
-      <c r="A108" s="8"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
-      <c r="D108" s="9"/>
-      <c r="E108" s="9"/>
-      <c r="F108" s="9"/>
-      <c r="G108" s="9"/>
-      <c r="H108" s="9"/>
+      <c r="A108" s="11"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
+      <c r="H108" s="12"/>
       <c r="I108" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4999,14 +5026,14 @@
       <c r="N108" s="16"/>
     </row>
     <row r="109" spans="1:14">
-      <c r="A109" s="8"/>
-      <c r="B109" s="9"/>
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="9"/>
-      <c r="G109" s="9"/>
-      <c r="H109" s="9"/>
+      <c r="A109" s="11"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
+      <c r="H109" s="12"/>
       <c r="I109" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5021,14 +5048,14 @@
       <c r="N109" s="16"/>
     </row>
     <row r="110" spans="1:14">
-      <c r="A110" s="8"/>
-      <c r="B110" s="9"/>
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
+      <c r="A110" s="11"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="12"/>
       <c r="I110" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5043,14 +5070,14 @@
       <c r="N110" s="16"/>
     </row>
     <row r="111" spans="1:14">
-      <c r="A111" s="8"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
-      <c r="F111" s="9"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
+      <c r="A111" s="11"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
+      <c r="H111" s="12"/>
       <c r="I111" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5065,14 +5092,14 @@
       <c r="N111" s="16"/>
     </row>
     <row r="112" spans="1:14">
-      <c r="A112" s="8"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
+      <c r="A112" s="11"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
+      <c r="H112" s="12"/>
       <c r="I112" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5087,14 +5114,14 @@
       <c r="N112" s="16"/>
     </row>
     <row r="113" spans="1:14">
-      <c r="A113" s="8"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="9"/>
-      <c r="D113" s="9"/>
-      <c r="E113" s="9"/>
-      <c r="F113" s="9"/>
-      <c r="G113" s="9"/>
-      <c r="H113" s="9"/>
+      <c r="A113" s="11"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
+      <c r="H113" s="12"/>
       <c r="I113" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5109,14 +5136,14 @@
       <c r="N113" s="16"/>
     </row>
     <row r="114" spans="1:14">
-      <c r="A114" s="8"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
-      <c r="E114" s="9"/>
-      <c r="F114" s="9"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
+      <c r="A114" s="11"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
+      <c r="H114" s="12"/>
       <c r="I114" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5131,14 +5158,14 @@
       <c r="N114" s="16"/>
     </row>
     <row r="115" spans="1:14">
-      <c r="A115" s="8"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="9"/>
-      <c r="F115" s="9"/>
-      <c r="G115" s="9"/>
-      <c r="H115" s="9"/>
+      <c r="A115" s="11"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
+      <c r="H115" s="12"/>
       <c r="I115" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5153,14 +5180,14 @@
       <c r="N115" s="16"/>
     </row>
     <row r="116" spans="1:14">
-      <c r="A116" s="8"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
-      <c r="D116" s="9"/>
-      <c r="E116" s="9"/>
-      <c r="F116" s="9"/>
-      <c r="G116" s="9"/>
-      <c r="H116" s="9"/>
+      <c r="A116" s="11"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
+      <c r="H116" s="12"/>
       <c r="I116" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5175,14 +5202,14 @@
       <c r="N116" s="16"/>
     </row>
     <row r="117" spans="1:14">
-      <c r="A117" s="8"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9"/>
-      <c r="G117" s="9"/>
-      <c r="H117" s="9"/>
+      <c r="A117" s="11"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
       <c r="I117" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5197,14 +5224,14 @@
       <c r="N117" s="16"/>
     </row>
     <row r="118" spans="1:14">
-      <c r="A118" s="8"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
+      <c r="A118" s="11"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
+      <c r="H118" s="12"/>
       <c r="I118" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5219,14 +5246,14 @@
       <c r="N118" s="16"/>
     </row>
     <row r="119" spans="1:14">
-      <c r="A119" s="8"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
-      <c r="E119" s="9"/>
-      <c r="F119" s="9"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="9"/>
+      <c r="A119" s="11"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
+      <c r="H119" s="12"/>
       <c r="I119" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5241,14 +5268,14 @@
       <c r="N119" s="16"/>
     </row>
     <row r="120" spans="1:14">
-      <c r="A120" s="8"/>
-      <c r="B120" s="9"/>
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
-      <c r="E120" s="9"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="9"/>
-      <c r="H120" s="9"/>
+      <c r="A120" s="11"/>
+      <c r="B120" s="12"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
+      <c r="H120" s="12"/>
       <c r="I120" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5263,14 +5290,14 @@
       <c r="N120" s="16"/>
     </row>
     <row r="121" spans="1:14">
-      <c r="A121" s="8"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
-      <c r="E121" s="9"/>
-      <c r="F121" s="9"/>
-      <c r="G121" s="9"/>
-      <c r="H121" s="9"/>
+      <c r="A121" s="11"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
       <c r="I121" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5285,14 +5312,14 @@
       <c r="N121" s="16"/>
     </row>
     <row r="122" spans="1:14">
-      <c r="A122" s="8"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
+      <c r="A122" s="11"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
       <c r="I122" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5307,14 +5334,14 @@
       <c r="N122" s="16"/>
     </row>
     <row r="123" spans="1:14">
-      <c r="A123" s="8"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
+      <c r="A123" s="11"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="12"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
       <c r="I123" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5329,14 +5356,14 @@
       <c r="N123" s="16"/>
     </row>
     <row r="124" spans="1:14">
-      <c r="A124" s="8"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="9"/>
+      <c r="A124" s="11"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
       <c r="I124" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5351,14 +5378,14 @@
       <c r="N124" s="16"/>
     </row>
     <row r="125" spans="1:14">
-      <c r="A125" s="8"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="9"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="9"/>
+      <c r="A125" s="11"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="12"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
+      <c r="H125" s="12"/>
       <c r="I125" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5373,14 +5400,14 @@
       <c r="N125" s="16"/>
     </row>
     <row r="126" spans="1:14">
-      <c r="A126" s="8"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
+      <c r="A126" s="11"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="12"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="12"/>
       <c r="I126" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5395,14 +5422,14 @@
       <c r="N126" s="16"/>
     </row>
     <row r="127" spans="1:14">
-      <c r="A127" s="8"/>
-      <c r="B127" s="9"/>
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
+      <c r="A127" s="11"/>
+      <c r="B127" s="12"/>
+      <c r="C127" s="12"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="12"/>
       <c r="I127" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5417,14 +5444,14 @@
       <c r="N127" s="16"/>
     </row>
     <row r="128" spans="1:14">
-      <c r="A128" s="8"/>
-      <c r="B128" s="9"/>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="9"/>
+      <c r="A128" s="11"/>
+      <c r="B128" s="12"/>
+      <c r="C128" s="12"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="12"/>
       <c r="I128" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5439,14 +5466,14 @@
       <c r="N128" s="16"/>
     </row>
     <row r="129" spans="1:14">
-      <c r="A129" s="8"/>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="9"/>
+      <c r="A129" s="11"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="12"/>
+      <c r="H129" s="12"/>
       <c r="I129" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5461,14 +5488,14 @@
       <c r="N129" s="16"/>
     </row>
     <row r="130" spans="1:14">
-      <c r="A130" s="8"/>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
+      <c r="A130" s="11"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="12"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
       <c r="I130" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5483,14 +5510,14 @@
       <c r="N130" s="16"/>
     </row>
     <row r="131" spans="1:14">
-      <c r="A131" s="8"/>
-      <c r="B131" s="9"/>
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
+      <c r="A131" s="11"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="12"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="12"/>
+      <c r="H131" s="12"/>
       <c r="I131" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5505,14 +5532,14 @@
       <c r="N131" s="16"/>
     </row>
     <row r="132" spans="1:14">
-      <c r="A132" s="8"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="9"/>
-      <c r="H132" s="9"/>
+      <c r="A132" s="11"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="12"/>
+      <c r="D132" s="12"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="12"/>
       <c r="I132" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5527,14 +5554,14 @@
       <c r="N132" s="16"/>
     </row>
     <row r="133" spans="1:14">
-      <c r="A133" s="8"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="9"/>
-      <c r="G133" s="9"/>
-      <c r="H133" s="9"/>
+      <c r="A133" s="11"/>
+      <c r="B133" s="12"/>
+      <c r="C133" s="12"/>
+      <c r="D133" s="12"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="12"/>
       <c r="I133" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5549,14 +5576,14 @@
       <c r="N133" s="16"/>
     </row>
     <row r="134" spans="1:14">
-      <c r="A134" s="8"/>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
+      <c r="A134" s="11"/>
+      <c r="B134" s="12"/>
+      <c r="C134" s="12"/>
+      <c r="D134" s="12"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="12"/>
       <c r="I134" s="13" t="str">
         <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
@@ -5571,14 +5598,14 @@
       <c r="N134" s="16"/>
     </row>
     <row r="135" spans="1:14">
-      <c r="A135" s="8"/>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
+      <c r="A135" s="11"/>
+      <c r="B135" s="12"/>
+      <c r="C135" s="12"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="12"/>
+      <c r="H135" s="12"/>
       <c r="I135" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5593,14 +5620,14 @@
       <c r="N135" s="16"/>
     </row>
     <row r="136" spans="1:14">
-      <c r="A136" s="8"/>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
-      <c r="F136" s="9"/>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
+      <c r="A136" s="11"/>
+      <c r="B136" s="12"/>
+      <c r="C136" s="12"/>
+      <c r="D136" s="12"/>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="12"/>
+      <c r="H136" s="12"/>
       <c r="I136" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5615,14 +5642,14 @@
       <c r="N136" s="16"/>
     </row>
     <row r="137" spans="1:14">
-      <c r="A137" s="8"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="9"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
-      <c r="F137" s="9"/>
-      <c r="G137" s="9"/>
-      <c r="H137" s="9"/>
+      <c r="A137" s="11"/>
+      <c r="B137" s="12"/>
+      <c r="C137" s="12"/>
+      <c r="D137" s="12"/>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="12"/>
       <c r="I137" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5637,14 +5664,14 @@
       <c r="N137" s="16"/>
     </row>
     <row r="138" spans="1:14">
-      <c r="A138" s="8"/>
-      <c r="B138" s="9"/>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
+      <c r="A138" s="11"/>
+      <c r="B138" s="12"/>
+      <c r="C138" s="12"/>
+      <c r="D138" s="12"/>
+      <c r="E138" s="12"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+      <c r="H138" s="12"/>
       <c r="I138" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5659,14 +5686,14 @@
       <c r="N138" s="16"/>
     </row>
     <row r="139" spans="1:14">
-      <c r="A139" s="8"/>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
+      <c r="A139" s="11"/>
+      <c r="B139" s="12"/>
+      <c r="C139" s="12"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12"/>
+      <c r="G139" s="12"/>
+      <c r="H139" s="12"/>
       <c r="I139" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5681,14 +5708,14 @@
       <c r="N139" s="16"/>
     </row>
     <row r="140" spans="1:14">
-      <c r="A140" s="8"/>
-      <c r="B140" s="9"/>
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
+      <c r="A140" s="11"/>
+      <c r="B140" s="12"/>
+      <c r="C140" s="12"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="12"/>
+      <c r="F140" s="12"/>
+      <c r="G140" s="12"/>
+      <c r="H140" s="12"/>
       <c r="I140" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5703,14 +5730,14 @@
       <c r="N140" s="16"/>
     </row>
     <row r="141" spans="1:14">
-      <c r="A141" s="8"/>
-      <c r="B141" s="9"/>
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
+      <c r="A141" s="11"/>
+      <c r="B141" s="12"/>
+      <c r="C141" s="12"/>
+      <c r="D141" s="12"/>
+      <c r="E141" s="12"/>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
+      <c r="H141" s="12"/>
       <c r="I141" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5725,14 +5752,14 @@
       <c r="N141" s="16"/>
     </row>
     <row r="142" spans="1:14">
-      <c r="A142" s="8"/>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
+      <c r="A142" s="11"/>
+      <c r="B142" s="12"/>
+      <c r="C142" s="12"/>
+      <c r="D142" s="12"/>
+      <c r="E142" s="12"/>
+      <c r="F142" s="12"/>
+      <c r="G142" s="12"/>
+      <c r="H142" s="12"/>
       <c r="I142" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5747,14 +5774,14 @@
       <c r="N142" s="16"/>
     </row>
     <row r="143" spans="1:14">
-      <c r="A143" s="8"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
+      <c r="A143" s="11"/>
+      <c r="B143" s="12"/>
+      <c r="C143" s="12"/>
+      <c r="D143" s="12"/>
+      <c r="E143" s="12"/>
+      <c r="F143" s="12"/>
+      <c r="G143" s="12"/>
+      <c r="H143" s="12"/>
       <c r="I143" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5769,14 +5796,14 @@
       <c r="N143" s="16"/>
     </row>
     <row r="144" spans="1:14">
-      <c r="A144" s="8"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
+      <c r="A144" s="11"/>
+      <c r="B144" s="12"/>
+      <c r="C144" s="12"/>
+      <c r="D144" s="12"/>
+      <c r="E144" s="12"/>
+      <c r="F144" s="12"/>
+      <c r="G144" s="12"/>
+      <c r="H144" s="12"/>
       <c r="I144" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5791,14 +5818,14 @@
       <c r="N144" s="16"/>
     </row>
     <row r="145" spans="1:14">
-      <c r="A145" s="8"/>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
+      <c r="A145" s="11"/>
+      <c r="B145" s="12"/>
+      <c r="C145" s="12"/>
+      <c r="D145" s="12"/>
+      <c r="E145" s="12"/>
+      <c r="F145" s="12"/>
+      <c r="G145" s="12"/>
+      <c r="H145" s="12"/>
       <c r="I145" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5813,14 +5840,14 @@
       <c r="N145" s="16"/>
     </row>
     <row r="146" spans="1:14">
-      <c r="A146" s="8"/>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
+      <c r="A146" s="11"/>
+      <c r="B146" s="12"/>
+      <c r="C146" s="12"/>
+      <c r="D146" s="12"/>
+      <c r="E146" s="12"/>
+      <c r="F146" s="12"/>
+      <c r="G146" s="12"/>
+      <c r="H146" s="12"/>
       <c r="I146" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5835,14 +5862,14 @@
       <c r="N146" s="16"/>
     </row>
     <row r="147" spans="1:14">
-      <c r="A147" s="8"/>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
-      <c r="F147" s="9"/>
-      <c r="G147" s="9"/>
-      <c r="H147" s="9"/>
+      <c r="A147" s="11"/>
+      <c r="B147" s="12"/>
+      <c r="C147" s="12"/>
+      <c r="D147" s="12"/>
+      <c r="E147" s="12"/>
+      <c r="F147" s="12"/>
+      <c r="G147" s="12"/>
+      <c r="H147" s="12"/>
       <c r="I147" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5857,14 +5884,14 @@
       <c r="N147" s="16"/>
     </row>
     <row r="148" spans="1:14">
-      <c r="A148" s="8"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
+      <c r="A148" s="11"/>
+      <c r="B148" s="12"/>
+      <c r="C148" s="12"/>
+      <c r="D148" s="12"/>
+      <c r="E148" s="12"/>
+      <c r="F148" s="12"/>
+      <c r="G148" s="12"/>
+      <c r="H148" s="12"/>
       <c r="I148" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5879,14 +5906,14 @@
       <c r="N148" s="16"/>
     </row>
     <row r="149" spans="1:14">
-      <c r="A149" s="8"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="9"/>
-      <c r="D149" s="9"/>
-      <c r="E149" s="9"/>
-      <c r="F149" s="9"/>
-      <c r="G149" s="9"/>
-      <c r="H149" s="9"/>
+      <c r="A149" s="11"/>
+      <c r="B149" s="12"/>
+      <c r="C149" s="12"/>
+      <c r="D149" s="12"/>
+      <c r="E149" s="12"/>
+      <c r="F149" s="12"/>
+      <c r="G149" s="12"/>
+      <c r="H149" s="12"/>
       <c r="I149" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5901,14 +5928,14 @@
       <c r="N149" s="16"/>
     </row>
     <row r="150" spans="1:14">
-      <c r="A150" s="8"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
-      <c r="D150" s="9"/>
-      <c r="E150" s="9"/>
-      <c r="F150" s="9"/>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
+      <c r="A150" s="11"/>
+      <c r="B150" s="12"/>
+      <c r="C150" s="12"/>
+      <c r="D150" s="12"/>
+      <c r="E150" s="12"/>
+      <c r="F150" s="12"/>
+      <c r="G150" s="12"/>
+      <c r="H150" s="12"/>
       <c r="I150" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5923,14 +5950,14 @@
       <c r="N150" s="16"/>
     </row>
     <row r="151" spans="1:14">
-      <c r="A151" s="8"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
-      <c r="D151" s="9"/>
-      <c r="E151" s="9"/>
-      <c r="F151" s="9"/>
-      <c r="G151" s="9"/>
-      <c r="H151" s="9"/>
+      <c r="A151" s="11"/>
+      <c r="B151" s="12"/>
+      <c r="C151" s="12"/>
+      <c r="D151" s="12"/>
+      <c r="E151" s="12"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="12"/>
+      <c r="H151" s="12"/>
       <c r="I151" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5945,14 +5972,14 @@
       <c r="N151" s="16"/>
     </row>
     <row r="152" spans="1:14">
-      <c r="A152" s="8"/>
-      <c r="B152" s="9"/>
-      <c r="C152" s="9"/>
-      <c r="D152" s="9"/>
-      <c r="E152" s="9"/>
-      <c r="F152" s="9"/>
-      <c r="G152" s="9"/>
-      <c r="H152" s="9"/>
+      <c r="A152" s="11"/>
+      <c r="B152" s="12"/>
+      <c r="C152" s="12"/>
+      <c r="D152" s="12"/>
+      <c r="E152" s="12"/>
+      <c r="F152" s="12"/>
+      <c r="G152" s="12"/>
+      <c r="H152" s="12"/>
       <c r="I152" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5967,14 +5994,14 @@
       <c r="N152" s="16"/>
     </row>
     <row r="153" spans="1:14">
-      <c r="A153" s="8"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9"/>
-      <c r="E153" s="9"/>
-      <c r="F153" s="9"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="9"/>
+      <c r="A153" s="11"/>
+      <c r="B153" s="12"/>
+      <c r="C153" s="12"/>
+      <c r="D153" s="12"/>
+      <c r="E153" s="12"/>
+      <c r="F153" s="12"/>
+      <c r="G153" s="12"/>
+      <c r="H153" s="12"/>
       <c r="I153" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5989,14 +6016,14 @@
       <c r="N153" s="16"/>
     </row>
     <row r="154" spans="1:14">
-      <c r="A154" s="8"/>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
-      <c r="D154" s="9"/>
-      <c r="E154" s="9"/>
-      <c r="F154" s="9"/>
-      <c r="G154" s="9"/>
-      <c r="H154" s="9"/>
+      <c r="A154" s="11"/>
+      <c r="B154" s="12"/>
+      <c r="C154" s="12"/>
+      <c r="D154" s="12"/>
+      <c r="E154" s="12"/>
+      <c r="F154" s="12"/>
+      <c r="G154" s="12"/>
+      <c r="H154" s="12"/>
       <c r="I154" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6011,14 +6038,14 @@
       <c r="N154" s="16"/>
     </row>
     <row r="155" spans="1:14">
-      <c r="A155" s="8"/>
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
-      <c r="D155" s="9"/>
-      <c r="E155" s="9"/>
-      <c r="F155" s="9"/>
-      <c r="G155" s="9"/>
-      <c r="H155" s="9"/>
+      <c r="A155" s="11"/>
+      <c r="B155" s="12"/>
+      <c r="C155" s="12"/>
+      <c r="D155" s="12"/>
+      <c r="E155" s="12"/>
+      <c r="F155" s="12"/>
+      <c r="G155" s="12"/>
+      <c r="H155" s="12"/>
       <c r="I155" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6033,14 +6060,14 @@
       <c r="N155" s="16"/>
     </row>
     <row r="156" spans="1:14">
-      <c r="A156" s="8"/>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
-      <c r="D156" s="9"/>
-      <c r="E156" s="9"/>
-      <c r="F156" s="9"/>
-      <c r="G156" s="9"/>
-      <c r="H156" s="9"/>
+      <c r="A156" s="11"/>
+      <c r="B156" s="12"/>
+      <c r="C156" s="12"/>
+      <c r="D156" s="12"/>
+      <c r="E156" s="12"/>
+      <c r="F156" s="12"/>
+      <c r="G156" s="12"/>
+      <c r="H156" s="12"/>
       <c r="I156" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6055,14 +6082,14 @@
       <c r="N156" s="16"/>
     </row>
     <row r="157" spans="1:14">
-      <c r="A157" s="8"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
-      <c r="D157" s="9"/>
-      <c r="E157" s="9"/>
-      <c r="F157" s="9"/>
-      <c r="G157" s="9"/>
-      <c r="H157" s="9"/>
+      <c r="A157" s="11"/>
+      <c r="B157" s="12"/>
+      <c r="C157" s="12"/>
+      <c r="D157" s="12"/>
+      <c r="E157" s="12"/>
+      <c r="F157" s="12"/>
+      <c r="G157" s="12"/>
+      <c r="H157" s="12"/>
       <c r="I157" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6077,14 +6104,14 @@
       <c r="N157" s="16"/>
     </row>
     <row r="158" spans="1:14">
-      <c r="A158" s="8"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="9"/>
-      <c r="D158" s="9"/>
-      <c r="E158" s="9"/>
-      <c r="F158" s="9"/>
-      <c r="G158" s="9"/>
-      <c r="H158" s="9"/>
+      <c r="A158" s="11"/>
+      <c r="B158" s="12"/>
+      <c r="C158" s="12"/>
+      <c r="D158" s="12"/>
+      <c r="E158" s="12"/>
+      <c r="F158" s="12"/>
+      <c r="G158" s="12"/>
+      <c r="H158" s="12"/>
       <c r="I158" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6099,14 +6126,14 @@
       <c r="N158" s="16"/>
     </row>
     <row r="159" spans="1:14">
-      <c r="A159" s="8"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
-      <c r="D159" s="9"/>
-      <c r="E159" s="9"/>
-      <c r="F159" s="9"/>
-      <c r="G159" s="9"/>
-      <c r="H159" s="9"/>
+      <c r="A159" s="11"/>
+      <c r="B159" s="12"/>
+      <c r="C159" s="12"/>
+      <c r="D159" s="12"/>
+      <c r="E159" s="12"/>
+      <c r="F159" s="12"/>
+      <c r="G159" s="12"/>
+      <c r="H159" s="12"/>
       <c r="I159" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6121,14 +6148,14 @@
       <c r="N159" s="16"/>
     </row>
     <row r="160" spans="1:14">
-      <c r="A160" s="8"/>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
-      <c r="D160" s="9"/>
-      <c r="E160" s="9"/>
-      <c r="F160" s="9"/>
-      <c r="G160" s="9"/>
-      <c r="H160" s="9"/>
+      <c r="A160" s="11"/>
+      <c r="B160" s="12"/>
+      <c r="C160" s="12"/>
+      <c r="D160" s="12"/>
+      <c r="E160" s="12"/>
+      <c r="F160" s="12"/>
+      <c r="G160" s="12"/>
+      <c r="H160" s="12"/>
       <c r="I160" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6143,14 +6170,14 @@
       <c r="N160" s="16"/>
     </row>
     <row r="161" spans="1:14">
-      <c r="A161" s="8"/>
-      <c r="B161" s="9"/>
-      <c r="C161" s="9"/>
-      <c r="D161" s="9"/>
-      <c r="E161" s="9"/>
-      <c r="F161" s="9"/>
-      <c r="G161" s="9"/>
-      <c r="H161" s="9"/>
+      <c r="A161" s="11"/>
+      <c r="B161" s="12"/>
+      <c r="C161" s="12"/>
+      <c r="D161" s="12"/>
+      <c r="E161" s="12"/>
+      <c r="F161" s="12"/>
+      <c r="G161" s="12"/>
+      <c r="H161" s="12"/>
       <c r="I161" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6165,14 +6192,14 @@
       <c r="N161" s="16"/>
     </row>
     <row r="162" spans="1:14">
-      <c r="A162" s="8"/>
-      <c r="B162" s="9"/>
-      <c r="C162" s="9"/>
-      <c r="D162" s="9"/>
-      <c r="E162" s="9"/>
-      <c r="F162" s="9"/>
-      <c r="G162" s="9"/>
-      <c r="H162" s="9"/>
+      <c r="A162" s="11"/>
+      <c r="B162" s="12"/>
+      <c r="C162" s="12"/>
+      <c r="D162" s="12"/>
+      <c r="E162" s="12"/>
+      <c r="F162" s="12"/>
+      <c r="G162" s="12"/>
+      <c r="H162" s="12"/>
       <c r="I162" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6187,14 +6214,14 @@
       <c r="N162" s="16"/>
     </row>
     <row r="163" spans="1:14">
-      <c r="A163" s="8"/>
-      <c r="B163" s="9"/>
-      <c r="C163" s="9"/>
-      <c r="D163" s="9"/>
-      <c r="E163" s="9"/>
-      <c r="F163" s="9"/>
-      <c r="G163" s="9"/>
-      <c r="H163" s="9"/>
+      <c r="A163" s="11"/>
+      <c r="B163" s="12"/>
+      <c r="C163" s="12"/>
+      <c r="D163" s="12"/>
+      <c r="E163" s="12"/>
+      <c r="F163" s="12"/>
+      <c r="G163" s="12"/>
+      <c r="H163" s="12"/>
       <c r="I163" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6209,14 +6236,14 @@
       <c r="N163" s="16"/>
     </row>
     <row r="164" spans="1:14">
-      <c r="A164" s="8"/>
-      <c r="B164" s="9"/>
-      <c r="C164" s="9"/>
-      <c r="D164" s="9"/>
-      <c r="E164" s="9"/>
-      <c r="F164" s="9"/>
-      <c r="G164" s="9"/>
-      <c r="H164" s="9"/>
+      <c r="A164" s="11"/>
+      <c r="B164" s="12"/>
+      <c r="C164" s="12"/>
+      <c r="D164" s="12"/>
+      <c r="E164" s="12"/>
+      <c r="F164" s="12"/>
+      <c r="G164" s="12"/>
+      <c r="H164" s="12"/>
       <c r="I164" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6231,14 +6258,14 @@
       <c r="N164" s="16"/>
     </row>
     <row r="165" spans="1:14">
-      <c r="A165" s="8"/>
-      <c r="B165" s="9"/>
-      <c r="C165" s="9"/>
-      <c r="D165" s="9"/>
-      <c r="E165" s="9"/>
-      <c r="F165" s="9"/>
-      <c r="G165" s="9"/>
-      <c r="H165" s="9"/>
+      <c r="A165" s="11"/>
+      <c r="B165" s="12"/>
+      <c r="C165" s="12"/>
+      <c r="D165" s="12"/>
+      <c r="E165" s="12"/>
+      <c r="F165" s="12"/>
+      <c r="G165" s="12"/>
+      <c r="H165" s="12"/>
       <c r="I165" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6253,14 +6280,14 @@
       <c r="N165" s="16"/>
     </row>
     <row r="166" spans="1:14">
-      <c r="A166" s="8"/>
-      <c r="B166" s="9"/>
-      <c r="C166" s="9"/>
-      <c r="D166" s="9"/>
-      <c r="E166" s="9"/>
-      <c r="F166" s="9"/>
-      <c r="G166" s="9"/>
-      <c r="H166" s="9"/>
+      <c r="A166" s="11"/>
+      <c r="B166" s="12"/>
+      <c r="C166" s="12"/>
+      <c r="D166" s="12"/>
+      <c r="E166" s="12"/>
+      <c r="F166" s="12"/>
+      <c r="G166" s="12"/>
+      <c r="H166" s="12"/>
       <c r="I166" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6275,14 +6302,14 @@
       <c r="N166" s="16"/>
     </row>
     <row r="167" spans="1:14">
-      <c r="A167" s="8"/>
-      <c r="B167" s="9"/>
-      <c r="C167" s="9"/>
-      <c r="D167" s="9"/>
-      <c r="E167" s="9"/>
-      <c r="F167" s="9"/>
-      <c r="G167" s="9"/>
-      <c r="H167" s="9"/>
+      <c r="A167" s="11"/>
+      <c r="B167" s="12"/>
+      <c r="C167" s="12"/>
+      <c r="D167" s="12"/>
+      <c r="E167" s="12"/>
+      <c r="F167" s="12"/>
+      <c r="G167" s="12"/>
+      <c r="H167" s="12"/>
       <c r="I167" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6297,14 +6324,14 @@
       <c r="N167" s="16"/>
     </row>
     <row r="168" spans="1:14">
-      <c r="A168" s="8"/>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-      <c r="D168" s="9"/>
-      <c r="E168" s="9"/>
-      <c r="F168" s="9"/>
-      <c r="G168" s="9"/>
-      <c r="H168" s="9"/>
+      <c r="A168" s="11"/>
+      <c r="B168" s="12"/>
+      <c r="C168" s="12"/>
+      <c r="D168" s="12"/>
+      <c r="E168" s="12"/>
+      <c r="F168" s="12"/>
+      <c r="G168" s="12"/>
+      <c r="H168" s="12"/>
       <c r="I168" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6319,14 +6346,14 @@
       <c r="N168" s="16"/>
     </row>
     <row r="169" spans="1:14">
-      <c r="A169" s="8"/>
-      <c r="B169" s="9"/>
-      <c r="C169" s="9"/>
-      <c r="D169" s="9"/>
-      <c r="E169" s="9"/>
-      <c r="F169" s="9"/>
-      <c r="G169" s="9"/>
-      <c r="H169" s="9"/>
+      <c r="A169" s="11"/>
+      <c r="B169" s="12"/>
+      <c r="C169" s="12"/>
+      <c r="D169" s="12"/>
+      <c r="E169" s="12"/>
+      <c r="F169" s="12"/>
+      <c r="G169" s="12"/>
+      <c r="H169" s="12"/>
       <c r="I169" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6341,14 +6368,14 @@
       <c r="N169" s="16"/>
     </row>
     <row r="170" spans="1:14">
-      <c r="A170" s="8"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="9"/>
-      <c r="D170" s="9"/>
-      <c r="E170" s="9"/>
-      <c r="F170" s="9"/>
-      <c r="G170" s="9"/>
-      <c r="H170" s="9"/>
+      <c r="A170" s="11"/>
+      <c r="B170" s="12"/>
+      <c r="C170" s="12"/>
+      <c r="D170" s="12"/>
+      <c r="E170" s="12"/>
+      <c r="F170" s="12"/>
+      <c r="G170" s="12"/>
+      <c r="H170" s="12"/>
       <c r="I170" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6363,14 +6390,14 @@
       <c r="N170" s="16"/>
     </row>
     <row r="171" spans="1:14">
-      <c r="A171" s="8"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="9"/>
-      <c r="D171" s="9"/>
-      <c r="E171" s="9"/>
-      <c r="F171" s="9"/>
-      <c r="G171" s="9"/>
-      <c r="H171" s="9"/>
+      <c r="A171" s="11"/>
+      <c r="B171" s="12"/>
+      <c r="C171" s="12"/>
+      <c r="D171" s="12"/>
+      <c r="E171" s="12"/>
+      <c r="F171" s="12"/>
+      <c r="G171" s="12"/>
+      <c r="H171" s="12"/>
       <c r="I171" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6385,14 +6412,14 @@
       <c r="N171" s="16"/>
     </row>
     <row r="172" spans="1:14">
-      <c r="A172" s="8"/>
-      <c r="B172" s="9"/>
-      <c r="C172" s="9"/>
-      <c r="D172" s="9"/>
-      <c r="E172" s="9"/>
-      <c r="F172" s="9"/>
-      <c r="G172" s="9"/>
-      <c r="H172" s="9"/>
+      <c r="A172" s="11"/>
+      <c r="B172" s="12"/>
+      <c r="C172" s="12"/>
+      <c r="D172" s="12"/>
+      <c r="E172" s="12"/>
+      <c r="F172" s="12"/>
+      <c r="G172" s="12"/>
+      <c r="H172" s="12"/>
       <c r="I172" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6407,14 +6434,14 @@
       <c r="N172" s="16"/>
     </row>
     <row r="173" spans="1:14">
-      <c r="A173" s="8"/>
-      <c r="B173" s="9"/>
-      <c r="C173" s="9"/>
-      <c r="D173" s="9"/>
-      <c r="E173" s="9"/>
-      <c r="F173" s="9"/>
-      <c r="G173" s="9"/>
-      <c r="H173" s="9"/>
+      <c r="A173" s="11"/>
+      <c r="B173" s="12"/>
+      <c r="C173" s="12"/>
+      <c r="D173" s="12"/>
+      <c r="E173" s="12"/>
+      <c r="F173" s="12"/>
+      <c r="G173" s="12"/>
+      <c r="H173" s="12"/>
       <c r="I173" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6429,14 +6456,14 @@
       <c r="N173" s="16"/>
     </row>
     <row r="174" spans="1:14">
-      <c r="A174" s="8"/>
-      <c r="B174" s="9"/>
-      <c r="C174" s="9"/>
-      <c r="D174" s="9"/>
-      <c r="E174" s="9"/>
-      <c r="F174" s="9"/>
-      <c r="G174" s="9"/>
-      <c r="H174" s="9"/>
+      <c r="A174" s="11"/>
+      <c r="B174" s="12"/>
+      <c r="C174" s="12"/>
+      <c r="D174" s="12"/>
+      <c r="E174" s="12"/>
+      <c r="F174" s="12"/>
+      <c r="G174" s="12"/>
+      <c r="H174" s="12"/>
       <c r="I174" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6451,14 +6478,14 @@
       <c r="N174" s="16"/>
     </row>
     <row r="175" spans="1:14">
-      <c r="A175" s="8"/>
-      <c r="B175" s="9"/>
-      <c r="C175" s="9"/>
-      <c r="D175" s="9"/>
-      <c r="E175" s="9"/>
-      <c r="F175" s="9"/>
-      <c r="G175" s="9"/>
-      <c r="H175" s="9"/>
+      <c r="A175" s="11"/>
+      <c r="B175" s="12"/>
+      <c r="C175" s="12"/>
+      <c r="D175" s="12"/>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12"/>
+      <c r="G175" s="12"/>
+      <c r="H175" s="12"/>
       <c r="I175" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6473,14 +6500,14 @@
       <c r="N175" s="16"/>
     </row>
     <row r="176" spans="1:14">
-      <c r="A176" s="8"/>
-      <c r="B176" s="9"/>
-      <c r="C176" s="9"/>
-      <c r="D176" s="9"/>
-      <c r="E176" s="9"/>
-      <c r="F176" s="9"/>
-      <c r="G176" s="9"/>
-      <c r="H176" s="9"/>
+      <c r="A176" s="11"/>
+      <c r="B176" s="12"/>
+      <c r="C176" s="12"/>
+      <c r="D176" s="12"/>
+      <c r="E176" s="12"/>
+      <c r="F176" s="12"/>
+      <c r="G176" s="12"/>
+      <c r="H176" s="12"/>
       <c r="I176" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6495,14 +6522,14 @@
       <c r="N176" s="16"/>
     </row>
     <row r="177" spans="1:14">
-      <c r="A177" s="8"/>
-      <c r="B177" s="9"/>
-      <c r="C177" s="9"/>
-      <c r="D177" s="9"/>
-      <c r="E177" s="9"/>
-      <c r="F177" s="9"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="9"/>
+      <c r="A177" s="11"/>
+      <c r="B177" s="12"/>
+      <c r="C177" s="12"/>
+      <c r="D177" s="12"/>
+      <c r="E177" s="12"/>
+      <c r="F177" s="12"/>
+      <c r="G177" s="12"/>
+      <c r="H177" s="12"/>
       <c r="I177" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6517,14 +6544,14 @@
       <c r="N177" s="16"/>
     </row>
     <row r="178" spans="1:14">
-      <c r="A178" s="8"/>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="9"/>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
+      <c r="A178" s="11"/>
+      <c r="B178" s="12"/>
+      <c r="C178" s="12"/>
+      <c r="D178" s="12"/>
+      <c r="E178" s="12"/>
+      <c r="F178" s="12"/>
+      <c r="G178" s="12"/>
+      <c r="H178" s="12"/>
       <c r="I178" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6539,14 +6566,14 @@
       <c r="N178" s="16"/>
     </row>
     <row r="179" spans="1:14">
-      <c r="A179" s="8"/>
-      <c r="B179" s="9"/>
-      <c r="C179" s="9"/>
-      <c r="D179" s="9"/>
-      <c r="E179" s="9"/>
-      <c r="F179" s="9"/>
-      <c r="G179" s="9"/>
-      <c r="H179" s="9"/>
+      <c r="A179" s="11"/>
+      <c r="B179" s="12"/>
+      <c r="C179" s="12"/>
+      <c r="D179" s="12"/>
+      <c r="E179" s="12"/>
+      <c r="F179" s="12"/>
+      <c r="G179" s="12"/>
+      <c r="H179" s="12"/>
       <c r="I179" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6561,14 +6588,14 @@
       <c r="N179" s="16"/>
     </row>
     <row r="180" spans="1:14">
-      <c r="A180" s="8"/>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
-      <c r="D180" s="9"/>
-      <c r="E180" s="9"/>
-      <c r="F180" s="9"/>
-      <c r="G180" s="9"/>
-      <c r="H180" s="9"/>
+      <c r="A180" s="11"/>
+      <c r="B180" s="12"/>
+      <c r="C180" s="12"/>
+      <c r="D180" s="12"/>
+      <c r="E180" s="12"/>
+      <c r="F180" s="12"/>
+      <c r="G180" s="12"/>
+      <c r="H180" s="12"/>
       <c r="I180" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6583,14 +6610,14 @@
       <c r="N180" s="16"/>
     </row>
     <row r="181" spans="1:14">
-      <c r="A181" s="8"/>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-      <c r="D181" s="9"/>
-      <c r="E181" s="9"/>
-      <c r="F181" s="9"/>
-      <c r="G181" s="9"/>
-      <c r="H181" s="9"/>
+      <c r="A181" s="11"/>
+      <c r="B181" s="12"/>
+      <c r="C181" s="12"/>
+      <c r="D181" s="12"/>
+      <c r="E181" s="12"/>
+      <c r="F181" s="12"/>
+      <c r="G181" s="12"/>
+      <c r="H181" s="12"/>
       <c r="I181" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6605,14 +6632,14 @@
       <c r="N181" s="16"/>
     </row>
     <row r="182" spans="1:14">
-      <c r="A182" s="8"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="9"/>
-      <c r="E182" s="9"/>
-      <c r="F182" s="9"/>
-      <c r="G182" s="9"/>
-      <c r="H182" s="9"/>
+      <c r="A182" s="11"/>
+      <c r="B182" s="12"/>
+      <c r="C182" s="12"/>
+      <c r="D182" s="12"/>
+      <c r="E182" s="12"/>
+      <c r="F182" s="12"/>
+      <c r="G182" s="12"/>
+      <c r="H182" s="12"/>
       <c r="I182" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6627,14 +6654,14 @@
       <c r="N182" s="16"/>
     </row>
     <row r="183" spans="1:14">
-      <c r="A183" s="8"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="9"/>
-      <c r="E183" s="9"/>
-      <c r="F183" s="9"/>
-      <c r="G183" s="9"/>
-      <c r="H183" s="9"/>
+      <c r="A183" s="11"/>
+      <c r="B183" s="12"/>
+      <c r="C183" s="12"/>
+      <c r="D183" s="12"/>
+      <c r="E183" s="12"/>
+      <c r="F183" s="12"/>
+      <c r="G183" s="12"/>
+      <c r="H183" s="12"/>
       <c r="I183" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6649,14 +6676,14 @@
       <c r="N183" s="16"/>
     </row>
     <row r="184" spans="1:14">
-      <c r="A184" s="8"/>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
-      <c r="D184" s="9"/>
-      <c r="E184" s="9"/>
-      <c r="F184" s="9"/>
-      <c r="G184" s="9"/>
-      <c r="H184" s="9"/>
+      <c r="A184" s="11"/>
+      <c r="B184" s="12"/>
+      <c r="C184" s="12"/>
+      <c r="D184" s="12"/>
+      <c r="E184" s="12"/>
+      <c r="F184" s="12"/>
+      <c r="G184" s="12"/>
+      <c r="H184" s="12"/>
       <c r="I184" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6671,14 +6698,14 @@
       <c r="N184" s="16"/>
     </row>
     <row r="185" spans="1:14">
-      <c r="A185" s="8"/>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
-      <c r="E185" s="9"/>
-      <c r="F185" s="9"/>
-      <c r="G185" s="9"/>
-      <c r="H185" s="9"/>
+      <c r="A185" s="11"/>
+      <c r="B185" s="12"/>
+      <c r="C185" s="12"/>
+      <c r="D185" s="12"/>
+      <c r="E185" s="12"/>
+      <c r="F185" s="12"/>
+      <c r="G185" s="12"/>
+      <c r="H185" s="12"/>
       <c r="I185" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6693,14 +6720,14 @@
       <c r="N185" s="16"/>
     </row>
     <row r="186" spans="1:14">
-      <c r="A186" s="8"/>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="9"/>
-      <c r="G186" s="9"/>
-      <c r="H186" s="9"/>
+      <c r="A186" s="11"/>
+      <c r="B186" s="12"/>
+      <c r="C186" s="12"/>
+      <c r="D186" s="12"/>
+      <c r="E186" s="12"/>
+      <c r="F186" s="12"/>
+      <c r="G186" s="12"/>
+      <c r="H186" s="12"/>
       <c r="I186" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6715,14 +6742,14 @@
       <c r="N186" s="16"/>
     </row>
     <row r="187" spans="1:14">
-      <c r="A187" s="8"/>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
-      <c r="E187" s="9"/>
-      <c r="F187" s="9"/>
-      <c r="G187" s="9"/>
-      <c r="H187" s="9"/>
+      <c r="A187" s="11"/>
+      <c r="B187" s="12"/>
+      <c r="C187" s="12"/>
+      <c r="D187" s="12"/>
+      <c r="E187" s="12"/>
+      <c r="F187" s="12"/>
+      <c r="G187" s="12"/>
+      <c r="H187" s="12"/>
       <c r="I187" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6737,14 +6764,14 @@
       <c r="N187" s="16"/>
     </row>
     <row r="188" spans="1:14">
-      <c r="A188" s="8"/>
-      <c r="B188" s="9"/>
-      <c r="C188" s="9"/>
-      <c r="D188" s="9"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="9"/>
-      <c r="G188" s="9"/>
-      <c r="H188" s="9"/>
+      <c r="A188" s="11"/>
+      <c r="B188" s="12"/>
+      <c r="C188" s="12"/>
+      <c r="D188" s="12"/>
+      <c r="E188" s="12"/>
+      <c r="F188" s="12"/>
+      <c r="G188" s="12"/>
+      <c r="H188" s="12"/>
       <c r="I188" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6759,14 +6786,14 @@
       <c r="N188" s="16"/>
     </row>
     <row r="189" spans="1:14">
-      <c r="A189" s="8"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
-      <c r="D189" s="9"/>
-      <c r="E189" s="9"/>
-      <c r="F189" s="9"/>
-      <c r="G189" s="9"/>
-      <c r="H189" s="9"/>
+      <c r="A189" s="11"/>
+      <c r="B189" s="12"/>
+      <c r="C189" s="12"/>
+      <c r="D189" s="12"/>
+      <c r="E189" s="12"/>
+      <c r="F189" s="12"/>
+      <c r="G189" s="12"/>
+      <c r="H189" s="12"/>
       <c r="I189" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6781,14 +6808,14 @@
       <c r="N189" s="16"/>
     </row>
     <row r="190" spans="1:14">
-      <c r="A190" s="8"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="9"/>
-      <c r="G190" s="9"/>
-      <c r="H190" s="9"/>
+      <c r="A190" s="11"/>
+      <c r="B190" s="12"/>
+      <c r="C190" s="12"/>
+      <c r="D190" s="12"/>
+      <c r="E190" s="12"/>
+      <c r="F190" s="12"/>
+      <c r="G190" s="12"/>
+      <c r="H190" s="12"/>
       <c r="I190" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6803,14 +6830,14 @@
       <c r="N190" s="16"/>
     </row>
     <row r="191" spans="1:14">
-      <c r="A191" s="8"/>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
-      <c r="D191" s="9"/>
-      <c r="E191" s="9"/>
-      <c r="F191" s="9"/>
-      <c r="G191" s="9"/>
-      <c r="H191" s="9"/>
+      <c r="A191" s="11"/>
+      <c r="B191" s="12"/>
+      <c r="C191" s="12"/>
+      <c r="D191" s="12"/>
+      <c r="E191" s="12"/>
+      <c r="F191" s="12"/>
+      <c r="G191" s="12"/>
+      <c r="H191" s="12"/>
       <c r="I191" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6825,14 +6852,14 @@
       <c r="N191" s="16"/>
     </row>
     <row r="192" spans="1:14">
-      <c r="A192" s="8"/>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
-      <c r="D192" s="9"/>
-      <c r="E192" s="9"/>
-      <c r="F192" s="9"/>
-      <c r="G192" s="9"/>
-      <c r="H192" s="9"/>
+      <c r="A192" s="11"/>
+      <c r="B192" s="12"/>
+      <c r="C192" s="12"/>
+      <c r="D192" s="12"/>
+      <c r="E192" s="12"/>
+      <c r="F192" s="12"/>
+      <c r="G192" s="12"/>
+      <c r="H192" s="12"/>
       <c r="I192" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6847,14 +6874,14 @@
       <c r="N192" s="16"/>
     </row>
     <row r="193" spans="1:14">
-      <c r="A193" s="8"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
-      <c r="D193" s="9"/>
-      <c r="E193" s="9"/>
-      <c r="F193" s="9"/>
-      <c r="G193" s="9"/>
-      <c r="H193" s="9"/>
+      <c r="A193" s="11"/>
+      <c r="B193" s="12"/>
+      <c r="C193" s="12"/>
+      <c r="D193" s="12"/>
+      <c r="E193" s="12"/>
+      <c r="F193" s="12"/>
+      <c r="G193" s="12"/>
+      <c r="H193" s="12"/>
       <c r="I193" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6869,14 +6896,14 @@
       <c r="N193" s="16"/>
     </row>
     <row r="194" spans="1:14">
-      <c r="A194" s="8"/>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
-      <c r="D194" s="9"/>
-      <c r="E194" s="9"/>
-      <c r="F194" s="9"/>
-      <c r="G194" s="9"/>
-      <c r="H194" s="9"/>
+      <c r="A194" s="11"/>
+      <c r="B194" s="12"/>
+      <c r="C194" s="12"/>
+      <c r="D194" s="12"/>
+      <c r="E194" s="12"/>
+      <c r="F194" s="12"/>
+      <c r="G194" s="12"/>
+      <c r="H194" s="12"/>
       <c r="I194" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6891,14 +6918,14 @@
       <c r="N194" s="16"/>
     </row>
     <row r="195" spans="1:14">
-      <c r="A195" s="8"/>
-      <c r="B195" s="9"/>
-      <c r="C195" s="9"/>
-      <c r="D195" s="9"/>
-      <c r="E195" s="9"/>
-      <c r="F195" s="9"/>
-      <c r="G195" s="9"/>
-      <c r="H195" s="9"/>
+      <c r="A195" s="11"/>
+      <c r="B195" s="12"/>
+      <c r="C195" s="12"/>
+      <c r="D195" s="12"/>
+      <c r="E195" s="12"/>
+      <c r="F195" s="12"/>
+      <c r="G195" s="12"/>
+      <c r="H195" s="12"/>
       <c r="I195" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6913,14 +6940,14 @@
       <c r="N195" s="16"/>
     </row>
     <row r="196" spans="1:14">
-      <c r="A196" s="8"/>
-      <c r="B196" s="9"/>
-      <c r="C196" s="9"/>
-      <c r="D196" s="9"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="9"/>
-      <c r="G196" s="9"/>
-      <c r="H196" s="9"/>
+      <c r="A196" s="11"/>
+      <c r="B196" s="12"/>
+      <c r="C196" s="12"/>
+      <c r="D196" s="12"/>
+      <c r="E196" s="12"/>
+      <c r="F196" s="12"/>
+      <c r="G196" s="12"/>
+      <c r="H196" s="12"/>
       <c r="I196" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6935,14 +6962,14 @@
       <c r="N196" s="16"/>
     </row>
     <row r="197" spans="1:14">
-      <c r="A197" s="8"/>
-      <c r="B197" s="9"/>
-      <c r="C197" s="9"/>
-      <c r="D197" s="9"/>
-      <c r="E197" s="9"/>
-      <c r="F197" s="9"/>
-      <c r="G197" s="9"/>
-      <c r="H197" s="9"/>
+      <c r="A197" s="11"/>
+      <c r="B197" s="12"/>
+      <c r="C197" s="12"/>
+      <c r="D197" s="12"/>
+      <c r="E197" s="12"/>
+      <c r="F197" s="12"/>
+      <c r="G197" s="12"/>
+      <c r="H197" s="12"/>
       <c r="I197" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -6957,14 +6984,14 @@
       <c r="N197" s="16"/>
     </row>
     <row r="198" spans="1:14">
-      <c r="A198" s="8"/>
-      <c r="B198" s="9"/>
-      <c r="C198" s="9"/>
-      <c r="D198" s="9"/>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="9"/>
-      <c r="H198" s="9"/>
+      <c r="A198" s="11"/>
+      <c r="B198" s="12"/>
+      <c r="C198" s="12"/>
+      <c r="D198" s="12"/>
+      <c r="E198" s="12"/>
+      <c r="F198" s="12"/>
+      <c r="G198" s="12"/>
+      <c r="H198" s="12"/>
       <c r="I198" s="13" t="str">
         <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
@@ -6979,14 +7006,14 @@
       <c r="N198" s="16"/>
     </row>
     <row r="199" spans="1:14">
-      <c r="A199" s="8"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
-      <c r="G199" s="9"/>
-      <c r="H199" s="9"/>
+      <c r="A199" s="11"/>
+      <c r="B199" s="12"/>
+      <c r="C199" s="12"/>
+      <c r="D199" s="12"/>
+      <c r="E199" s="12"/>
+      <c r="F199" s="12"/>
+      <c r="G199" s="12"/>
+      <c r="H199" s="12"/>
       <c r="I199" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7001,14 +7028,14 @@
       <c r="N199" s="16"/>
     </row>
     <row r="200" spans="1:14">
-      <c r="A200" s="8"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="9"/>
-      <c r="D200" s="9"/>
-      <c r="E200" s="9"/>
-      <c r="F200" s="9"/>
-      <c r="G200" s="9"/>
-      <c r="H200" s="9"/>
+      <c r="A200" s="11"/>
+      <c r="B200" s="12"/>
+      <c r="C200" s="12"/>
+      <c r="D200" s="12"/>
+      <c r="E200" s="12"/>
+      <c r="F200" s="12"/>
+      <c r="G200" s="12"/>
+      <c r="H200" s="12"/>
       <c r="I200" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7023,14 +7050,14 @@
       <c r="N200" s="16"/>
     </row>
     <row r="201" spans="1:14">
-      <c r="A201" s="8"/>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9"/>
-      <c r="D201" s="9"/>
-      <c r="E201" s="9"/>
-      <c r="F201" s="9"/>
-      <c r="G201" s="9"/>
-      <c r="H201" s="9"/>
+      <c r="A201" s="11"/>
+      <c r="B201" s="12"/>
+      <c r="C201" s="12"/>
+      <c r="D201" s="12"/>
+      <c r="E201" s="12"/>
+      <c r="F201" s="12"/>
+      <c r="G201" s="12"/>
+      <c r="H201" s="12"/>
       <c r="I201" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7045,14 +7072,14 @@
       <c r="N201" s="16"/>
     </row>
     <row r="202" spans="1:14">
-      <c r="A202" s="8"/>
-      <c r="B202" s="9"/>
-      <c r="C202" s="9"/>
-      <c r="D202" s="9"/>
-      <c r="E202" s="9"/>
-      <c r="F202" s="9"/>
-      <c r="G202" s="9"/>
-      <c r="H202" s="9"/>
+      <c r="A202" s="11"/>
+      <c r="B202" s="12"/>
+      <c r="C202" s="12"/>
+      <c r="D202" s="12"/>
+      <c r="E202" s="12"/>
+      <c r="F202" s="12"/>
+      <c r="G202" s="12"/>
+      <c r="H202" s="12"/>
       <c r="I202" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7067,14 +7094,14 @@
       <c r="N202" s="16"/>
     </row>
     <row r="203" spans="1:14">
-      <c r="A203" s="8"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="9"/>
-      <c r="D203" s="9"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="9"/>
-      <c r="G203" s="9"/>
-      <c r="H203" s="9"/>
+      <c r="A203" s="11"/>
+      <c r="B203" s="12"/>
+      <c r="C203" s="12"/>
+      <c r="D203" s="12"/>
+      <c r="E203" s="12"/>
+      <c r="F203" s="12"/>
+      <c r="G203" s="12"/>
+      <c r="H203" s="12"/>
       <c r="I203" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7089,14 +7116,14 @@
       <c r="N203" s="16"/>
     </row>
     <row r="204" spans="1:14">
-      <c r="A204" s="8"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="9"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9"/>
-      <c r="G204" s="9"/>
-      <c r="H204" s="9"/>
+      <c r="A204" s="11"/>
+      <c r="B204" s="12"/>
+      <c r="C204" s="12"/>
+      <c r="D204" s="12"/>
+      <c r="E204" s="12"/>
+      <c r="F204" s="12"/>
+      <c r="G204" s="12"/>
+      <c r="H204" s="12"/>
       <c r="I204" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7111,14 +7138,14 @@
       <c r="N204" s="16"/>
     </row>
     <row r="205" spans="1:14">
-      <c r="A205" s="8"/>
-      <c r="B205" s="9"/>
-      <c r="C205" s="9"/>
-      <c r="D205" s="9"/>
-      <c r="E205" s="9"/>
-      <c r="F205" s="9"/>
-      <c r="G205" s="9"/>
-      <c r="H205" s="9"/>
+      <c r="A205" s="11"/>
+      <c r="B205" s="12"/>
+      <c r="C205" s="12"/>
+      <c r="D205" s="12"/>
+      <c r="E205" s="12"/>
+      <c r="F205" s="12"/>
+      <c r="G205" s="12"/>
+      <c r="H205" s="12"/>
       <c r="I205" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7133,14 +7160,14 @@
       <c r="N205" s="16"/>
     </row>
     <row r="206" spans="1:14">
-      <c r="A206" s="8"/>
-      <c r="B206" s="9"/>
-      <c r="C206" s="9"/>
-      <c r="D206" s="9"/>
-      <c r="E206" s="9"/>
-      <c r="F206" s="9"/>
-      <c r="G206" s="9"/>
-      <c r="H206" s="9"/>
+      <c r="A206" s="11"/>
+      <c r="B206" s="12"/>
+      <c r="C206" s="12"/>
+      <c r="D206" s="12"/>
+      <c r="E206" s="12"/>
+      <c r="F206" s="12"/>
+      <c r="G206" s="12"/>
+      <c r="H206" s="12"/>
       <c r="I206" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7155,14 +7182,14 @@
       <c r="N206" s="16"/>
     </row>
     <row r="207" spans="1:14">
-      <c r="A207" s="8"/>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
-      <c r="D207" s="9"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="9"/>
-      <c r="G207" s="9"/>
-      <c r="H207" s="9"/>
+      <c r="A207" s="11"/>
+      <c r="B207" s="12"/>
+      <c r="C207" s="12"/>
+      <c r="D207" s="12"/>
+      <c r="E207" s="12"/>
+      <c r="F207" s="12"/>
+      <c r="G207" s="12"/>
+      <c r="H207" s="12"/>
       <c r="I207" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7177,14 +7204,14 @@
       <c r="N207" s="16"/>
     </row>
     <row r="208" spans="1:14">
-      <c r="A208" s="8"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="9"/>
-      <c r="D208" s="9"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="9"/>
-      <c r="G208" s="9"/>
-      <c r="H208" s="9"/>
+      <c r="A208" s="11"/>
+      <c r="B208" s="12"/>
+      <c r="C208" s="12"/>
+      <c r="D208" s="12"/>
+      <c r="E208" s="12"/>
+      <c r="F208" s="12"/>
+      <c r="G208" s="12"/>
+      <c r="H208" s="12"/>
       <c r="I208" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7199,14 +7226,14 @@
       <c r="N208" s="16"/>
     </row>
     <row r="209" spans="1:14">
-      <c r="A209" s="8"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
-      <c r="D209" s="9"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="9"/>
-      <c r="G209" s="9"/>
-      <c r="H209" s="9"/>
+      <c r="A209" s="11"/>
+      <c r="B209" s="12"/>
+      <c r="C209" s="12"/>
+      <c r="D209" s="12"/>
+      <c r="E209" s="12"/>
+      <c r="F209" s="12"/>
+      <c r="G209" s="12"/>
+      <c r="H209" s="12"/>
       <c r="I209" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7221,14 +7248,14 @@
       <c r="N209" s="16"/>
     </row>
     <row r="210" spans="1:14">
-      <c r="A210" s="8"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="9"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="9"/>
-      <c r="G210" s="9"/>
-      <c r="H210" s="9"/>
+      <c r="A210" s="11"/>
+      <c r="B210" s="12"/>
+      <c r="C210" s="12"/>
+      <c r="D210" s="12"/>
+      <c r="E210" s="12"/>
+      <c r="F210" s="12"/>
+      <c r="G210" s="12"/>
+      <c r="H210" s="12"/>
       <c r="I210" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7243,14 +7270,14 @@
       <c r="N210" s="16"/>
     </row>
     <row r="211" spans="1:14">
-      <c r="A211" s="8"/>
-      <c r="B211" s="9"/>
-      <c r="C211" s="9"/>
-      <c r="D211" s="9"/>
-      <c r="E211" s="9"/>
-      <c r="F211" s="9"/>
-      <c r="G211" s="9"/>
-      <c r="H211" s="9"/>
+      <c r="A211" s="11"/>
+      <c r="B211" s="12"/>
+      <c r="C211" s="12"/>
+      <c r="D211" s="12"/>
+      <c r="E211" s="12"/>
+      <c r="F211" s="12"/>
+      <c r="G211" s="12"/>
+      <c r="H211" s="12"/>
       <c r="I211" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7265,14 +7292,14 @@
       <c r="N211" s="16"/>
     </row>
     <row r="212" spans="1:14">
-      <c r="A212" s="8"/>
-      <c r="B212" s="9"/>
-      <c r="C212" s="9"/>
-      <c r="D212" s="9"/>
-      <c r="E212" s="9"/>
-      <c r="F212" s="9"/>
-      <c r="G212" s="9"/>
-      <c r="H212" s="9"/>
+      <c r="A212" s="11"/>
+      <c r="B212" s="12"/>
+      <c r="C212" s="12"/>
+      <c r="D212" s="12"/>
+      <c r="E212" s="12"/>
+      <c r="F212" s="12"/>
+      <c r="G212" s="12"/>
+      <c r="H212" s="12"/>
       <c r="I212" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7287,14 +7314,14 @@
       <c r="N212" s="16"/>
     </row>
     <row r="213" spans="1:14">
-      <c r="A213" s="8"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="9"/>
-      <c r="D213" s="9"/>
-      <c r="E213" s="9"/>
-      <c r="F213" s="9"/>
-      <c r="G213" s="9"/>
-      <c r="H213" s="9"/>
+      <c r="A213" s="11"/>
+      <c r="B213" s="12"/>
+      <c r="C213" s="12"/>
+      <c r="D213" s="12"/>
+      <c r="E213" s="12"/>
+      <c r="F213" s="12"/>
+      <c r="G213" s="12"/>
+      <c r="H213" s="12"/>
       <c r="I213" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7309,14 +7336,14 @@
       <c r="N213" s="16"/>
     </row>
     <row r="214" spans="1:14">
-      <c r="A214" s="8"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="9"/>
-      <c r="D214" s="9"/>
-      <c r="E214" s="9"/>
-      <c r="F214" s="9"/>
-      <c r="G214" s="9"/>
-      <c r="H214" s="9"/>
+      <c r="A214" s="11"/>
+      <c r="B214" s="12"/>
+      <c r="C214" s="12"/>
+      <c r="D214" s="12"/>
+      <c r="E214" s="12"/>
+      <c r="F214" s="12"/>
+      <c r="G214" s="12"/>
+      <c r="H214" s="12"/>
       <c r="I214" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7331,14 +7358,14 @@
       <c r="N214" s="16"/>
     </row>
     <row r="215" spans="1:14">
-      <c r="A215" s="8"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
-      <c r="D215" s="9"/>
-      <c r="E215" s="9"/>
-      <c r="F215" s="9"/>
-      <c r="G215" s="9"/>
-      <c r="H215" s="9"/>
+      <c r="A215" s="11"/>
+      <c r="B215" s="12"/>
+      <c r="C215" s="12"/>
+      <c r="D215" s="12"/>
+      <c r="E215" s="12"/>
+      <c r="F215" s="12"/>
+      <c r="G215" s="12"/>
+      <c r="H215" s="12"/>
       <c r="I215" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7353,14 +7380,14 @@
       <c r="N215" s="16"/>
     </row>
     <row r="216" spans="1:14">
-      <c r="A216" s="8"/>
-      <c r="B216" s="9"/>
-      <c r="C216" s="9"/>
-      <c r="D216" s="9"/>
-      <c r="E216" s="9"/>
-      <c r="F216" s="9"/>
-      <c r="G216" s="9"/>
-      <c r="H216" s="9"/>
+      <c r="A216" s="11"/>
+      <c r="B216" s="12"/>
+      <c r="C216" s="12"/>
+      <c r="D216" s="12"/>
+      <c r="E216" s="12"/>
+      <c r="F216" s="12"/>
+      <c r="G216" s="12"/>
+      <c r="H216" s="12"/>
       <c r="I216" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7375,14 +7402,14 @@
       <c r="N216" s="16"/>
     </row>
     <row r="217" spans="1:14">
-      <c r="A217" s="8"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="9"/>
-      <c r="G217" s="9"/>
-      <c r="H217" s="9"/>
+      <c r="A217" s="11"/>
+      <c r="B217" s="12"/>
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
       <c r="I217" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7397,14 +7424,14 @@
       <c r="N217" s="16"/>
     </row>
     <row r="218" spans="1:14">
-      <c r="A218" s="8"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="9"/>
-      <c r="G218" s="9"/>
-      <c r="H218" s="9"/>
+      <c r="A218" s="11"/>
+      <c r="B218" s="12"/>
+      <c r="C218" s="12"/>
+      <c r="D218" s="12"/>
+      <c r="E218" s="12"/>
+      <c r="F218" s="12"/>
+      <c r="G218" s="12"/>
+      <c r="H218" s="12"/>
       <c r="I218" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7419,14 +7446,14 @@
       <c r="N218" s="16"/>
     </row>
     <row r="219" spans="1:14">
-      <c r="A219" s="8"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
-      <c r="E219" s="9"/>
-      <c r="F219" s="9"/>
-      <c r="G219" s="9"/>
-      <c r="H219" s="9"/>
+      <c r="A219" s="11"/>
+      <c r="B219" s="12"/>
+      <c r="C219" s="12"/>
+      <c r="D219" s="12"/>
+      <c r="E219" s="12"/>
+      <c r="F219" s="12"/>
+      <c r="G219" s="12"/>
+      <c r="H219" s="12"/>
       <c r="I219" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7441,14 +7468,14 @@
       <c r="N219" s="16"/>
     </row>
     <row r="220" spans="1:14">
-      <c r="A220" s="8"/>
-      <c r="B220" s="9"/>
-      <c r="C220" s="9"/>
-      <c r="D220" s="9"/>
-      <c r="E220" s="9"/>
-      <c r="F220" s="9"/>
-      <c r="G220" s="9"/>
-      <c r="H220" s="9"/>
+      <c r="A220" s="11"/>
+      <c r="B220" s="12"/>
+      <c r="C220" s="12"/>
+      <c r="D220" s="12"/>
+      <c r="E220" s="12"/>
+      <c r="F220" s="12"/>
+      <c r="G220" s="12"/>
+      <c r="H220" s="12"/>
       <c r="I220" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7463,14 +7490,14 @@
       <c r="N220" s="16"/>
     </row>
     <row r="221" spans="1:14">
-      <c r="A221" s="8"/>
-      <c r="B221" s="9"/>
-      <c r="C221" s="9"/>
-      <c r="D221" s="9"/>
-      <c r="E221" s="9"/>
-      <c r="F221" s="9"/>
-      <c r="G221" s="9"/>
-      <c r="H221" s="9"/>
+      <c r="A221" s="11"/>
+      <c r="B221" s="12"/>
+      <c r="C221" s="12"/>
+      <c r="D221" s="12"/>
+      <c r="E221" s="12"/>
+      <c r="F221" s="12"/>
+      <c r="G221" s="12"/>
+      <c r="H221" s="12"/>
       <c r="I221" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7485,14 +7512,14 @@
       <c r="N221" s="16"/>
     </row>
     <row r="222" spans="1:14">
-      <c r="A222" s="8"/>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="9"/>
-      <c r="G222" s="9"/>
-      <c r="H222" s="9"/>
+      <c r="A222" s="11"/>
+      <c r="B222" s="12"/>
+      <c r="C222" s="12"/>
+      <c r="D222" s="12"/>
+      <c r="E222" s="12"/>
+      <c r="F222" s="12"/>
+      <c r="G222" s="12"/>
+      <c r="H222" s="12"/>
       <c r="I222" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7507,14 +7534,14 @@
       <c r="N222" s="16"/>
     </row>
     <row r="223" spans="1:14">
-      <c r="A223" s="8"/>
-      <c r="B223" s="9"/>
-      <c r="C223" s="9"/>
-      <c r="D223" s="9"/>
-      <c r="E223" s="9"/>
-      <c r="F223" s="9"/>
-      <c r="G223" s="9"/>
-      <c r="H223" s="9"/>
+      <c r="A223" s="11"/>
+      <c r="B223" s="12"/>
+      <c r="C223" s="12"/>
+      <c r="D223" s="12"/>
+      <c r="E223" s="12"/>
+      <c r="F223" s="12"/>
+      <c r="G223" s="12"/>
+      <c r="H223" s="12"/>
       <c r="I223" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7529,14 +7556,14 @@
       <c r="N223" s="16"/>
     </row>
     <row r="224" spans="1:14">
-      <c r="A224" s="8"/>
-      <c r="B224" s="9"/>
-      <c r="C224" s="9"/>
-      <c r="D224" s="9"/>
-      <c r="E224" s="9"/>
-      <c r="F224" s="9"/>
-      <c r="G224" s="9"/>
-      <c r="H224" s="9"/>
+      <c r="A224" s="11"/>
+      <c r="B224" s="12"/>
+      <c r="C224" s="12"/>
+      <c r="D224" s="12"/>
+      <c r="E224" s="12"/>
+      <c r="F224" s="12"/>
+      <c r="G224" s="12"/>
+      <c r="H224" s="12"/>
       <c r="I224" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7551,14 +7578,14 @@
       <c r="N224" s="16"/>
     </row>
     <row r="225" spans="1:14">
-      <c r="A225" s="8"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
-      <c r="D225" s="9"/>
-      <c r="E225" s="9"/>
-      <c r="F225" s="9"/>
-      <c r="G225" s="9"/>
-      <c r="H225" s="9"/>
+      <c r="A225" s="11"/>
+      <c r="B225" s="12"/>
+      <c r="C225" s="12"/>
+      <c r="D225" s="12"/>
+      <c r="E225" s="12"/>
+      <c r="F225" s="12"/>
+      <c r="G225" s="12"/>
+      <c r="H225" s="12"/>
       <c r="I225" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7573,14 +7600,14 @@
       <c r="N225" s="16"/>
     </row>
     <row r="226" spans="1:14">
-      <c r="A226" s="8"/>
-      <c r="B226" s="9"/>
-      <c r="C226" s="9"/>
-      <c r="D226" s="9"/>
-      <c r="E226" s="9"/>
-      <c r="F226" s="9"/>
-      <c r="G226" s="9"/>
-      <c r="H226" s="9"/>
+      <c r="A226" s="11"/>
+      <c r="B226" s="12"/>
+      <c r="C226" s="12"/>
+      <c r="D226" s="12"/>
+      <c r="E226" s="12"/>
+      <c r="F226" s="12"/>
+      <c r="G226" s="12"/>
+      <c r="H226" s="12"/>
       <c r="I226" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7595,14 +7622,14 @@
       <c r="N226" s="16"/>
     </row>
     <row r="227" spans="1:14">
-      <c r="A227" s="8"/>
-      <c r="B227" s="9"/>
-      <c r="C227" s="9"/>
-      <c r="D227" s="9"/>
-      <c r="E227" s="9"/>
-      <c r="F227" s="9"/>
-      <c r="G227" s="9"/>
-      <c r="H227" s="9"/>
+      <c r="A227" s="11"/>
+      <c r="B227" s="12"/>
+      <c r="C227" s="12"/>
+      <c r="D227" s="12"/>
+      <c r="E227" s="12"/>
+      <c r="F227" s="12"/>
+      <c r="G227" s="12"/>
+      <c r="H227" s="12"/>
       <c r="I227" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7617,14 +7644,14 @@
       <c r="N227" s="16"/>
     </row>
     <row r="228" spans="1:14">
-      <c r="A228" s="8"/>
-      <c r="B228" s="9"/>
-      <c r="C228" s="9"/>
-      <c r="D228" s="9"/>
-      <c r="E228" s="9"/>
-      <c r="F228" s="9"/>
-      <c r="G228" s="9"/>
-      <c r="H228" s="9"/>
+      <c r="A228" s="11"/>
+      <c r="B228" s="12"/>
+      <c r="C228" s="12"/>
+      <c r="D228" s="12"/>
+      <c r="E228" s="12"/>
+      <c r="F228" s="12"/>
+      <c r="G228" s="12"/>
+      <c r="H228" s="12"/>
       <c r="I228" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7639,14 +7666,14 @@
       <c r="N228" s="16"/>
     </row>
     <row r="229" spans="1:14">
-      <c r="A229" s="8"/>
-      <c r="B229" s="9"/>
-      <c r="C229" s="9"/>
-      <c r="D229" s="9"/>
-      <c r="E229" s="9"/>
-      <c r="F229" s="9"/>
-      <c r="G229" s="9"/>
-      <c r="H229" s="9"/>
+      <c r="A229" s="11"/>
+      <c r="B229" s="12"/>
+      <c r="C229" s="12"/>
+      <c r="D229" s="12"/>
+      <c r="E229" s="12"/>
+      <c r="F229" s="12"/>
+      <c r="G229" s="12"/>
+      <c r="H229" s="12"/>
       <c r="I229" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7661,14 +7688,14 @@
       <c r="N229" s="16"/>
     </row>
     <row r="230" spans="1:14">
-      <c r="A230" s="8"/>
-      <c r="B230" s="9"/>
-      <c r="C230" s="9"/>
-      <c r="D230" s="9"/>
-      <c r="E230" s="9"/>
-      <c r="F230" s="9"/>
-      <c r="G230" s="9"/>
-      <c r="H230" s="9"/>
+      <c r="A230" s="11"/>
+      <c r="B230" s="12"/>
+      <c r="C230" s="12"/>
+      <c r="D230" s="12"/>
+      <c r="E230" s="12"/>
+      <c r="F230" s="12"/>
+      <c r="G230" s="12"/>
+      <c r="H230" s="12"/>
       <c r="I230" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7683,14 +7710,14 @@
       <c r="N230" s="16"/>
     </row>
     <row r="231" spans="1:14">
-      <c r="A231" s="8"/>
-      <c r="B231" s="9"/>
-      <c r="C231" s="9"/>
-      <c r="D231" s="9"/>
-      <c r="E231" s="9"/>
-      <c r="F231" s="9"/>
-      <c r="G231" s="9"/>
-      <c r="H231" s="9"/>
+      <c r="A231" s="11"/>
+      <c r="B231" s="12"/>
+      <c r="C231" s="12"/>
+      <c r="D231" s="12"/>
+      <c r="E231" s="12"/>
+      <c r="F231" s="12"/>
+      <c r="G231" s="12"/>
+      <c r="H231" s="12"/>
       <c r="I231" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7705,14 +7732,14 @@
       <c r="N231" s="16"/>
     </row>
     <row r="232" spans="1:14">
-      <c r="A232" s="8"/>
-      <c r="B232" s="9"/>
-      <c r="C232" s="9"/>
-      <c r="D232" s="9"/>
-      <c r="E232" s="9"/>
-      <c r="F232" s="9"/>
-      <c r="G232" s="9"/>
-      <c r="H232" s="9"/>
+      <c r="A232" s="11"/>
+      <c r="B232" s="12"/>
+      <c r="C232" s="12"/>
+      <c r="D232" s="12"/>
+      <c r="E232" s="12"/>
+      <c r="F232" s="12"/>
+      <c r="G232" s="12"/>
+      <c r="H232" s="12"/>
       <c r="I232" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7727,14 +7754,14 @@
       <c r="N232" s="16"/>
     </row>
     <row r="233" spans="1:14">
-      <c r="A233" s="8"/>
-      <c r="B233" s="9"/>
-      <c r="C233" s="9"/>
-      <c r="D233" s="9"/>
-      <c r="E233" s="9"/>
-      <c r="F233" s="9"/>
-      <c r="G233" s="9"/>
-      <c r="H233" s="9"/>
+      <c r="A233" s="11"/>
+      <c r="B233" s="12"/>
+      <c r="C233" s="12"/>
+      <c r="D233" s="12"/>
+      <c r="E233" s="12"/>
+      <c r="F233" s="12"/>
+      <c r="G233" s="12"/>
+      <c r="H233" s="12"/>
       <c r="I233" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7749,14 +7776,14 @@
       <c r="N233" s="16"/>
     </row>
     <row r="234" spans="1:14">
-      <c r="A234" s="8"/>
-      <c r="B234" s="9"/>
-      <c r="C234" s="9"/>
-      <c r="D234" s="9"/>
-      <c r="E234" s="9"/>
-      <c r="F234" s="9"/>
-      <c r="G234" s="9"/>
-      <c r="H234" s="9"/>
+      <c r="A234" s="11"/>
+      <c r="B234" s="12"/>
+      <c r="C234" s="12"/>
+      <c r="D234" s="12"/>
+      <c r="E234" s="12"/>
+      <c r="F234" s="12"/>
+      <c r="G234" s="12"/>
+      <c r="H234" s="12"/>
       <c r="I234" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7771,14 +7798,14 @@
       <c r="N234" s="16"/>
     </row>
     <row r="235" spans="1:14">
-      <c r="A235" s="8"/>
-      <c r="B235" s="9"/>
-      <c r="C235" s="9"/>
-      <c r="D235" s="9"/>
-      <c r="E235" s="9"/>
-      <c r="F235" s="9"/>
-      <c r="G235" s="9"/>
-      <c r="H235" s="9"/>
+      <c r="A235" s="11"/>
+      <c r="B235" s="12"/>
+      <c r="C235" s="12"/>
+      <c r="D235" s="12"/>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
+      <c r="G235" s="12"/>
+      <c r="H235" s="12"/>
       <c r="I235" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7793,14 +7820,14 @@
       <c r="N235" s="16"/>
     </row>
     <row r="236" spans="1:14">
-      <c r="A236" s="8"/>
-      <c r="B236" s="9"/>
-      <c r="C236" s="9"/>
-      <c r="D236" s="9"/>
-      <c r="E236" s="9"/>
-      <c r="F236" s="9"/>
-      <c r="G236" s="9"/>
-      <c r="H236" s="9"/>
+      <c r="A236" s="11"/>
+      <c r="B236" s="12"/>
+      <c r="C236" s="12"/>
+      <c r="D236" s="12"/>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12"/>
+      <c r="G236" s="12"/>
+      <c r="H236" s="12"/>
       <c r="I236" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7815,14 +7842,14 @@
       <c r="N236" s="16"/>
     </row>
     <row r="237" spans="1:14">
-      <c r="A237" s="8"/>
-      <c r="B237" s="9"/>
-      <c r="C237" s="9"/>
-      <c r="D237" s="9"/>
-      <c r="E237" s="9"/>
-      <c r="F237" s="9"/>
-      <c r="G237" s="9"/>
-      <c r="H237" s="9"/>
+      <c r="A237" s="11"/>
+      <c r="B237" s="12"/>
+      <c r="C237" s="12"/>
+      <c r="D237" s="12"/>
+      <c r="E237" s="12"/>
+      <c r="F237" s="12"/>
+      <c r="G237" s="12"/>
+      <c r="H237" s="12"/>
       <c r="I237" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7837,14 +7864,14 @@
       <c r="N237" s="16"/>
     </row>
     <row r="238" spans="1:14">
-      <c r="A238" s="8"/>
-      <c r="B238" s="9"/>
-      <c r="C238" s="9"/>
-      <c r="D238" s="9"/>
-      <c r="E238" s="9"/>
-      <c r="F238" s="9"/>
-      <c r="G238" s="9"/>
-      <c r="H238" s="9"/>
+      <c r="A238" s="11"/>
+      <c r="B238" s="12"/>
+      <c r="C238" s="12"/>
+      <c r="D238" s="12"/>
+      <c r="E238" s="12"/>
+      <c r="F238" s="12"/>
+      <c r="G238" s="12"/>
+      <c r="H238" s="12"/>
       <c r="I238" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7859,14 +7886,14 @@
       <c r="N238" s="16"/>
     </row>
     <row r="239" spans="1:14">
-      <c r="A239" s="8"/>
-      <c r="B239" s="9"/>
-      <c r="C239" s="9"/>
-      <c r="D239" s="9"/>
-      <c r="E239" s="9"/>
-      <c r="F239" s="9"/>
-      <c r="G239" s="9"/>
-      <c r="H239" s="9"/>
+      <c r="A239" s="11"/>
+      <c r="B239" s="12"/>
+      <c r="C239" s="12"/>
+      <c r="D239" s="12"/>
+      <c r="E239" s="12"/>
+      <c r="F239" s="12"/>
+      <c r="G239" s="12"/>
+      <c r="H239" s="12"/>
       <c r="I239" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7881,14 +7908,14 @@
       <c r="N239" s="16"/>
     </row>
     <row r="240" spans="1:14">
-      <c r="A240" s="8"/>
-      <c r="B240" s="9"/>
-      <c r="C240" s="9"/>
-      <c r="D240" s="9"/>
-      <c r="E240" s="9"/>
-      <c r="F240" s="9"/>
-      <c r="G240" s="9"/>
-      <c r="H240" s="9"/>
+      <c r="A240" s="11"/>
+      <c r="B240" s="12"/>
+      <c r="C240" s="12"/>
+      <c r="D240" s="12"/>
+      <c r="E240" s="12"/>
+      <c r="F240" s="12"/>
+      <c r="G240" s="12"/>
+      <c r="H240" s="12"/>
       <c r="I240" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7903,14 +7930,14 @@
       <c r="N240" s="16"/>
     </row>
     <row r="241" spans="1:14">
-      <c r="A241" s="8"/>
-      <c r="B241" s="9"/>
-      <c r="C241" s="9"/>
-      <c r="D241" s="9"/>
-      <c r="E241" s="9"/>
-      <c r="F241" s="9"/>
-      <c r="G241" s="9"/>
-      <c r="H241" s="9"/>
+      <c r="A241" s="11"/>
+      <c r="B241" s="12"/>
+      <c r="C241" s="12"/>
+      <c r="D241" s="12"/>
+      <c r="E241" s="12"/>
+      <c r="F241" s="12"/>
+      <c r="G241" s="12"/>
+      <c r="H241" s="12"/>
       <c r="I241" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7925,14 +7952,14 @@
       <c r="N241" s="16"/>
     </row>
     <row r="242" spans="1:14">
-      <c r="A242" s="8"/>
-      <c r="B242" s="9"/>
-      <c r="C242" s="9"/>
-      <c r="D242" s="9"/>
-      <c r="E242" s="9"/>
-      <c r="F242" s="9"/>
-      <c r="G242" s="9"/>
-      <c r="H242" s="9"/>
+      <c r="A242" s="11"/>
+      <c r="B242" s="12"/>
+      <c r="C242" s="12"/>
+      <c r="D242" s="12"/>
+      <c r="E242" s="12"/>
+      <c r="F242" s="12"/>
+      <c r="G242" s="12"/>
+      <c r="H242" s="12"/>
       <c r="I242" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7947,14 +7974,14 @@
       <c r="N242" s="16"/>
     </row>
     <row r="243" spans="1:14">
-      <c r="A243" s="8"/>
-      <c r="B243" s="9"/>
-      <c r="C243" s="9"/>
-      <c r="D243" s="9"/>
-      <c r="E243" s="9"/>
-      <c r="F243" s="9"/>
-      <c r="G243" s="9"/>
-      <c r="H243" s="9"/>
+      <c r="A243" s="11"/>
+      <c r="B243" s="12"/>
+      <c r="C243" s="12"/>
+      <c r="D243" s="12"/>
+      <c r="E243" s="12"/>
+      <c r="F243" s="12"/>
+      <c r="G243" s="12"/>
+      <c r="H243" s="12"/>
       <c r="I243" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7969,14 +7996,14 @@
       <c r="N243" s="16"/>
     </row>
     <row r="244" spans="1:14">
-      <c r="A244" s="8"/>
-      <c r="B244" s="9"/>
-      <c r="C244" s="9"/>
-      <c r="D244" s="9"/>
-      <c r="E244" s="9"/>
-      <c r="F244" s="9"/>
-      <c r="G244" s="9"/>
-      <c r="H244" s="9"/>
+      <c r="A244" s="11"/>
+      <c r="B244" s="12"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="12"/>
+      <c r="E244" s="12"/>
+      <c r="F244" s="12"/>
+      <c r="G244" s="12"/>
+      <c r="H244" s="12"/>
       <c r="I244" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -7991,14 +8018,14 @@
       <c r="N244" s="16"/>
     </row>
     <row r="245" spans="1:14">
-      <c r="A245" s="8"/>
-      <c r="B245" s="9"/>
-      <c r="C245" s="9"/>
-      <c r="D245" s="9"/>
-      <c r="E245" s="9"/>
-      <c r="F245" s="9"/>
-      <c r="G245" s="9"/>
-      <c r="H245" s="9"/>
+      <c r="A245" s="11"/>
+      <c r="B245" s="12"/>
+      <c r="C245" s="12"/>
+      <c r="D245" s="12"/>
+      <c r="E245" s="12"/>
+      <c r="F245" s="12"/>
+      <c r="G245" s="12"/>
+      <c r="H245" s="12"/>
       <c r="I245" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8013,14 +8040,14 @@
       <c r="N245" s="16"/>
     </row>
     <row r="246" spans="1:14">
-      <c r="A246" s="8"/>
-      <c r="B246" s="9"/>
-      <c r="C246" s="9"/>
-      <c r="D246" s="9"/>
-      <c r="E246" s="9"/>
-      <c r="F246" s="9"/>
-      <c r="G246" s="9"/>
-      <c r="H246" s="9"/>
+      <c r="A246" s="11"/>
+      <c r="B246" s="12"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="12"/>
+      <c r="E246" s="12"/>
+      <c r="F246" s="12"/>
+      <c r="G246" s="12"/>
+      <c r="H246" s="12"/>
       <c r="I246" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8035,14 +8062,14 @@
       <c r="N246" s="16"/>
     </row>
     <row r="247" spans="1:14">
-      <c r="A247" s="8"/>
-      <c r="B247" s="9"/>
-      <c r="C247" s="9"/>
-      <c r="D247" s="9"/>
-      <c r="E247" s="9"/>
-      <c r="F247" s="9"/>
-      <c r="G247" s="9"/>
-      <c r="H247" s="9"/>
+      <c r="A247" s="11"/>
+      <c r="B247" s="12"/>
+      <c r="C247" s="12"/>
+      <c r="D247" s="12"/>
+      <c r="E247" s="12"/>
+      <c r="F247" s="12"/>
+      <c r="G247" s="12"/>
+      <c r="H247" s="12"/>
       <c r="I247" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8057,14 +8084,14 @@
       <c r="N247" s="16"/>
     </row>
     <row r="248" spans="1:14">
-      <c r="A248" s="8"/>
-      <c r="B248" s="9"/>
-      <c r="C248" s="9"/>
-      <c r="D248" s="9"/>
-      <c r="E248" s="9"/>
-      <c r="F248" s="9"/>
-      <c r="G248" s="9"/>
-      <c r="H248" s="9"/>
+      <c r="A248" s="11"/>
+      <c r="B248" s="12"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="12"/>
+      <c r="E248" s="12"/>
+      <c r="F248" s="12"/>
+      <c r="G248" s="12"/>
+      <c r="H248" s="12"/>
       <c r="I248" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8079,14 +8106,14 @@
       <c r="N248" s="16"/>
     </row>
     <row r="249" spans="1:14">
-      <c r="A249" s="8"/>
-      <c r="B249" s="9"/>
-      <c r="C249" s="9"/>
-      <c r="D249" s="9"/>
-      <c r="E249" s="9"/>
-      <c r="F249" s="9"/>
-      <c r="G249" s="9"/>
-      <c r="H249" s="9"/>
+      <c r="A249" s="11"/>
+      <c r="B249" s="12"/>
+      <c r="C249" s="12"/>
+      <c r="D249" s="12"/>
+      <c r="E249" s="12"/>
+      <c r="F249" s="12"/>
+      <c r="G249" s="12"/>
+      <c r="H249" s="12"/>
       <c r="I249" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8101,14 +8128,14 @@
       <c r="N249" s="16"/>
     </row>
     <row r="250" spans="1:14">
-      <c r="A250" s="8"/>
-      <c r="B250" s="9"/>
-      <c r="C250" s="9"/>
-      <c r="D250" s="9"/>
-      <c r="E250" s="9"/>
-      <c r="F250" s="9"/>
-      <c r="G250" s="9"/>
-      <c r="H250" s="9"/>
+      <c r="A250" s="11"/>
+      <c r="B250" s="12"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="12"/>
+      <c r="E250" s="12"/>
+      <c r="F250" s="12"/>
+      <c r="G250" s="12"/>
+      <c r="H250" s="12"/>
       <c r="I250" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8123,14 +8150,14 @@
       <c r="N250" s="16"/>
     </row>
     <row r="251" spans="1:14">
-      <c r="A251" s="8"/>
-      <c r="B251" s="9"/>
-      <c r="C251" s="9"/>
-      <c r="D251" s="9"/>
-      <c r="E251" s="9"/>
-      <c r="F251" s="9"/>
-      <c r="G251" s="9"/>
-      <c r="H251" s="9"/>
+      <c r="A251" s="11"/>
+      <c r="B251" s="12"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="12"/>
+      <c r="E251" s="12"/>
+      <c r="F251" s="12"/>
+      <c r="G251" s="12"/>
+      <c r="H251" s="12"/>
       <c r="I251" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8145,14 +8172,14 @@
       <c r="N251" s="16"/>
     </row>
     <row r="252" spans="1:14">
-      <c r="A252" s="8"/>
-      <c r="B252" s="9"/>
-      <c r="C252" s="9"/>
-      <c r="D252" s="9"/>
-      <c r="E252" s="9"/>
-      <c r="F252" s="9"/>
-      <c r="G252" s="9"/>
-      <c r="H252" s="9"/>
+      <c r="A252" s="11"/>
+      <c r="B252" s="12"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="12"/>
+      <c r="E252" s="12"/>
+      <c r="F252" s="12"/>
+      <c r="G252" s="12"/>
+      <c r="H252" s="12"/>
       <c r="I252" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8167,14 +8194,14 @@
       <c r="N252" s="16"/>
     </row>
     <row r="253" spans="1:14">
-      <c r="A253" s="8"/>
-      <c r="B253" s="9"/>
-      <c r="C253" s="9"/>
-      <c r="D253" s="9"/>
-      <c r="E253" s="9"/>
-      <c r="F253" s="9"/>
-      <c r="G253" s="9"/>
-      <c r="H253" s="9"/>
+      <c r="A253" s="11"/>
+      <c r="B253" s="12"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="12"/>
+      <c r="E253" s="12"/>
+      <c r="F253" s="12"/>
+      <c r="G253" s="12"/>
+      <c r="H253" s="12"/>
       <c r="I253" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8189,14 +8216,14 @@
       <c r="N253" s="16"/>
     </row>
     <row r="254" spans="1:14">
-      <c r="A254" s="8"/>
-      <c r="B254" s="9"/>
-      <c r="C254" s="9"/>
-      <c r="D254" s="9"/>
-      <c r="E254" s="9"/>
-      <c r="F254" s="9"/>
-      <c r="G254" s="9"/>
-      <c r="H254" s="9"/>
+      <c r="A254" s="11"/>
+      <c r="B254" s="12"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="12"/>
+      <c r="E254" s="12"/>
+      <c r="F254" s="12"/>
+      <c r="G254" s="12"/>
+      <c r="H254" s="12"/>
       <c r="I254" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8211,14 +8238,14 @@
       <c r="N254" s="16"/>
     </row>
     <row r="255" spans="1:14">
-      <c r="A255" s="8"/>
-      <c r="B255" s="9"/>
-      <c r="C255" s="9"/>
-      <c r="D255" s="9"/>
-      <c r="E255" s="9"/>
-      <c r="F255" s="9"/>
-      <c r="G255" s="9"/>
-      <c r="H255" s="9"/>
+      <c r="A255" s="11"/>
+      <c r="B255" s="12"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="12"/>
+      <c r="E255" s="12"/>
+      <c r="F255" s="12"/>
+      <c r="G255" s="12"/>
+      <c r="H255" s="12"/>
       <c r="I255" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8233,14 +8260,14 @@
       <c r="N255" s="16"/>
     </row>
     <row r="256" spans="1:14">
-      <c r="A256" s="8"/>
-      <c r="B256" s="9"/>
-      <c r="C256" s="9"/>
-      <c r="D256" s="9"/>
-      <c r="E256" s="9"/>
-      <c r="F256" s="9"/>
-      <c r="G256" s="9"/>
-      <c r="H256" s="9"/>
+      <c r="A256" s="11"/>
+      <c r="B256" s="12"/>
+      <c r="C256" s="12"/>
+      <c r="D256" s="12"/>
+      <c r="E256" s="12"/>
+      <c r="F256" s="12"/>
+      <c r="G256" s="12"/>
+      <c r="H256" s="12"/>
       <c r="I256" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8255,14 +8282,14 @@
       <c r="N256" s="16"/>
     </row>
     <row r="257" spans="1:14">
-      <c r="A257" s="8"/>
-      <c r="B257" s="9"/>
-      <c r="C257" s="9"/>
-      <c r="D257" s="9"/>
-      <c r="E257" s="9"/>
-      <c r="F257" s="9"/>
-      <c r="G257" s="9"/>
-      <c r="H257" s="9"/>
+      <c r="A257" s="11"/>
+      <c r="B257" s="12"/>
+      <c r="C257" s="12"/>
+      <c r="D257" s="12"/>
+      <c r="E257" s="12"/>
+      <c r="F257" s="12"/>
+      <c r="G257" s="12"/>
+      <c r="H257" s="12"/>
       <c r="I257" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8277,14 +8304,14 @@
       <c r="N257" s="16"/>
     </row>
     <row r="258" spans="1:14">
-      <c r="A258" s="8"/>
-      <c r="B258" s="9"/>
-      <c r="C258" s="9"/>
-      <c r="D258" s="9"/>
-      <c r="E258" s="9"/>
-      <c r="F258" s="9"/>
-      <c r="G258" s="9"/>
-      <c r="H258" s="9"/>
+      <c r="A258" s="11"/>
+      <c r="B258" s="12"/>
+      <c r="C258" s="12"/>
+      <c r="D258" s="12"/>
+      <c r="E258" s="12"/>
+      <c r="F258" s="12"/>
+      <c r="G258" s="12"/>
+      <c r="H258" s="12"/>
       <c r="I258" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8299,14 +8326,14 @@
       <c r="N258" s="16"/>
     </row>
     <row r="259" spans="1:14">
-      <c r="A259" s="8"/>
-      <c r="B259" s="9"/>
-      <c r="C259" s="9"/>
-      <c r="D259" s="9"/>
-      <c r="E259" s="9"/>
-      <c r="F259" s="9"/>
-      <c r="G259" s="9"/>
-      <c r="H259" s="9"/>
+      <c r="A259" s="11"/>
+      <c r="B259" s="12"/>
+      <c r="C259" s="12"/>
+      <c r="D259" s="12"/>
+      <c r="E259" s="12"/>
+      <c r="F259" s="12"/>
+      <c r="G259" s="12"/>
+      <c r="H259" s="12"/>
       <c r="I259" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8321,14 +8348,14 @@
       <c r="N259" s="16"/>
     </row>
     <row r="260" spans="1:14">
-      <c r="A260" s="8"/>
-      <c r="B260" s="9"/>
-      <c r="C260" s="9"/>
-      <c r="D260" s="9"/>
-      <c r="E260" s="9"/>
-      <c r="F260" s="9"/>
-      <c r="G260" s="9"/>
-      <c r="H260" s="9"/>
+      <c r="A260" s="11"/>
+      <c r="B260" s="12"/>
+      <c r="C260" s="12"/>
+      <c r="D260" s="12"/>
+      <c r="E260" s="12"/>
+      <c r="F260" s="12"/>
+      <c r="G260" s="12"/>
+      <c r="H260" s="12"/>
       <c r="I260" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8343,14 +8370,14 @@
       <c r="N260" s="16"/>
     </row>
     <row r="261" spans="1:14">
-      <c r="A261" s="8"/>
-      <c r="B261" s="9"/>
-      <c r="C261" s="9"/>
-      <c r="D261" s="9"/>
-      <c r="E261" s="9"/>
-      <c r="F261" s="9"/>
-      <c r="G261" s="9"/>
-      <c r="H261" s="9"/>
+      <c r="A261" s="11"/>
+      <c r="B261" s="12"/>
+      <c r="C261" s="12"/>
+      <c r="D261" s="12"/>
+      <c r="E261" s="12"/>
+      <c r="F261" s="12"/>
+      <c r="G261" s="12"/>
+      <c r="H261" s="12"/>
       <c r="I261" s="13" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -8365,14 +8392,14 @@
       <c r="N261" s="16"/>
     </row>
     <row r="262" spans="1:14">
-      <c r="A262" s="8"/>
-      <c r="B262" s="9"/>
-      <c r="C262" s="9"/>
-      <c r="D262" s="9"/>
-      <c r="E262" s="9"/>
-      <c r="F262" s="9"/>
-      <c r="G262" s="9"/>
-      <c r="H262" s="9"/>
+      <c r="A262" s="11"/>
+      <c r="B262" s="12"/>
+      <c r="C262" s="12"/>
+      <c r="D262" s="12"/>
+      <c r="E262" s="12"/>
+      <c r="F262" s="12"/>
+      <c r="G262" s="12"/>
+      <c r="H262" s="12"/>
       <c r="I262" s="13" t="str">
         <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
@@ -8387,14 +8414,14 @@
       <c r="N262" s="16"/>
     </row>
     <row r="263" spans="1:14">
-      <c r="A263" s="8"/>
-      <c r="B263" s="9"/>
-      <c r="C263" s="9"/>
-      <c r="D263" s="9"/>
-      <c r="E263" s="9"/>
-      <c r="F263" s="9"/>
-      <c r="G263" s="9"/>
-      <c r="H263" s="9"/>
+      <c r="A263" s="11"/>
+      <c r="B263" s="12"/>
+      <c r="C263" s="12"/>
+      <c r="D263" s="12"/>
+      <c r="E263" s="12"/>
+      <c r="F263" s="12"/>
+      <c r="G263" s="12"/>
+      <c r="H263" s="12"/>
       <c r="I263" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8409,14 +8436,14 @@
       <c r="N263" s="16"/>
     </row>
     <row r="264" spans="1:14">
-      <c r="A264" s="8"/>
-      <c r="B264" s="9"/>
-      <c r="C264" s="9"/>
-      <c r="D264" s="9"/>
-      <c r="E264" s="9"/>
-      <c r="F264" s="9"/>
-      <c r="G264" s="9"/>
-      <c r="H264" s="9"/>
+      <c r="A264" s="11"/>
+      <c r="B264" s="12"/>
+      <c r="C264" s="12"/>
+      <c r="D264" s="12"/>
+      <c r="E264" s="12"/>
+      <c r="F264" s="12"/>
+      <c r="G264" s="12"/>
+      <c r="H264" s="12"/>
       <c r="I264" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8431,14 +8458,14 @@
       <c r="N264" s="16"/>
     </row>
     <row r="265" spans="1:14">
-      <c r="A265" s="8"/>
-      <c r="B265" s="9"/>
-      <c r="C265" s="9"/>
-      <c r="D265" s="9"/>
-      <c r="E265" s="9"/>
-      <c r="F265" s="9"/>
-      <c r="G265" s="9"/>
-      <c r="H265" s="9"/>
+      <c r="A265" s="11"/>
+      <c r="B265" s="12"/>
+      <c r="C265" s="12"/>
+      <c r="D265" s="12"/>
+      <c r="E265" s="12"/>
+      <c r="F265" s="12"/>
+      <c r="G265" s="12"/>
+      <c r="H265" s="12"/>
       <c r="I265" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8453,14 +8480,14 @@
       <c r="N265" s="16"/>
     </row>
     <row r="266" spans="1:14">
-      <c r="A266" s="8"/>
-      <c r="B266" s="9"/>
-      <c r="C266" s="9"/>
-      <c r="D266" s="9"/>
-      <c r="E266" s="9"/>
-      <c r="F266" s="9"/>
-      <c r="G266" s="9"/>
-      <c r="H266" s="9"/>
+      <c r="A266" s="11"/>
+      <c r="B266" s="12"/>
+      <c r="C266" s="12"/>
+      <c r="D266" s="12"/>
+      <c r="E266" s="12"/>
+      <c r="F266" s="12"/>
+      <c r="G266" s="12"/>
+      <c r="H266" s="12"/>
       <c r="I266" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8475,14 +8502,14 @@
       <c r="N266" s="16"/>
     </row>
     <row r="267" spans="1:14">
-      <c r="A267" s="8"/>
-      <c r="B267" s="9"/>
-      <c r="C267" s="9"/>
-      <c r="D267" s="9"/>
-      <c r="E267" s="9"/>
-      <c r="F267" s="9"/>
-      <c r="G267" s="9"/>
-      <c r="H267" s="9"/>
+      <c r="A267" s="11"/>
+      <c r="B267" s="12"/>
+      <c r="C267" s="12"/>
+      <c r="D267" s="12"/>
+      <c r="E267" s="12"/>
+      <c r="F267" s="12"/>
+      <c r="G267" s="12"/>
+      <c r="H267" s="12"/>
       <c r="I267" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8497,14 +8524,14 @@
       <c r="N267" s="16"/>
     </row>
     <row r="268" spans="1:14">
-      <c r="A268" s="8"/>
-      <c r="B268" s="9"/>
-      <c r="C268" s="9"/>
-      <c r="D268" s="9"/>
-      <c r="E268" s="9"/>
-      <c r="F268" s="9"/>
-      <c r="G268" s="9"/>
-      <c r="H268" s="9"/>
+      <c r="A268" s="11"/>
+      <c r="B268" s="12"/>
+      <c r="C268" s="12"/>
+      <c r="D268" s="12"/>
+      <c r="E268" s="12"/>
+      <c r="F268" s="12"/>
+      <c r="G268" s="12"/>
+      <c r="H268" s="12"/>
       <c r="I268" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8519,14 +8546,14 @@
       <c r="N268" s="16"/>
     </row>
     <row r="269" spans="1:14">
-      <c r="A269" s="8"/>
-      <c r="B269" s="9"/>
-      <c r="C269" s="9"/>
-      <c r="D269" s="9"/>
-      <c r="E269" s="9"/>
-      <c r="F269" s="9"/>
-      <c r="G269" s="9"/>
-      <c r="H269" s="9"/>
+      <c r="A269" s="11"/>
+      <c r="B269" s="12"/>
+      <c r="C269" s="12"/>
+      <c r="D269" s="12"/>
+      <c r="E269" s="12"/>
+      <c r="F269" s="12"/>
+      <c r="G269" s="12"/>
+      <c r="H269" s="12"/>
       <c r="I269" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8541,14 +8568,14 @@
       <c r="N269" s="16"/>
     </row>
     <row r="270" spans="1:14">
-      <c r="A270" s="8"/>
-      <c r="B270" s="9"/>
-      <c r="C270" s="9"/>
-      <c r="D270" s="9"/>
-      <c r="E270" s="9"/>
-      <c r="F270" s="9"/>
-      <c r="G270" s="9"/>
-      <c r="H270" s="9"/>
+      <c r="A270" s="11"/>
+      <c r="B270" s="12"/>
+      <c r="C270" s="12"/>
+      <c r="D270" s="12"/>
+      <c r="E270" s="12"/>
+      <c r="F270" s="12"/>
+      <c r="G270" s="12"/>
+      <c r="H270" s="12"/>
       <c r="I270" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8563,14 +8590,14 @@
       <c r="N270" s="16"/>
     </row>
     <row r="271" spans="1:14">
-      <c r="A271" s="8"/>
-      <c r="B271" s="9"/>
-      <c r="C271" s="9"/>
-      <c r="D271" s="9"/>
-      <c r="E271" s="9"/>
-      <c r="F271" s="9"/>
-      <c r="G271" s="9"/>
-      <c r="H271" s="9"/>
+      <c r="A271" s="11"/>
+      <c r="B271" s="12"/>
+      <c r="C271" s="12"/>
+      <c r="D271" s="12"/>
+      <c r="E271" s="12"/>
+      <c r="F271" s="12"/>
+      <c r="G271" s="12"/>
+      <c r="H271" s="12"/>
       <c r="I271" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8585,14 +8612,14 @@
       <c r="N271" s="16"/>
     </row>
     <row r="272" spans="1:14">
-      <c r="A272" s="8"/>
-      <c r="B272" s="9"/>
-      <c r="C272" s="9"/>
-      <c r="D272" s="9"/>
-      <c r="E272" s="9"/>
-      <c r="F272" s="9"/>
-      <c r="G272" s="9"/>
-      <c r="H272" s="9"/>
+      <c r="A272" s="11"/>
+      <c r="B272" s="12"/>
+      <c r="C272" s="12"/>
+      <c r="D272" s="12"/>
+      <c r="E272" s="12"/>
+      <c r="F272" s="12"/>
+      <c r="G272" s="12"/>
+      <c r="H272" s="12"/>
       <c r="I272" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8607,14 +8634,14 @@
       <c r="N272" s="16"/>
     </row>
     <row r="273" spans="1:14">
-      <c r="A273" s="8"/>
-      <c r="B273" s="9"/>
-      <c r="C273" s="9"/>
-      <c r="D273" s="9"/>
-      <c r="E273" s="9"/>
-      <c r="F273" s="9"/>
-      <c r="G273" s="9"/>
-      <c r="H273" s="9"/>
+      <c r="A273" s="11"/>
+      <c r="B273" s="12"/>
+      <c r="C273" s="12"/>
+      <c r="D273" s="12"/>
+      <c r="E273" s="12"/>
+      <c r="F273" s="12"/>
+      <c r="G273" s="12"/>
+      <c r="H273" s="12"/>
       <c r="I273" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8629,14 +8656,14 @@
       <c r="N273" s="16"/>
     </row>
     <row r="274" spans="1:14">
-      <c r="A274" s="8"/>
-      <c r="B274" s="9"/>
-      <c r="C274" s="9"/>
-      <c r="D274" s="9"/>
-      <c r="E274" s="9"/>
-      <c r="F274" s="9"/>
-      <c r="G274" s="9"/>
-      <c r="H274" s="9"/>
+      <c r="A274" s="11"/>
+      <c r="B274" s="12"/>
+      <c r="C274" s="12"/>
+      <c r="D274" s="12"/>
+      <c r="E274" s="12"/>
+      <c r="F274" s="12"/>
+      <c r="G274" s="12"/>
+      <c r="H274" s="12"/>
       <c r="I274" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8651,14 +8678,14 @@
       <c r="N274" s="16"/>
     </row>
     <row r="275" spans="1:14">
-      <c r="A275" s="8"/>
-      <c r="B275" s="9"/>
-      <c r="C275" s="9"/>
-      <c r="D275" s="9"/>
-      <c r="E275" s="9"/>
-      <c r="F275" s="9"/>
-      <c r="G275" s="9"/>
-      <c r="H275" s="9"/>
+      <c r="A275" s="11"/>
+      <c r="B275" s="12"/>
+      <c r="C275" s="12"/>
+      <c r="D275" s="12"/>
+      <c r="E275" s="12"/>
+      <c r="F275" s="12"/>
+      <c r="G275" s="12"/>
+      <c r="H275" s="12"/>
       <c r="I275" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8673,14 +8700,14 @@
       <c r="N275" s="16"/>
     </row>
     <row r="276" spans="1:14">
-      <c r="A276" s="8"/>
-      <c r="B276" s="9"/>
-      <c r="C276" s="9"/>
-      <c r="D276" s="9"/>
-      <c r="E276" s="9"/>
-      <c r="F276" s="9"/>
-      <c r="G276" s="9"/>
-      <c r="H276" s="9"/>
+      <c r="A276" s="11"/>
+      <c r="B276" s="12"/>
+      <c r="C276" s="12"/>
+      <c r="D276" s="12"/>
+      <c r="E276" s="12"/>
+      <c r="F276" s="12"/>
+      <c r="G276" s="12"/>
+      <c r="H276" s="12"/>
       <c r="I276" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8695,14 +8722,14 @@
       <c r="N276" s="16"/>
     </row>
     <row r="277" spans="1:14">
-      <c r="A277" s="8"/>
-      <c r="B277" s="9"/>
-      <c r="C277" s="9"/>
-      <c r="D277" s="9"/>
-      <c r="E277" s="9"/>
-      <c r="F277" s="9"/>
-      <c r="G277" s="9"/>
-      <c r="H277" s="9"/>
+      <c r="A277" s="11"/>
+      <c r="B277" s="12"/>
+      <c r="C277" s="12"/>
+      <c r="D277" s="12"/>
+      <c r="E277" s="12"/>
+      <c r="F277" s="12"/>
+      <c r="G277" s="12"/>
+      <c r="H277" s="12"/>
       <c r="I277" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8717,14 +8744,14 @@
       <c r="N277" s="16"/>
     </row>
     <row r="278" spans="1:14">
-      <c r="A278" s="8"/>
-      <c r="B278" s="9"/>
-      <c r="C278" s="9"/>
-      <c r="D278" s="9"/>
-      <c r="E278" s="9"/>
-      <c r="F278" s="9"/>
-      <c r="G278" s="9"/>
-      <c r="H278" s="9"/>
+      <c r="A278" s="11"/>
+      <c r="B278" s="12"/>
+      <c r="C278" s="12"/>
+      <c r="D278" s="12"/>
+      <c r="E278" s="12"/>
+      <c r="F278" s="12"/>
+      <c r="G278" s="12"/>
+      <c r="H278" s="12"/>
       <c r="I278" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8739,14 +8766,14 @@
       <c r="N278" s="16"/>
     </row>
     <row r="279" spans="1:14">
-      <c r="A279" s="8"/>
-      <c r="B279" s="9"/>
-      <c r="C279" s="9"/>
-      <c r="D279" s="9"/>
-      <c r="E279" s="9"/>
-      <c r="F279" s="9"/>
-      <c r="G279" s="9"/>
-      <c r="H279" s="9"/>
+      <c r="A279" s="11"/>
+      <c r="B279" s="12"/>
+      <c r="C279" s="12"/>
+      <c r="D279" s="12"/>
+      <c r="E279" s="12"/>
+      <c r="F279" s="12"/>
+      <c r="G279" s="12"/>
+      <c r="H279" s="12"/>
       <c r="I279" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8761,14 +8788,14 @@
       <c r="N279" s="16"/>
     </row>
     <row r="280" spans="1:14">
-      <c r="A280" s="8"/>
-      <c r="B280" s="9"/>
-      <c r="C280" s="9"/>
-      <c r="D280" s="9"/>
-      <c r="E280" s="9"/>
-      <c r="F280" s="9"/>
-      <c r="G280" s="9"/>
-      <c r="H280" s="9"/>
+      <c r="A280" s="11"/>
+      <c r="B280" s="12"/>
+      <c r="C280" s="12"/>
+      <c r="D280" s="12"/>
+      <c r="E280" s="12"/>
+      <c r="F280" s="12"/>
+      <c r="G280" s="12"/>
+      <c r="H280" s="12"/>
       <c r="I280" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8783,14 +8810,14 @@
       <c r="N280" s="16"/>
     </row>
     <row r="281" spans="1:14">
-      <c r="A281" s="8"/>
-      <c r="B281" s="9"/>
-      <c r="C281" s="9"/>
-      <c r="D281" s="9"/>
-      <c r="E281" s="9"/>
-      <c r="F281" s="9"/>
-      <c r="G281" s="9"/>
-      <c r="H281" s="9"/>
+      <c r="A281" s="11"/>
+      <c r="B281" s="12"/>
+      <c r="C281" s="12"/>
+      <c r="D281" s="12"/>
+      <c r="E281" s="12"/>
+      <c r="F281" s="12"/>
+      <c r="G281" s="12"/>
+      <c r="H281" s="12"/>
       <c r="I281" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8805,14 +8832,14 @@
       <c r="N281" s="16"/>
     </row>
     <row r="282" spans="1:14">
-      <c r="A282" s="8"/>
-      <c r="B282" s="9"/>
-      <c r="C282" s="9"/>
-      <c r="D282" s="9"/>
-      <c r="E282" s="9"/>
-      <c r="F282" s="9"/>
-      <c r="G282" s="9"/>
-      <c r="H282" s="9"/>
+      <c r="A282" s="11"/>
+      <c r="B282" s="12"/>
+      <c r="C282" s="12"/>
+      <c r="D282" s="12"/>
+      <c r="E282" s="12"/>
+      <c r="F282" s="12"/>
+      <c r="G282" s="12"/>
+      <c r="H282" s="12"/>
       <c r="I282" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8827,14 +8854,14 @@
       <c r="N282" s="16"/>
     </row>
     <row r="283" spans="1:14">
-      <c r="A283" s="8"/>
-      <c r="B283" s="9"/>
-      <c r="C283" s="9"/>
-      <c r="D283" s="9"/>
-      <c r="E283" s="9"/>
-      <c r="F283" s="9"/>
-      <c r="G283" s="9"/>
-      <c r="H283" s="9"/>
+      <c r="A283" s="11"/>
+      <c r="B283" s="12"/>
+      <c r="C283" s="12"/>
+      <c r="D283" s="12"/>
+      <c r="E283" s="12"/>
+      <c r="F283" s="12"/>
+      <c r="G283" s="12"/>
+      <c r="H283" s="12"/>
       <c r="I283" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8849,14 +8876,14 @@
       <c r="N283" s="16"/>
     </row>
     <row r="284" spans="1:14">
-      <c r="A284" s="8"/>
-      <c r="B284" s="9"/>
-      <c r="C284" s="9"/>
-      <c r="D284" s="9"/>
-      <c r="E284" s="9"/>
-      <c r="F284" s="9"/>
-      <c r="G284" s="9"/>
-      <c r="H284" s="9"/>
+      <c r="A284" s="11"/>
+      <c r="B284" s="12"/>
+      <c r="C284" s="12"/>
+      <c r="D284" s="12"/>
+      <c r="E284" s="12"/>
+      <c r="F284" s="12"/>
+      <c r="G284" s="12"/>
+      <c r="H284" s="12"/>
       <c r="I284" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8871,14 +8898,14 @@
       <c r="N284" s="16"/>
     </row>
     <row r="285" spans="1:14">
-      <c r="A285" s="8"/>
-      <c r="B285" s="9"/>
-      <c r="C285" s="9"/>
-      <c r="D285" s="9"/>
-      <c r="E285" s="9"/>
-      <c r="F285" s="9"/>
-      <c r="G285" s="9"/>
-      <c r="H285" s="9"/>
+      <c r="A285" s="11"/>
+      <c r="B285" s="12"/>
+      <c r="C285" s="12"/>
+      <c r="D285" s="12"/>
+      <c r="E285" s="12"/>
+      <c r="F285" s="12"/>
+      <c r="G285" s="12"/>
+      <c r="H285" s="12"/>
       <c r="I285" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8893,14 +8920,14 @@
       <c r="N285" s="16"/>
     </row>
     <row r="286" spans="1:14">
-      <c r="A286" s="8"/>
-      <c r="B286" s="9"/>
-      <c r="C286" s="9"/>
-      <c r="D286" s="9"/>
-      <c r="E286" s="9"/>
-      <c r="F286" s="9"/>
-      <c r="G286" s="9"/>
-      <c r="H286" s="9"/>
+      <c r="A286" s="11"/>
+      <c r="B286" s="12"/>
+      <c r="C286" s="12"/>
+      <c r="D286" s="12"/>
+      <c r="E286" s="12"/>
+      <c r="F286" s="12"/>
+      <c r="G286" s="12"/>
+      <c r="H286" s="12"/>
       <c r="I286" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8915,14 +8942,14 @@
       <c r="N286" s="16"/>
     </row>
     <row r="287" spans="1:14">
-      <c r="A287" s="8"/>
-      <c r="B287" s="9"/>
-      <c r="C287" s="9"/>
-      <c r="D287" s="9"/>
-      <c r="E287" s="9"/>
-      <c r="F287" s="9"/>
-      <c r="G287" s="9"/>
-      <c r="H287" s="9"/>
+      <c r="A287" s="11"/>
+      <c r="B287" s="12"/>
+      <c r="C287" s="12"/>
+      <c r="D287" s="12"/>
+      <c r="E287" s="12"/>
+      <c r="F287" s="12"/>
+      <c r="G287" s="12"/>
+      <c r="H287" s="12"/>
       <c r="I287" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8937,14 +8964,14 @@
       <c r="N287" s="16"/>
     </row>
     <row r="288" spans="1:14">
-      <c r="A288" s="8"/>
-      <c r="B288" s="9"/>
-      <c r="C288" s="9"/>
-      <c r="D288" s="9"/>
-      <c r="E288" s="9"/>
-      <c r="F288" s="9"/>
-      <c r="G288" s="9"/>
-      <c r="H288" s="9"/>
+      <c r="A288" s="11"/>
+      <c r="B288" s="12"/>
+      <c r="C288" s="12"/>
+      <c r="D288" s="12"/>
+      <c r="E288" s="12"/>
+      <c r="F288" s="12"/>
+      <c r="G288" s="12"/>
+      <c r="H288" s="12"/>
       <c r="I288" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8959,14 +8986,14 @@
       <c r="N288" s="16"/>
     </row>
     <row r="289" spans="1:14">
-      <c r="A289" s="8"/>
-      <c r="B289" s="9"/>
-      <c r="C289" s="9"/>
-      <c r="D289" s="9"/>
-      <c r="E289" s="9"/>
-      <c r="F289" s="9"/>
-      <c r="G289" s="9"/>
-      <c r="H289" s="9"/>
+      <c r="A289" s="11"/>
+      <c r="B289" s="12"/>
+      <c r="C289" s="12"/>
+      <c r="D289" s="12"/>
+      <c r="E289" s="12"/>
+      <c r="F289" s="12"/>
+      <c r="G289" s="12"/>
+      <c r="H289" s="12"/>
       <c r="I289" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -8981,14 +9008,14 @@
       <c r="N289" s="16"/>
     </row>
     <row r="290" spans="1:14">
-      <c r="A290" s="8"/>
-      <c r="B290" s="9"/>
-      <c r="C290" s="9"/>
-      <c r="D290" s="9"/>
-      <c r="E290" s="9"/>
-      <c r="F290" s="9"/>
-      <c r="G290" s="9"/>
-      <c r="H290" s="9"/>
+      <c r="A290" s="11"/>
+      <c r="B290" s="12"/>
+      <c r="C290" s="12"/>
+      <c r="D290" s="12"/>
+      <c r="E290" s="12"/>
+      <c r="F290" s="12"/>
+      <c r="G290" s="12"/>
+      <c r="H290" s="12"/>
       <c r="I290" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9003,14 +9030,14 @@
       <c r="N290" s="16"/>
     </row>
     <row r="291" spans="1:14">
-      <c r="A291" s="8"/>
-      <c r="B291" s="9"/>
-      <c r="C291" s="9"/>
-      <c r="D291" s="9"/>
-      <c r="E291" s="9"/>
-      <c r="F291" s="9"/>
-      <c r="G291" s="9"/>
-      <c r="H291" s="9"/>
+      <c r="A291" s="11"/>
+      <c r="B291" s="12"/>
+      <c r="C291" s="12"/>
+      <c r="D291" s="12"/>
+      <c r="E291" s="12"/>
+      <c r="F291" s="12"/>
+      <c r="G291" s="12"/>
+      <c r="H291" s="12"/>
       <c r="I291" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9025,14 +9052,14 @@
       <c r="N291" s="16"/>
     </row>
     <row r="292" spans="1:14">
-      <c r="A292" s="8"/>
-      <c r="B292" s="9"/>
-      <c r="C292" s="9"/>
-      <c r="D292" s="9"/>
-      <c r="E292" s="9"/>
-      <c r="F292" s="9"/>
-      <c r="G292" s="9"/>
-      <c r="H292" s="9"/>
+      <c r="A292" s="11"/>
+      <c r="B292" s="12"/>
+      <c r="C292" s="12"/>
+      <c r="D292" s="12"/>
+      <c r="E292" s="12"/>
+      <c r="F292" s="12"/>
+      <c r="G292" s="12"/>
+      <c r="H292" s="12"/>
       <c r="I292" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9047,14 +9074,14 @@
       <c r="N292" s="16"/>
     </row>
     <row r="293" spans="1:14">
-      <c r="A293" s="8"/>
-      <c r="B293" s="9"/>
-      <c r="C293" s="9"/>
-      <c r="D293" s="9"/>
-      <c r="E293" s="9"/>
-      <c r="F293" s="9"/>
-      <c r="G293" s="9"/>
-      <c r="H293" s="9"/>
+      <c r="A293" s="11"/>
+      <c r="B293" s="12"/>
+      <c r="C293" s="12"/>
+      <c r="D293" s="12"/>
+      <c r="E293" s="12"/>
+      <c r="F293" s="12"/>
+      <c r="G293" s="12"/>
+      <c r="H293" s="12"/>
       <c r="I293" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9069,14 +9096,14 @@
       <c r="N293" s="16"/>
     </row>
     <row r="294" spans="1:14">
-      <c r="A294" s="8"/>
-      <c r="B294" s="9"/>
-      <c r="C294" s="9"/>
-      <c r="D294" s="9"/>
-      <c r="E294" s="9"/>
-      <c r="F294" s="9"/>
-      <c r="G294" s="9"/>
-      <c r="H294" s="9"/>
+      <c r="A294" s="11"/>
+      <c r="B294" s="12"/>
+      <c r="C294" s="12"/>
+      <c r="D294" s="12"/>
+      <c r="E294" s="12"/>
+      <c r="F294" s="12"/>
+      <c r="G294" s="12"/>
+      <c r="H294" s="12"/>
       <c r="I294" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9091,14 +9118,14 @@
       <c r="N294" s="16"/>
     </row>
     <row r="295" spans="1:14">
-      <c r="A295" s="8"/>
-      <c r="B295" s="9"/>
-      <c r="C295" s="9"/>
-      <c r="D295" s="9"/>
-      <c r="E295" s="9"/>
-      <c r="F295" s="9"/>
-      <c r="G295" s="9"/>
-      <c r="H295" s="9"/>
+      <c r="A295" s="11"/>
+      <c r="B295" s="12"/>
+      <c r="C295" s="12"/>
+      <c r="D295" s="12"/>
+      <c r="E295" s="12"/>
+      <c r="F295" s="12"/>
+      <c r="G295" s="12"/>
+      <c r="H295" s="12"/>
       <c r="I295" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9113,14 +9140,14 @@
       <c r="N295" s="16"/>
     </row>
     <row r="296" spans="1:14">
-      <c r="A296" s="8"/>
-      <c r="B296" s="9"/>
-      <c r="C296" s="9"/>
-      <c r="D296" s="9"/>
-      <c r="E296" s="9"/>
-      <c r="F296" s="9"/>
-      <c r="G296" s="9"/>
-      <c r="H296" s="9"/>
+      <c r="A296" s="11"/>
+      <c r="B296" s="12"/>
+      <c r="C296" s="12"/>
+      <c r="D296" s="12"/>
+      <c r="E296" s="12"/>
+      <c r="F296" s="12"/>
+      <c r="G296" s="12"/>
+      <c r="H296" s="12"/>
       <c r="I296" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9135,14 +9162,14 @@
       <c r="N296" s="16"/>
     </row>
     <row r="297" spans="1:14">
-      <c r="A297" s="8"/>
-      <c r="B297" s="9"/>
-      <c r="C297" s="9"/>
-      <c r="D297" s="9"/>
-      <c r="E297" s="9"/>
-      <c r="F297" s="9"/>
-      <c r="G297" s="9"/>
-      <c r="H297" s="9"/>
+      <c r="A297" s="11"/>
+      <c r="B297" s="12"/>
+      <c r="C297" s="12"/>
+      <c r="D297" s="12"/>
+      <c r="E297" s="12"/>
+      <c r="F297" s="12"/>
+      <c r="G297" s="12"/>
+      <c r="H297" s="12"/>
       <c r="I297" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9157,14 +9184,14 @@
       <c r="N297" s="16"/>
     </row>
     <row r="298" spans="1:14">
-      <c r="A298" s="8"/>
-      <c r="B298" s="9"/>
-      <c r="C298" s="9"/>
-      <c r="D298" s="9"/>
-      <c r="E298" s="9"/>
-      <c r="F298" s="9"/>
-      <c r="G298" s="9"/>
-      <c r="H298" s="9"/>
+      <c r="A298" s="11"/>
+      <c r="B298" s="12"/>
+      <c r="C298" s="12"/>
+      <c r="D298" s="12"/>
+      <c r="E298" s="12"/>
+      <c r="F298" s="12"/>
+      <c r="G298" s="12"/>
+      <c r="H298" s="12"/>
       <c r="I298" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9179,14 +9206,14 @@
       <c r="N298" s="16"/>
     </row>
     <row r="299" spans="1:14">
-      <c r="A299" s="8"/>
-      <c r="B299" s="9"/>
-      <c r="C299" s="9"/>
-      <c r="D299" s="9"/>
-      <c r="E299" s="9"/>
-      <c r="F299" s="9"/>
-      <c r="G299" s="9"/>
-      <c r="H299" s="9"/>
+      <c r="A299" s="11"/>
+      <c r="B299" s="12"/>
+      <c r="C299" s="12"/>
+      <c r="D299" s="12"/>
+      <c r="E299" s="12"/>
+      <c r="F299" s="12"/>
+      <c r="G299" s="12"/>
+      <c r="H299" s="12"/>
       <c r="I299" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9201,14 +9228,14 @@
       <c r="N299" s="16"/>
     </row>
     <row r="300" spans="1:14">
-      <c r="A300" s="8"/>
-      <c r="B300" s="9"/>
-      <c r="C300" s="9"/>
-      <c r="D300" s="9"/>
-      <c r="E300" s="9"/>
-      <c r="F300" s="9"/>
-      <c r="G300" s="9"/>
-      <c r="H300" s="9"/>
+      <c r="A300" s="11"/>
+      <c r="B300" s="12"/>
+      <c r="C300" s="12"/>
+      <c r="D300" s="12"/>
+      <c r="E300" s="12"/>
+      <c r="F300" s="12"/>
+      <c r="G300" s="12"/>
+      <c r="H300" s="12"/>
       <c r="I300" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9223,14 +9250,14 @@
       <c r="N300" s="16"/>
     </row>
     <row r="301" spans="1:14">
-      <c r="A301" s="8"/>
-      <c r="B301" s="9"/>
-      <c r="C301" s="9"/>
-      <c r="D301" s="9"/>
-      <c r="E301" s="9"/>
-      <c r="F301" s="9"/>
-      <c r="G301" s="9"/>
-      <c r="H301" s="9"/>
+      <c r="A301" s="11"/>
+      <c r="B301" s="12"/>
+      <c r="C301" s="12"/>
+      <c r="D301" s="12"/>
+      <c r="E301" s="12"/>
+      <c r="F301" s="12"/>
+      <c r="G301" s="12"/>
+      <c r="H301" s="12"/>
       <c r="I301" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9245,14 +9272,14 @@
       <c r="N301" s="16"/>
     </row>
     <row r="302" spans="1:14">
-      <c r="A302" s="8"/>
-      <c r="B302" s="9"/>
-      <c r="C302" s="9"/>
-      <c r="D302" s="9"/>
-      <c r="E302" s="9"/>
-      <c r="F302" s="9"/>
-      <c r="G302" s="9"/>
-      <c r="H302" s="9"/>
+      <c r="A302" s="11"/>
+      <c r="B302" s="12"/>
+      <c r="C302" s="12"/>
+      <c r="D302" s="12"/>
+      <c r="E302" s="12"/>
+      <c r="F302" s="12"/>
+      <c r="G302" s="12"/>
+      <c r="H302" s="12"/>
       <c r="I302" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9267,14 +9294,14 @@
       <c r="N302" s="16"/>
     </row>
     <row r="303" spans="1:14">
-      <c r="A303" s="8"/>
-      <c r="B303" s="9"/>
-      <c r="C303" s="9"/>
-      <c r="D303" s="9"/>
-      <c r="E303" s="9"/>
-      <c r="F303" s="9"/>
-      <c r="G303" s="9"/>
-      <c r="H303" s="9"/>
+      <c r="A303" s="11"/>
+      <c r="B303" s="12"/>
+      <c r="C303" s="12"/>
+      <c r="D303" s="12"/>
+      <c r="E303" s="12"/>
+      <c r="F303" s="12"/>
+      <c r="G303" s="12"/>
+      <c r="H303" s="12"/>
       <c r="I303" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9289,14 +9316,14 @@
       <c r="N303" s="16"/>
     </row>
     <row r="304" spans="1:14">
-      <c r="A304" s="8"/>
-      <c r="B304" s="9"/>
-      <c r="C304" s="9"/>
-      <c r="D304" s="9"/>
-      <c r="E304" s="9"/>
-      <c r="F304" s="9"/>
-      <c r="G304" s="9"/>
-      <c r="H304" s="9"/>
+      <c r="A304" s="11"/>
+      <c r="B304" s="12"/>
+      <c r="C304" s="12"/>
+      <c r="D304" s="12"/>
+      <c r="E304" s="12"/>
+      <c r="F304" s="12"/>
+      <c r="G304" s="12"/>
+      <c r="H304" s="12"/>
       <c r="I304" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9311,14 +9338,14 @@
       <c r="N304" s="16"/>
     </row>
     <row r="305" spans="1:14">
-      <c r="A305" s="8"/>
-      <c r="B305" s="9"/>
-      <c r="C305" s="9"/>
-      <c r="D305" s="9"/>
-      <c r="E305" s="9"/>
-      <c r="F305" s="9"/>
-      <c r="G305" s="9"/>
-      <c r="H305" s="9"/>
+      <c r="A305" s="11"/>
+      <c r="B305" s="12"/>
+      <c r="C305" s="12"/>
+      <c r="D305" s="12"/>
+      <c r="E305" s="12"/>
+      <c r="F305" s="12"/>
+      <c r="G305" s="12"/>
+      <c r="H305" s="12"/>
       <c r="I305" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9333,14 +9360,14 @@
       <c r="N305" s="16"/>
     </row>
     <row r="306" spans="1:14">
-      <c r="A306" s="8"/>
-      <c r="B306" s="9"/>
-      <c r="C306" s="9"/>
-      <c r="D306" s="9"/>
-      <c r="E306" s="9"/>
-      <c r="F306" s="9"/>
-      <c r="G306" s="9"/>
-      <c r="H306" s="9"/>
+      <c r="A306" s="11"/>
+      <c r="B306" s="12"/>
+      <c r="C306" s="12"/>
+      <c r="D306" s="12"/>
+      <c r="E306" s="12"/>
+      <c r="F306" s="12"/>
+      <c r="G306" s="12"/>
+      <c r="H306" s="12"/>
       <c r="I306" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9355,14 +9382,14 @@
       <c r="N306" s="16"/>
     </row>
     <row r="307" spans="1:14">
-      <c r="A307" s="8"/>
-      <c r="B307" s="9"/>
-      <c r="C307" s="9"/>
-      <c r="D307" s="9"/>
-      <c r="E307" s="9"/>
-      <c r="F307" s="9"/>
-      <c r="G307" s="9"/>
-      <c r="H307" s="9"/>
+      <c r="A307" s="11"/>
+      <c r="B307" s="12"/>
+      <c r="C307" s="12"/>
+      <c r="D307" s="12"/>
+      <c r="E307" s="12"/>
+      <c r="F307" s="12"/>
+      <c r="G307" s="12"/>
+      <c r="H307" s="12"/>
       <c r="I307" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9377,14 +9404,14 @@
       <c r="N307" s="16"/>
     </row>
     <row r="308" spans="1:14">
-      <c r="A308" s="8"/>
-      <c r="B308" s="9"/>
-      <c r="C308" s="9"/>
-      <c r="D308" s="9"/>
-      <c r="E308" s="9"/>
-      <c r="F308" s="9"/>
-      <c r="G308" s="9"/>
-      <c r="H308" s="9"/>
+      <c r="A308" s="11"/>
+      <c r="B308" s="12"/>
+      <c r="C308" s="12"/>
+      <c r="D308" s="12"/>
+      <c r="E308" s="12"/>
+      <c r="F308" s="12"/>
+      <c r="G308" s="12"/>
+      <c r="H308" s="12"/>
       <c r="I308" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9399,14 +9426,14 @@
       <c r="N308" s="16"/>
     </row>
     <row r="309" spans="1:14">
-      <c r="A309" s="8"/>
-      <c r="B309" s="9"/>
-      <c r="C309" s="9"/>
-      <c r="D309" s="9"/>
-      <c r="E309" s="9"/>
-      <c r="F309" s="9"/>
-      <c r="G309" s="9"/>
-      <c r="H309" s="9"/>
+      <c r="A309" s="11"/>
+      <c r="B309" s="12"/>
+      <c r="C309" s="12"/>
+      <c r="D309" s="12"/>
+      <c r="E309" s="12"/>
+      <c r="F309" s="12"/>
+      <c r="G309" s="12"/>
+      <c r="H309" s="12"/>
       <c r="I309" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9421,14 +9448,14 @@
       <c r="N309" s="16"/>
     </row>
     <row r="310" spans="1:14">
-      <c r="A310" s="8"/>
-      <c r="B310" s="9"/>
-      <c r="C310" s="9"/>
-      <c r="D310" s="9"/>
-      <c r="E310" s="9"/>
-      <c r="F310" s="9"/>
-      <c r="G310" s="9"/>
-      <c r="H310" s="9"/>
+      <c r="A310" s="11"/>
+      <c r="B310" s="12"/>
+      <c r="C310" s="12"/>
+      <c r="D310" s="12"/>
+      <c r="E310" s="12"/>
+      <c r="F310" s="12"/>
+      <c r="G310" s="12"/>
+      <c r="H310" s="12"/>
       <c r="I310" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9443,14 +9470,14 @@
       <c r="N310" s="16"/>
     </row>
     <row r="311" spans="1:14">
-      <c r="A311" s="8"/>
-      <c r="B311" s="9"/>
-      <c r="C311" s="9"/>
-      <c r="D311" s="9"/>
-      <c r="E311" s="9"/>
-      <c r="F311" s="9"/>
-      <c r="G311" s="9"/>
-      <c r="H311" s="9"/>
+      <c r="A311" s="11"/>
+      <c r="B311" s="12"/>
+      <c r="C311" s="12"/>
+      <c r="D311" s="12"/>
+      <c r="E311" s="12"/>
+      <c r="F311" s="12"/>
+      <c r="G311" s="12"/>
+      <c r="H311" s="12"/>
       <c r="I311" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9465,14 +9492,14 @@
       <c r="N311" s="16"/>
     </row>
     <row r="312" spans="1:14">
-      <c r="A312" s="8"/>
-      <c r="B312" s="9"/>
-      <c r="C312" s="9"/>
-      <c r="D312" s="9"/>
-      <c r="E312" s="9"/>
-      <c r="F312" s="9"/>
-      <c r="G312" s="9"/>
-      <c r="H312" s="9"/>
+      <c r="A312" s="11"/>
+      <c r="B312" s="12"/>
+      <c r="C312" s="12"/>
+      <c r="D312" s="12"/>
+      <c r="E312" s="12"/>
+      <c r="F312" s="12"/>
+      <c r="G312" s="12"/>
+      <c r="H312" s="12"/>
       <c r="I312" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9487,14 +9514,14 @@
       <c r="N312" s="16"/>
     </row>
     <row r="313" spans="1:14">
-      <c r="A313" s="8"/>
-      <c r="B313" s="9"/>
-      <c r="C313" s="9"/>
-      <c r="D313" s="9"/>
-      <c r="E313" s="9"/>
-      <c r="F313" s="9"/>
-      <c r="G313" s="9"/>
-      <c r="H313" s="9"/>
+      <c r="A313" s="11"/>
+      <c r="B313" s="12"/>
+      <c r="C313" s="12"/>
+      <c r="D313" s="12"/>
+      <c r="E313" s="12"/>
+      <c r="F313" s="12"/>
+      <c r="G313" s="12"/>
+      <c r="H313" s="12"/>
       <c r="I313" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9509,14 +9536,14 @@
       <c r="N313" s="16"/>
     </row>
     <row r="314" spans="1:14">
-      <c r="A314" s="8"/>
-      <c r="B314" s="9"/>
-      <c r="C314" s="9"/>
-      <c r="D314" s="9"/>
-      <c r="E314" s="9"/>
-      <c r="F314" s="9"/>
-      <c r="G314" s="9"/>
-      <c r="H314" s="9"/>
+      <c r="A314" s="11"/>
+      <c r="B314" s="12"/>
+      <c r="C314" s="12"/>
+      <c r="D314" s="12"/>
+      <c r="E314" s="12"/>
+      <c r="F314" s="12"/>
+      <c r="G314" s="12"/>
+      <c r="H314" s="12"/>
       <c r="I314" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9531,14 +9558,14 @@
       <c r="N314" s="16"/>
     </row>
     <row r="315" spans="1:14">
-      <c r="A315" s="8"/>
-      <c r="B315" s="9"/>
-      <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
-      <c r="E315" s="9"/>
-      <c r="F315" s="9"/>
-      <c r="G315" s="9"/>
-      <c r="H315" s="9"/>
+      <c r="A315" s="11"/>
+      <c r="B315" s="12"/>
+      <c r="C315" s="12"/>
+      <c r="D315" s="12"/>
+      <c r="E315" s="12"/>
+      <c r="F315" s="12"/>
+      <c r="G315" s="12"/>
+      <c r="H315" s="12"/>
       <c r="I315" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9553,14 +9580,14 @@
       <c r="N315" s="16"/>
     </row>
     <row r="316" spans="1:14">
-      <c r="A316" s="8"/>
-      <c r="B316" s="9"/>
-      <c r="C316" s="9"/>
-      <c r="D316" s="9"/>
-      <c r="E316" s="9"/>
-      <c r="F316" s="9"/>
-      <c r="G316" s="9"/>
-      <c r="H316" s="9"/>
+      <c r="A316" s="11"/>
+      <c r="B316" s="12"/>
+      <c r="C316" s="12"/>
+      <c r="D316" s="12"/>
+      <c r="E316" s="12"/>
+      <c r="F316" s="12"/>
+      <c r="G316" s="12"/>
+      <c r="H316" s="12"/>
       <c r="I316" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9575,14 +9602,14 @@
       <c r="N316" s="16"/>
     </row>
     <row r="317" spans="1:14">
-      <c r="A317" s="8"/>
-      <c r="B317" s="9"/>
-      <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
-      <c r="E317" s="9"/>
-      <c r="F317" s="9"/>
-      <c r="G317" s="9"/>
-      <c r="H317" s="9"/>
+      <c r="A317" s="11"/>
+      <c r="B317" s="12"/>
+      <c r="C317" s="12"/>
+      <c r="D317" s="12"/>
+      <c r="E317" s="12"/>
+      <c r="F317" s="12"/>
+      <c r="G317" s="12"/>
+      <c r="H317" s="12"/>
       <c r="I317" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9597,14 +9624,14 @@
       <c r="N317" s="16"/>
     </row>
     <row r="318" spans="1:14">
-      <c r="A318" s="8"/>
-      <c r="B318" s="9"/>
-      <c r="C318" s="9"/>
-      <c r="D318" s="9"/>
-      <c r="E318" s="9"/>
-      <c r="F318" s="9"/>
-      <c r="G318" s="9"/>
-      <c r="H318" s="9"/>
+      <c r="A318" s="11"/>
+      <c r="B318" s="12"/>
+      <c r="C318" s="12"/>
+      <c r="D318" s="12"/>
+      <c r="E318" s="12"/>
+      <c r="F318" s="12"/>
+      <c r="G318" s="12"/>
+      <c r="H318" s="12"/>
       <c r="I318" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9619,14 +9646,14 @@
       <c r="N318" s="16"/>
     </row>
     <row r="319" spans="1:14">
-      <c r="A319" s="8"/>
-      <c r="B319" s="9"/>
-      <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
-      <c r="E319" s="9"/>
-      <c r="F319" s="9"/>
-      <c r="G319" s="9"/>
-      <c r="H319" s="9"/>
+      <c r="A319" s="11"/>
+      <c r="B319" s="12"/>
+      <c r="C319" s="12"/>
+      <c r="D319" s="12"/>
+      <c r="E319" s="12"/>
+      <c r="F319" s="12"/>
+      <c r="G319" s="12"/>
+      <c r="H319" s="12"/>
       <c r="I319" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9641,14 +9668,14 @@
       <c r="N319" s="16"/>
     </row>
     <row r="320" spans="1:14">
-      <c r="A320" s="8"/>
-      <c r="B320" s="9"/>
-      <c r="C320" s="9"/>
-      <c r="D320" s="9"/>
-      <c r="E320" s="9"/>
-      <c r="F320" s="9"/>
-      <c r="G320" s="9"/>
-      <c r="H320" s="9"/>
+      <c r="A320" s="11"/>
+      <c r="B320" s="12"/>
+      <c r="C320" s="12"/>
+      <c r="D320" s="12"/>
+      <c r="E320" s="12"/>
+      <c r="F320" s="12"/>
+      <c r="G320" s="12"/>
+      <c r="H320" s="12"/>
       <c r="I320" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9663,14 +9690,14 @@
       <c r="N320" s="16"/>
     </row>
     <row r="321" spans="1:14">
-      <c r="A321" s="8"/>
-      <c r="B321" s="9"/>
-      <c r="C321" s="9"/>
-      <c r="D321" s="9"/>
-      <c r="E321" s="9"/>
-      <c r="F321" s="9"/>
-      <c r="G321" s="9"/>
-      <c r="H321" s="9"/>
+      <c r="A321" s="11"/>
+      <c r="B321" s="12"/>
+      <c r="C321" s="12"/>
+      <c r="D321" s="12"/>
+      <c r="E321" s="12"/>
+      <c r="F321" s="12"/>
+      <c r="G321" s="12"/>
+      <c r="H321" s="12"/>
       <c r="I321" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9685,14 +9712,14 @@
       <c r="N321" s="16"/>
     </row>
     <row r="322" spans="1:14">
-      <c r="A322" s="8"/>
-      <c r="B322" s="9"/>
-      <c r="C322" s="9"/>
-      <c r="D322" s="9"/>
-      <c r="E322" s="9"/>
-      <c r="F322" s="9"/>
-      <c r="G322" s="9"/>
-      <c r="H322" s="9"/>
+      <c r="A322" s="11"/>
+      <c r="B322" s="12"/>
+      <c r="C322" s="12"/>
+      <c r="D322" s="12"/>
+      <c r="E322" s="12"/>
+      <c r="F322" s="12"/>
+      <c r="G322" s="12"/>
+      <c r="H322" s="12"/>
       <c r="I322" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9707,14 +9734,14 @@
       <c r="N322" s="16"/>
     </row>
     <row r="323" spans="1:14">
-      <c r="A323" s="8"/>
-      <c r="B323" s="9"/>
-      <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
-      <c r="E323" s="9"/>
-      <c r="F323" s="9"/>
-      <c r="G323" s="9"/>
-      <c r="H323" s="9"/>
+      <c r="A323" s="11"/>
+      <c r="B323" s="12"/>
+      <c r="C323" s="12"/>
+      <c r="D323" s="12"/>
+      <c r="E323" s="12"/>
+      <c r="F323" s="12"/>
+      <c r="G323" s="12"/>
+      <c r="H323" s="12"/>
       <c r="I323" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9729,14 +9756,14 @@
       <c r="N323" s="16"/>
     </row>
     <row r="324" spans="1:14">
-      <c r="A324" s="8"/>
-      <c r="B324" s="9"/>
-      <c r="C324" s="9"/>
-      <c r="D324" s="9"/>
-      <c r="E324" s="9"/>
-      <c r="F324" s="9"/>
-      <c r="G324" s="9"/>
-      <c r="H324" s="9"/>
+      <c r="A324" s="11"/>
+      <c r="B324" s="12"/>
+      <c r="C324" s="12"/>
+      <c r="D324" s="12"/>
+      <c r="E324" s="12"/>
+      <c r="F324" s="12"/>
+      <c r="G324" s="12"/>
+      <c r="H324" s="12"/>
       <c r="I324" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9751,14 +9778,14 @@
       <c r="N324" s="16"/>
     </row>
     <row r="325" spans="1:14">
-      <c r="A325" s="8"/>
-      <c r="B325" s="9"/>
-      <c r="C325" s="9"/>
-      <c r="D325" s="9"/>
-      <c r="E325" s="9"/>
-      <c r="F325" s="9"/>
-      <c r="G325" s="9"/>
-      <c r="H325" s="9"/>
+      <c r="A325" s="11"/>
+      <c r="B325" s="12"/>
+      <c r="C325" s="12"/>
+      <c r="D325" s="12"/>
+      <c r="E325" s="12"/>
+      <c r="F325" s="12"/>
+      <c r="G325" s="12"/>
+      <c r="H325" s="12"/>
       <c r="I325" s="13" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -9773,14 +9800,14 @@
       <c r="N325" s="16"/>
     </row>
     <row r="326" spans="1:14">
-      <c r="A326" s="8"/>
-      <c r="B326" s="9"/>
-      <c r="C326" s="9"/>
-      <c r="D326" s="9"/>
-      <c r="E326" s="9"/>
-      <c r="F326" s="9"/>
-      <c r="G326" s="9"/>
-      <c r="H326" s="9"/>
+      <c r="A326" s="11"/>
+      <c r="B326" s="12"/>
+      <c r="C326" s="12"/>
+      <c r="D326" s="12"/>
+      <c r="E326" s="12"/>
+      <c r="F326" s="12"/>
+      <c r="G326" s="12"/>
+      <c r="H326" s="12"/>
       <c r="I326" s="13" t="str">
         <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
@@ -9795,14 +9822,14 @@
       <c r="N326" s="16"/>
     </row>
     <row r="327" spans="1:14">
-      <c r="A327" s="8"/>
-      <c r="B327" s="9"/>
-      <c r="C327" s="9"/>
-      <c r="D327" s="9"/>
-      <c r="E327" s="9"/>
-      <c r="F327" s="9"/>
-      <c r="G327" s="9"/>
-      <c r="H327" s="9"/>
+      <c r="A327" s="11"/>
+      <c r="B327" s="12"/>
+      <c r="C327" s="12"/>
+      <c r="D327" s="12"/>
+      <c r="E327" s="12"/>
+      <c r="F327" s="12"/>
+      <c r="G327" s="12"/>
+      <c r="H327" s="12"/>
       <c r="I327" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9817,14 +9844,14 @@
       <c r="N327" s="16"/>
     </row>
     <row r="328" spans="1:14">
-      <c r="A328" s="8"/>
-      <c r="B328" s="9"/>
-      <c r="C328" s="9"/>
-      <c r="D328" s="9"/>
-      <c r="E328" s="9"/>
-      <c r="F328" s="9"/>
-      <c r="G328" s="9"/>
-      <c r="H328" s="9"/>
+      <c r="A328" s="11"/>
+      <c r="B328" s="12"/>
+      <c r="C328" s="12"/>
+      <c r="D328" s="12"/>
+      <c r="E328" s="12"/>
+      <c r="F328" s="12"/>
+      <c r="G328" s="12"/>
+      <c r="H328" s="12"/>
       <c r="I328" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9839,14 +9866,14 @@
       <c r="N328" s="16"/>
     </row>
     <row r="329" spans="1:14">
-      <c r="A329" s="8"/>
-      <c r="B329" s="9"/>
-      <c r="C329" s="9"/>
-      <c r="D329" s="9"/>
-      <c r="E329" s="9"/>
-      <c r="F329" s="9"/>
-      <c r="G329" s="9"/>
-      <c r="H329" s="9"/>
+      <c r="A329" s="11"/>
+      <c r="B329" s="12"/>
+      <c r="C329" s="12"/>
+      <c r="D329" s="12"/>
+      <c r="E329" s="12"/>
+      <c r="F329" s="12"/>
+      <c r="G329" s="12"/>
+      <c r="H329" s="12"/>
       <c r="I329" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9861,14 +9888,14 @@
       <c r="N329" s="16"/>
     </row>
     <row r="330" spans="1:14">
-      <c r="A330" s="8"/>
-      <c r="B330" s="9"/>
-      <c r="C330" s="9"/>
-      <c r="D330" s="9"/>
-      <c r="E330" s="9"/>
-      <c r="F330" s="9"/>
-      <c r="G330" s="9"/>
-      <c r="H330" s="9"/>
+      <c r="A330" s="11"/>
+      <c r="B330" s="12"/>
+      <c r="C330" s="12"/>
+      <c r="D330" s="12"/>
+      <c r="E330" s="12"/>
+      <c r="F330" s="12"/>
+      <c r="G330" s="12"/>
+      <c r="H330" s="12"/>
       <c r="I330" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9883,14 +9910,14 @@
       <c r="N330" s="16"/>
     </row>
     <row r="331" spans="1:14">
-      <c r="A331" s="8"/>
-      <c r="B331" s="9"/>
-      <c r="C331" s="9"/>
-      <c r="D331" s="9"/>
-      <c r="E331" s="9"/>
-      <c r="F331" s="9"/>
-      <c r="G331" s="9"/>
-      <c r="H331" s="9"/>
+      <c r="A331" s="11"/>
+      <c r="B331" s="12"/>
+      <c r="C331" s="12"/>
+      <c r="D331" s="12"/>
+      <c r="E331" s="12"/>
+      <c r="F331" s="12"/>
+      <c r="G331" s="12"/>
+      <c r="H331" s="12"/>
       <c r="I331" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9905,14 +9932,14 @@
       <c r="N331" s="16"/>
     </row>
     <row r="332" spans="1:14">
-      <c r="A332" s="8"/>
-      <c r="B332" s="9"/>
-      <c r="C332" s="9"/>
-      <c r="D332" s="9"/>
-      <c r="E332" s="9"/>
-      <c r="F332" s="9"/>
-      <c r="G332" s="9"/>
-      <c r="H332" s="9"/>
+      <c r="A332" s="11"/>
+      <c r="B332" s="12"/>
+      <c r="C332" s="12"/>
+      <c r="D332" s="12"/>
+      <c r="E332" s="12"/>
+      <c r="F332" s="12"/>
+      <c r="G332" s="12"/>
+      <c r="H332" s="12"/>
       <c r="I332" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9927,14 +9954,14 @@
       <c r="N332" s="16"/>
     </row>
     <row r="333" spans="1:14">
-      <c r="A333" s="8"/>
-      <c r="B333" s="9"/>
-      <c r="C333" s="9"/>
-      <c r="D333" s="9"/>
-      <c r="E333" s="9"/>
-      <c r="F333" s="9"/>
-      <c r="G333" s="9"/>
-      <c r="H333" s="9"/>
+      <c r="A333" s="11"/>
+      <c r="B333" s="12"/>
+      <c r="C333" s="12"/>
+      <c r="D333" s="12"/>
+      <c r="E333" s="12"/>
+      <c r="F333" s="12"/>
+      <c r="G333" s="12"/>
+      <c r="H333" s="12"/>
       <c r="I333" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9949,14 +9976,14 @@
       <c r="N333" s="16"/>
     </row>
     <row r="334" spans="1:14">
-      <c r="A334" s="8"/>
-      <c r="B334" s="9"/>
-      <c r="C334" s="9"/>
-      <c r="D334" s="9"/>
-      <c r="E334" s="9"/>
-      <c r="F334" s="9"/>
-      <c r="G334" s="9"/>
-      <c r="H334" s="9"/>
+      <c r="A334" s="11"/>
+      <c r="B334" s="12"/>
+      <c r="C334" s="12"/>
+      <c r="D334" s="12"/>
+      <c r="E334" s="12"/>
+      <c r="F334" s="12"/>
+      <c r="G334" s="12"/>
+      <c r="H334" s="12"/>
       <c r="I334" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9971,14 +9998,14 @@
       <c r="N334" s="16"/>
     </row>
     <row r="335" spans="1:14">
-      <c r="A335" s="8"/>
-      <c r="B335" s="9"/>
-      <c r="C335" s="9"/>
-      <c r="D335" s="9"/>
-      <c r="E335" s="9"/>
-      <c r="F335" s="9"/>
-      <c r="G335" s="9"/>
-      <c r="H335" s="9"/>
+      <c r="A335" s="11"/>
+      <c r="B335" s="12"/>
+      <c r="C335" s="12"/>
+      <c r="D335" s="12"/>
+      <c r="E335" s="12"/>
+      <c r="F335" s="12"/>
+      <c r="G335" s="12"/>
+      <c r="H335" s="12"/>
       <c r="I335" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -9993,14 +10020,14 @@
       <c r="N335" s="16"/>
     </row>
     <row r="336" spans="1:14">
-      <c r="A336" s="8"/>
-      <c r="B336" s="9"/>
-      <c r="C336" s="9"/>
-      <c r="D336" s="9"/>
-      <c r="E336" s="9"/>
-      <c r="F336" s="9"/>
-      <c r="G336" s="9"/>
-      <c r="H336" s="9"/>
+      <c r="A336" s="11"/>
+      <c r="B336" s="12"/>
+      <c r="C336" s="12"/>
+      <c r="D336" s="12"/>
+      <c r="E336" s="12"/>
+      <c r="F336" s="12"/>
+      <c r="G336" s="12"/>
+      <c r="H336" s="12"/>
       <c r="I336" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10015,14 +10042,14 @@
       <c r="N336" s="16"/>
     </row>
     <row r="337" spans="1:14">
-      <c r="A337" s="8"/>
-      <c r="B337" s="9"/>
-      <c r="C337" s="9"/>
-      <c r="D337" s="9"/>
-      <c r="E337" s="9"/>
-      <c r="F337" s="9"/>
-      <c r="G337" s="9"/>
-      <c r="H337" s="9"/>
+      <c r="A337" s="11"/>
+      <c r="B337" s="12"/>
+      <c r="C337" s="12"/>
+      <c r="D337" s="12"/>
+      <c r="E337" s="12"/>
+      <c r="F337" s="12"/>
+      <c r="G337" s="12"/>
+      <c r="H337" s="12"/>
       <c r="I337" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10037,14 +10064,14 @@
       <c r="N337" s="16"/>
     </row>
     <row r="338" spans="1:14">
-      <c r="A338" s="8"/>
-      <c r="B338" s="9"/>
-      <c r="C338" s="9"/>
-      <c r="D338" s="9"/>
-      <c r="E338" s="9"/>
-      <c r="F338" s="9"/>
-      <c r="G338" s="9"/>
-      <c r="H338" s="9"/>
+      <c r="A338" s="11"/>
+      <c r="B338" s="12"/>
+      <c r="C338" s="12"/>
+      <c r="D338" s="12"/>
+      <c r="E338" s="12"/>
+      <c r="F338" s="12"/>
+      <c r="G338" s="12"/>
+      <c r="H338" s="12"/>
       <c r="I338" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10059,14 +10086,14 @@
       <c r="N338" s="16"/>
     </row>
     <row r="339" spans="1:14">
-      <c r="A339" s="8"/>
-      <c r="B339" s="9"/>
-      <c r="C339" s="9"/>
-      <c r="D339" s="9"/>
-      <c r="E339" s="9"/>
-      <c r="F339" s="9"/>
-      <c r="G339" s="9"/>
-      <c r="H339" s="9"/>
+      <c r="A339" s="11"/>
+      <c r="B339" s="12"/>
+      <c r="C339" s="12"/>
+      <c r="D339" s="12"/>
+      <c r="E339" s="12"/>
+      <c r="F339" s="12"/>
+      <c r="G339" s="12"/>
+      <c r="H339" s="12"/>
       <c r="I339" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10081,14 +10108,14 @@
       <c r="N339" s="16"/>
     </row>
     <row r="340" spans="1:14">
-      <c r="A340" s="8"/>
-      <c r="B340" s="9"/>
-      <c r="C340" s="9"/>
-      <c r="D340" s="9"/>
-      <c r="E340" s="9"/>
-      <c r="F340" s="9"/>
-      <c r="G340" s="9"/>
-      <c r="H340" s="9"/>
+      <c r="A340" s="11"/>
+      <c r="B340" s="12"/>
+      <c r="C340" s="12"/>
+      <c r="D340" s="12"/>
+      <c r="E340" s="12"/>
+      <c r="F340" s="12"/>
+      <c r="G340" s="12"/>
+      <c r="H340" s="12"/>
       <c r="I340" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10103,14 +10130,14 @@
       <c r="N340" s="16"/>
     </row>
     <row r="341" spans="1:14">
-      <c r="A341" s="8"/>
-      <c r="B341" s="9"/>
-      <c r="C341" s="9"/>
-      <c r="D341" s="9"/>
-      <c r="E341" s="9"/>
-      <c r="F341" s="9"/>
-      <c r="G341" s="9"/>
-      <c r="H341" s="9"/>
+      <c r="A341" s="11"/>
+      <c r="B341" s="12"/>
+      <c r="C341" s="12"/>
+      <c r="D341" s="12"/>
+      <c r="E341" s="12"/>
+      <c r="F341" s="12"/>
+      <c r="G341" s="12"/>
+      <c r="H341" s="12"/>
       <c r="I341" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10125,14 +10152,14 @@
       <c r="N341" s="16"/>
     </row>
     <row r="342" spans="1:14">
-      <c r="A342" s="8"/>
-      <c r="B342" s="9"/>
-      <c r="C342" s="9"/>
-      <c r="D342" s="9"/>
-      <c r="E342" s="9"/>
-      <c r="F342" s="9"/>
-      <c r="G342" s="9"/>
-      <c r="H342" s="9"/>
+      <c r="A342" s="11"/>
+      <c r="B342" s="12"/>
+      <c r="C342" s="12"/>
+      <c r="D342" s="12"/>
+      <c r="E342" s="12"/>
+      <c r="F342" s="12"/>
+      <c r="G342" s="12"/>
+      <c r="H342" s="12"/>
       <c r="I342" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10147,14 +10174,14 @@
       <c r="N342" s="16"/>
     </row>
     <row r="343" spans="1:14">
-      <c r="A343" s="8"/>
-      <c r="B343" s="9"/>
-      <c r="C343" s="9"/>
-      <c r="D343" s="9"/>
-      <c r="E343" s="9"/>
-      <c r="F343" s="9"/>
-      <c r="G343" s="9"/>
-      <c r="H343" s="9"/>
+      <c r="A343" s="11"/>
+      <c r="B343" s="12"/>
+      <c r="C343" s="12"/>
+      <c r="D343" s="12"/>
+      <c r="E343" s="12"/>
+      <c r="F343" s="12"/>
+      <c r="G343" s="12"/>
+      <c r="H343" s="12"/>
       <c r="I343" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10169,14 +10196,14 @@
       <c r="N343" s="16"/>
     </row>
     <row r="344" spans="1:14">
-      <c r="A344" s="8"/>
-      <c r="B344" s="9"/>
-      <c r="C344" s="9"/>
-      <c r="D344" s="9"/>
-      <c r="E344" s="9"/>
-      <c r="F344" s="9"/>
-      <c r="G344" s="9"/>
-      <c r="H344" s="9"/>
+      <c r="A344" s="11"/>
+      <c r="B344" s="12"/>
+      <c r="C344" s="12"/>
+      <c r="D344" s="12"/>
+      <c r="E344" s="12"/>
+      <c r="F344" s="12"/>
+      <c r="G344" s="12"/>
+      <c r="H344" s="12"/>
       <c r="I344" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10191,14 +10218,14 @@
       <c r="N344" s="16"/>
     </row>
     <row r="345" spans="1:14">
-      <c r="A345" s="8"/>
-      <c r="B345" s="9"/>
-      <c r="C345" s="9"/>
-      <c r="D345" s="9"/>
-      <c r="E345" s="9"/>
-      <c r="F345" s="9"/>
-      <c r="G345" s="9"/>
-      <c r="H345" s="9"/>
+      <c r="A345" s="11"/>
+      <c r="B345" s="12"/>
+      <c r="C345" s="12"/>
+      <c r="D345" s="12"/>
+      <c r="E345" s="12"/>
+      <c r="F345" s="12"/>
+      <c r="G345" s="12"/>
+      <c r="H345" s="12"/>
       <c r="I345" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10213,14 +10240,14 @@
       <c r="N345" s="16"/>
     </row>
     <row r="346" spans="1:14">
-      <c r="A346" s="8"/>
-      <c r="B346" s="9"/>
-      <c r="C346" s="9"/>
-      <c r="D346" s="9"/>
-      <c r="E346" s="9"/>
-      <c r="F346" s="9"/>
-      <c r="G346" s="9"/>
-      <c r="H346" s="9"/>
+      <c r="A346" s="11"/>
+      <c r="B346" s="12"/>
+      <c r="C346" s="12"/>
+      <c r="D346" s="12"/>
+      <c r="E346" s="12"/>
+      <c r="F346" s="12"/>
+      <c r="G346" s="12"/>
+      <c r="H346" s="12"/>
       <c r="I346" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10235,14 +10262,14 @@
       <c r="N346" s="16"/>
     </row>
     <row r="347" spans="1:14">
-      <c r="A347" s="8"/>
-      <c r="B347" s="9"/>
-      <c r="C347" s="9"/>
-      <c r="D347" s="9"/>
-      <c r="E347" s="9"/>
-      <c r="F347" s="9"/>
-      <c r="G347" s="9"/>
-      <c r="H347" s="9"/>
+      <c r="A347" s="11"/>
+      <c r="B347" s="12"/>
+      <c r="C347" s="12"/>
+      <c r="D347" s="12"/>
+      <c r="E347" s="12"/>
+      <c r="F347" s="12"/>
+      <c r="G347" s="12"/>
+      <c r="H347" s="12"/>
       <c r="I347" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10257,14 +10284,14 @@
       <c r="N347" s="16"/>
     </row>
     <row r="348" spans="1:14">
-      <c r="A348" s="8"/>
-      <c r="B348" s="9"/>
-      <c r="C348" s="9"/>
-      <c r="D348" s="9"/>
-      <c r="E348" s="9"/>
-      <c r="F348" s="9"/>
-      <c r="G348" s="9"/>
-      <c r="H348" s="9"/>
+      <c r="A348" s="11"/>
+      <c r="B348" s="12"/>
+      <c r="C348" s="12"/>
+      <c r="D348" s="12"/>
+      <c r="E348" s="12"/>
+      <c r="F348" s="12"/>
+      <c r="G348" s="12"/>
+      <c r="H348" s="12"/>
       <c r="I348" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10279,14 +10306,14 @@
       <c r="N348" s="16"/>
     </row>
     <row r="349" spans="1:14">
-      <c r="A349" s="8"/>
-      <c r="B349" s="9"/>
-      <c r="C349" s="9"/>
-      <c r="D349" s="9"/>
-      <c r="E349" s="9"/>
-      <c r="F349" s="9"/>
-      <c r="G349" s="9"/>
-      <c r="H349" s="9"/>
+      <c r="A349" s="11"/>
+      <c r="B349" s="12"/>
+      <c r="C349" s="12"/>
+      <c r="D349" s="12"/>
+      <c r="E349" s="12"/>
+      <c r="F349" s="12"/>
+      <c r="G349" s="12"/>
+      <c r="H349" s="12"/>
       <c r="I349" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10301,14 +10328,14 @@
       <c r="N349" s="16"/>
     </row>
     <row r="350" spans="1:14">
-      <c r="A350" s="8"/>
-      <c r="B350" s="9"/>
-      <c r="C350" s="9"/>
-      <c r="D350" s="9"/>
-      <c r="E350" s="9"/>
-      <c r="F350" s="9"/>
-      <c r="G350" s="9"/>
-      <c r="H350" s="9"/>
+      <c r="A350" s="11"/>
+      <c r="B350" s="12"/>
+      <c r="C350" s="12"/>
+      <c r="D350" s="12"/>
+      <c r="E350" s="12"/>
+      <c r="F350" s="12"/>
+      <c r="G350" s="12"/>
+      <c r="H350" s="12"/>
       <c r="I350" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10323,14 +10350,14 @@
       <c r="N350" s="16"/>
     </row>
     <row r="351" spans="1:14">
-      <c r="A351" s="8"/>
-      <c r="B351" s="9"/>
-      <c r="C351" s="9"/>
-      <c r="D351" s="9"/>
-      <c r="E351" s="9"/>
-      <c r="F351" s="9"/>
-      <c r="G351" s="9"/>
-      <c r="H351" s="9"/>
+      <c r="A351" s="11"/>
+      <c r="B351" s="12"/>
+      <c r="C351" s="12"/>
+      <c r="D351" s="12"/>
+      <c r="E351" s="12"/>
+      <c r="F351" s="12"/>
+      <c r="G351" s="12"/>
+      <c r="H351" s="12"/>
       <c r="I351" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10345,14 +10372,14 @@
       <c r="N351" s="16"/>
     </row>
     <row r="352" spans="1:14">
-      <c r="A352" s="8"/>
-      <c r="B352" s="9"/>
-      <c r="C352" s="9"/>
-      <c r="D352" s="9"/>
-      <c r="E352" s="9"/>
-      <c r="F352" s="9"/>
-      <c r="G352" s="9"/>
-      <c r="H352" s="9"/>
+      <c r="A352" s="11"/>
+      <c r="B352" s="12"/>
+      <c r="C352" s="12"/>
+      <c r="D352" s="12"/>
+      <c r="E352" s="12"/>
+      <c r="F352" s="12"/>
+      <c r="G352" s="12"/>
+      <c r="H352" s="12"/>
       <c r="I352" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10367,14 +10394,14 @@
       <c r="N352" s="16"/>
     </row>
     <row r="353" spans="1:14">
-      <c r="A353" s="8"/>
-      <c r="B353" s="9"/>
-      <c r="C353" s="9"/>
-      <c r="D353" s="9"/>
-      <c r="E353" s="9"/>
-      <c r="F353" s="9"/>
-      <c r="G353" s="9"/>
-      <c r="H353" s="9"/>
+      <c r="A353" s="11"/>
+      <c r="B353" s="12"/>
+      <c r="C353" s="12"/>
+      <c r="D353" s="12"/>
+      <c r="E353" s="12"/>
+      <c r="F353" s="12"/>
+      <c r="G353" s="12"/>
+      <c r="H353" s="12"/>
       <c r="I353" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10389,14 +10416,14 @@
       <c r="N353" s="16"/>
     </row>
     <row r="354" spans="1:14">
-      <c r="A354" s="8"/>
-      <c r="B354" s="9"/>
-      <c r="C354" s="9"/>
-      <c r="D354" s="9"/>
-      <c r="E354" s="9"/>
-      <c r="F354" s="9"/>
-      <c r="G354" s="9"/>
-      <c r="H354" s="9"/>
+      <c r="A354" s="11"/>
+      <c r="B354" s="12"/>
+      <c r="C354" s="12"/>
+      <c r="D354" s="12"/>
+      <c r="E354" s="12"/>
+      <c r="F354" s="12"/>
+      <c r="G354" s="12"/>
+      <c r="H354" s="12"/>
       <c r="I354" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10411,14 +10438,14 @@
       <c r="N354" s="16"/>
     </row>
     <row r="355" spans="1:14">
-      <c r="A355" s="8"/>
-      <c r="B355" s="9"/>
-      <c r="C355" s="9"/>
-      <c r="D355" s="9"/>
-      <c r="E355" s="9"/>
-      <c r="F355" s="9"/>
-      <c r="G355" s="9"/>
-      <c r="H355" s="9"/>
+      <c r="A355" s="11"/>
+      <c r="B355" s="12"/>
+      <c r="C355" s="12"/>
+      <c r="D355" s="12"/>
+      <c r="E355" s="12"/>
+      <c r="F355" s="12"/>
+      <c r="G355" s="12"/>
+      <c r="H355" s="12"/>
       <c r="I355" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10433,14 +10460,14 @@
       <c r="N355" s="16"/>
     </row>
     <row r="356" spans="1:14">
-      <c r="A356" s="8"/>
-      <c r="B356" s="9"/>
-      <c r="C356" s="9"/>
-      <c r="D356" s="9"/>
-      <c r="E356" s="9"/>
-      <c r="F356" s="9"/>
-      <c r="G356" s="9"/>
-      <c r="H356" s="9"/>
+      <c r="A356" s="11"/>
+      <c r="B356" s="12"/>
+      <c r="C356" s="12"/>
+      <c r="D356" s="12"/>
+      <c r="E356" s="12"/>
+      <c r="F356" s="12"/>
+      <c r="G356" s="12"/>
+      <c r="H356" s="12"/>
       <c r="I356" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10455,14 +10482,14 @@
       <c r="N356" s="16"/>
     </row>
     <row r="357" spans="1:14">
-      <c r="A357" s="8"/>
-      <c r="B357" s="9"/>
-      <c r="C357" s="9"/>
-      <c r="D357" s="9"/>
-      <c r="E357" s="9"/>
-      <c r="F357" s="9"/>
-      <c r="G357" s="9"/>
-      <c r="H357" s="9"/>
+      <c r="A357" s="11"/>
+      <c r="B357" s="12"/>
+      <c r="C357" s="12"/>
+      <c r="D357" s="12"/>
+      <c r="E357" s="12"/>
+      <c r="F357" s="12"/>
+      <c r="G357" s="12"/>
+      <c r="H357" s="12"/>
       <c r="I357" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10477,14 +10504,14 @@
       <c r="N357" s="16"/>
     </row>
     <row r="358" spans="1:14">
-      <c r="A358" s="8"/>
-      <c r="B358" s="9"/>
-      <c r="C358" s="9"/>
-      <c r="D358" s="9"/>
-      <c r="E358" s="9"/>
-      <c r="F358" s="9"/>
-      <c r="G358" s="9"/>
-      <c r="H358" s="9"/>
+      <c r="A358" s="11"/>
+      <c r="B358" s="12"/>
+      <c r="C358" s="12"/>
+      <c r="D358" s="12"/>
+      <c r="E358" s="12"/>
+      <c r="F358" s="12"/>
+      <c r="G358" s="12"/>
+      <c r="H358" s="12"/>
       <c r="I358" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10499,14 +10526,14 @@
       <c r="N358" s="16"/>
     </row>
     <row r="359" spans="1:14">
-      <c r="A359" s="8"/>
-      <c r="B359" s="9"/>
-      <c r="C359" s="9"/>
-      <c r="D359" s="9"/>
-      <c r="E359" s="9"/>
-      <c r="F359" s="9"/>
-      <c r="G359" s="9"/>
-      <c r="H359" s="9"/>
+      <c r="A359" s="11"/>
+      <c r="B359" s="12"/>
+      <c r="C359" s="12"/>
+      <c r="D359" s="12"/>
+      <c r="E359" s="12"/>
+      <c r="F359" s="12"/>
+      <c r="G359" s="12"/>
+      <c r="H359" s="12"/>
       <c r="I359" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10521,14 +10548,14 @@
       <c r="N359" s="16"/>
     </row>
     <row r="360" spans="1:14">
-      <c r="A360" s="8"/>
-      <c r="B360" s="9"/>
-      <c r="C360" s="9"/>
-      <c r="D360" s="9"/>
-      <c r="E360" s="9"/>
-      <c r="F360" s="9"/>
-      <c r="G360" s="9"/>
-      <c r="H360" s="9"/>
+      <c r="A360" s="11"/>
+      <c r="B360" s="12"/>
+      <c r="C360" s="12"/>
+      <c r="D360" s="12"/>
+      <c r="E360" s="12"/>
+      <c r="F360" s="12"/>
+      <c r="G360" s="12"/>
+      <c r="H360" s="12"/>
       <c r="I360" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10543,14 +10570,14 @@
       <c r="N360" s="16"/>
     </row>
     <row r="361" spans="1:14">
-      <c r="A361" s="8"/>
-      <c r="B361" s="9"/>
-      <c r="C361" s="9"/>
-      <c r="D361" s="9"/>
-      <c r="E361" s="9"/>
-      <c r="F361" s="9"/>
-      <c r="G361" s="9"/>
-      <c r="H361" s="9"/>
+      <c r="A361" s="11"/>
+      <c r="B361" s="12"/>
+      <c r="C361" s="12"/>
+      <c r="D361" s="12"/>
+      <c r="E361" s="12"/>
+      <c r="F361" s="12"/>
+      <c r="G361" s="12"/>
+      <c r="H361" s="12"/>
       <c r="I361" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10565,14 +10592,14 @@
       <c r="N361" s="16"/>
     </row>
     <row r="362" spans="1:14">
-      <c r="A362" s="8"/>
-      <c r="B362" s="9"/>
-      <c r="C362" s="9"/>
-      <c r="D362" s="9"/>
-      <c r="E362" s="9"/>
-      <c r="F362" s="9"/>
-      <c r="G362" s="9"/>
-      <c r="H362" s="9"/>
+      <c r="A362" s="11"/>
+      <c r="B362" s="12"/>
+      <c r="C362" s="12"/>
+      <c r="D362" s="12"/>
+      <c r="E362" s="12"/>
+      <c r="F362" s="12"/>
+      <c r="G362" s="12"/>
+      <c r="H362" s="12"/>
       <c r="I362" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10587,14 +10614,14 @@
       <c r="N362" s="16"/>
     </row>
     <row r="363" spans="1:14">
-      <c r="A363" s="8"/>
-      <c r="B363" s="9"/>
-      <c r="C363" s="9"/>
-      <c r="D363" s="9"/>
-      <c r="E363" s="9"/>
-      <c r="F363" s="9"/>
-      <c r="G363" s="9"/>
-      <c r="H363" s="9"/>
+      <c r="A363" s="11"/>
+      <c r="B363" s="12"/>
+      <c r="C363" s="12"/>
+      <c r="D363" s="12"/>
+      <c r="E363" s="12"/>
+      <c r="F363" s="12"/>
+      <c r="G363" s="12"/>
+      <c r="H363" s="12"/>
       <c r="I363" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10609,14 +10636,14 @@
       <c r="N363" s="16"/>
     </row>
     <row r="364" spans="1:14">
-      <c r="A364" s="8"/>
-      <c r="B364" s="9"/>
-      <c r="C364" s="9"/>
-      <c r="D364" s="9"/>
-      <c r="E364" s="9"/>
-      <c r="F364" s="9"/>
-      <c r="G364" s="9"/>
-      <c r="H364" s="9"/>
+      <c r="A364" s="11"/>
+      <c r="B364" s="12"/>
+      <c r="C364" s="12"/>
+      <c r="D364" s="12"/>
+      <c r="E364" s="12"/>
+      <c r="F364" s="12"/>
+      <c r="G364" s="12"/>
+      <c r="H364" s="12"/>
       <c r="I364" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10631,14 +10658,14 @@
       <c r="N364" s="16"/>
     </row>
     <row r="365" spans="1:14">
-      <c r="A365" s="8"/>
-      <c r="B365" s="9"/>
-      <c r="C365" s="9"/>
-      <c r="D365" s="9"/>
-      <c r="E365" s="9"/>
-      <c r="F365" s="9"/>
-      <c r="G365" s="9"/>
-      <c r="H365" s="9"/>
+      <c r="A365" s="11"/>
+      <c r="B365" s="12"/>
+      <c r="C365" s="12"/>
+      <c r="D365" s="12"/>
+      <c r="E365" s="12"/>
+      <c r="F365" s="12"/>
+      <c r="G365" s="12"/>
+      <c r="H365" s="12"/>
       <c r="I365" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10653,14 +10680,14 @@
       <c r="N365" s="16"/>
     </row>
     <row r="366" spans="1:14">
-      <c r="A366" s="8"/>
-      <c r="B366" s="9"/>
-      <c r="C366" s="9"/>
-      <c r="D366" s="9"/>
-      <c r="E366" s="9"/>
-      <c r="F366" s="9"/>
-      <c r="G366" s="9"/>
-      <c r="H366" s="9"/>
+      <c r="A366" s="11"/>
+      <c r="B366" s="12"/>
+      <c r="C366" s="12"/>
+      <c r="D366" s="12"/>
+      <c r="E366" s="12"/>
+      <c r="F366" s="12"/>
+      <c r="G366" s="12"/>
+      <c r="H366" s="12"/>
       <c r="I366" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10675,14 +10702,14 @@
       <c r="N366" s="16"/>
     </row>
     <row r="367" spans="1:14">
-      <c r="A367" s="8"/>
-      <c r="B367" s="9"/>
-      <c r="C367" s="9"/>
-      <c r="D367" s="9"/>
-      <c r="E367" s="9"/>
-      <c r="F367" s="9"/>
-      <c r="G367" s="9"/>
-      <c r="H367" s="9"/>
+      <c r="A367" s="11"/>
+      <c r="B367" s="12"/>
+      <c r="C367" s="12"/>
+      <c r="D367" s="12"/>
+      <c r="E367" s="12"/>
+      <c r="F367" s="12"/>
+      <c r="G367" s="12"/>
+      <c r="H367" s="12"/>
       <c r="I367" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10697,14 +10724,14 @@
       <c r="N367" s="16"/>
     </row>
     <row r="368" spans="1:14">
-      <c r="A368" s="8"/>
-      <c r="B368" s="9"/>
-      <c r="C368" s="9"/>
-      <c r="D368" s="9"/>
-      <c r="E368" s="9"/>
-      <c r="F368" s="9"/>
-      <c r="G368" s="9"/>
-      <c r="H368" s="9"/>
+      <c r="A368" s="11"/>
+      <c r="B368" s="12"/>
+      <c r="C368" s="12"/>
+      <c r="D368" s="12"/>
+      <c r="E368" s="12"/>
+      <c r="F368" s="12"/>
+      <c r="G368" s="12"/>
+      <c r="H368" s="12"/>
       <c r="I368" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10719,14 +10746,14 @@
       <c r="N368" s="16"/>
     </row>
     <row r="369" spans="1:14">
-      <c r="A369" s="8"/>
-      <c r="B369" s="9"/>
-      <c r="C369" s="9"/>
-      <c r="D369" s="9"/>
-      <c r="E369" s="9"/>
-      <c r="F369" s="9"/>
-      <c r="G369" s="9"/>
-      <c r="H369" s="9"/>
+      <c r="A369" s="11"/>
+      <c r="B369" s="12"/>
+      <c r="C369" s="12"/>
+      <c r="D369" s="12"/>
+      <c r="E369" s="12"/>
+      <c r="F369" s="12"/>
+      <c r="G369" s="12"/>
+      <c r="H369" s="12"/>
       <c r="I369" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10741,14 +10768,14 @@
       <c r="N369" s="16"/>
     </row>
     <row r="370" spans="1:14">
-      <c r="A370" s="8"/>
-      <c r="B370" s="9"/>
-      <c r="C370" s="9"/>
-      <c r="D370" s="9"/>
-      <c r="E370" s="9"/>
-      <c r="F370" s="9"/>
-      <c r="G370" s="9"/>
-      <c r="H370" s="9"/>
+      <c r="A370" s="11"/>
+      <c r="B370" s="12"/>
+      <c r="C370" s="12"/>
+      <c r="D370" s="12"/>
+      <c r="E370" s="12"/>
+      <c r="F370" s="12"/>
+      <c r="G370" s="12"/>
+      <c r="H370" s="12"/>
       <c r="I370" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10763,14 +10790,14 @@
       <c r="N370" s="16"/>
     </row>
     <row r="371" spans="1:14">
-      <c r="A371" s="8"/>
-      <c r="B371" s="9"/>
-      <c r="C371" s="9"/>
-      <c r="D371" s="9"/>
-      <c r="E371" s="9"/>
-      <c r="F371" s="9"/>
-      <c r="G371" s="9"/>
-      <c r="H371" s="9"/>
+      <c r="A371" s="11"/>
+      <c r="B371" s="12"/>
+      <c r="C371" s="12"/>
+      <c r="D371" s="12"/>
+      <c r="E371" s="12"/>
+      <c r="F371" s="12"/>
+      <c r="G371" s="12"/>
+      <c r="H371" s="12"/>
       <c r="I371" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10785,14 +10812,14 @@
       <c r="N371" s="16"/>
     </row>
     <row r="372" spans="1:14">
-      <c r="A372" s="8"/>
-      <c r="B372" s="9"/>
-      <c r="C372" s="9"/>
-      <c r="D372" s="9"/>
-      <c r="E372" s="9"/>
-      <c r="F372" s="9"/>
-      <c r="G372" s="9"/>
-      <c r="H372" s="9"/>
+      <c r="A372" s="11"/>
+      <c r="B372" s="12"/>
+      <c r="C372" s="12"/>
+      <c r="D372" s="12"/>
+      <c r="E372" s="12"/>
+      <c r="F372" s="12"/>
+      <c r="G372" s="12"/>
+      <c r="H372" s="12"/>
       <c r="I372" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10807,14 +10834,14 @@
       <c r="N372" s="16"/>
     </row>
     <row r="373" spans="1:14">
-      <c r="A373" s="8"/>
-      <c r="B373" s="9"/>
-      <c r="C373" s="9"/>
-      <c r="D373" s="9"/>
-      <c r="E373" s="9"/>
-      <c r="F373" s="9"/>
-      <c r="G373" s="9"/>
-      <c r="H373" s="9"/>
+      <c r="A373" s="11"/>
+      <c r="B373" s="12"/>
+      <c r="C373" s="12"/>
+      <c r="D373" s="12"/>
+      <c r="E373" s="12"/>
+      <c r="F373" s="12"/>
+      <c r="G373" s="12"/>
+      <c r="H373" s="12"/>
       <c r="I373" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10829,14 +10856,14 @@
       <c r="N373" s="16"/>
     </row>
     <row r="374" spans="1:14">
-      <c r="A374" s="8"/>
-      <c r="B374" s="9"/>
-      <c r="C374" s="9"/>
-      <c r="D374" s="9"/>
-      <c r="E374" s="9"/>
-      <c r="F374" s="9"/>
-      <c r="G374" s="9"/>
-      <c r="H374" s="9"/>
+      <c r="A374" s="11"/>
+      <c r="B374" s="12"/>
+      <c r="C374" s="12"/>
+      <c r="D374" s="12"/>
+      <c r="E374" s="12"/>
+      <c r="F374" s="12"/>
+      <c r="G374" s="12"/>
+      <c r="H374" s="12"/>
       <c r="I374" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10851,14 +10878,14 @@
       <c r="N374" s="16"/>
     </row>
     <row r="375" spans="1:14">
-      <c r="A375" s="8"/>
-      <c r="B375" s="9"/>
-      <c r="C375" s="9"/>
-      <c r="D375" s="9"/>
-      <c r="E375" s="9"/>
-      <c r="F375" s="9"/>
-      <c r="G375" s="9"/>
-      <c r="H375" s="9"/>
+      <c r="A375" s="11"/>
+      <c r="B375" s="12"/>
+      <c r="C375" s="12"/>
+      <c r="D375" s="12"/>
+      <c r="E375" s="12"/>
+      <c r="F375" s="12"/>
+      <c r="G375" s="12"/>
+      <c r="H375" s="12"/>
       <c r="I375" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10873,14 +10900,14 @@
       <c r="N375" s="16"/>
     </row>
     <row r="376" spans="1:14">
-      <c r="A376" s="8"/>
-      <c r="B376" s="9"/>
-      <c r="C376" s="9"/>
-      <c r="D376" s="9"/>
-      <c r="E376" s="9"/>
-      <c r="F376" s="9"/>
-      <c r="G376" s="9"/>
-      <c r="H376" s="9"/>
+      <c r="A376" s="11"/>
+      <c r="B376" s="12"/>
+      <c r="C376" s="12"/>
+      <c r="D376" s="12"/>
+      <c r="E376" s="12"/>
+      <c r="F376" s="12"/>
+      <c r="G376" s="12"/>
+      <c r="H376" s="12"/>
       <c r="I376" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10895,14 +10922,14 @@
       <c r="N376" s="16"/>
     </row>
     <row r="377" spans="1:14">
-      <c r="A377" s="8"/>
-      <c r="B377" s="9"/>
-      <c r="C377" s="9"/>
-      <c r="D377" s="9"/>
-      <c r="E377" s="9"/>
-      <c r="F377" s="9"/>
-      <c r="G377" s="9"/>
-      <c r="H377" s="9"/>
+      <c r="A377" s="11"/>
+      <c r="B377" s="12"/>
+      <c r="C377" s="12"/>
+      <c r="D377" s="12"/>
+      <c r="E377" s="12"/>
+      <c r="F377" s="12"/>
+      <c r="G377" s="12"/>
+      <c r="H377" s="12"/>
       <c r="I377" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10917,14 +10944,14 @@
       <c r="N377" s="16"/>
     </row>
     <row r="378" spans="1:14">
-      <c r="A378" s="8"/>
-      <c r="B378" s="9"/>
-      <c r="C378" s="9"/>
-      <c r="D378" s="9"/>
-      <c r="E378" s="9"/>
-      <c r="F378" s="9"/>
-      <c r="G378" s="9"/>
-      <c r="H378" s="9"/>
+      <c r="A378" s="11"/>
+      <c r="B378" s="12"/>
+      <c r="C378" s="12"/>
+      <c r="D378" s="12"/>
+      <c r="E378" s="12"/>
+      <c r="F378" s="12"/>
+      <c r="G378" s="12"/>
+      <c r="H378" s="12"/>
       <c r="I378" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10939,14 +10966,14 @@
       <c r="N378" s="16"/>
     </row>
     <row r="379" spans="1:14">
-      <c r="A379" s="8"/>
-      <c r="B379" s="9"/>
-      <c r="C379" s="9"/>
-      <c r="D379" s="9"/>
-      <c r="E379" s="9"/>
-      <c r="F379" s="9"/>
-      <c r="G379" s="9"/>
-      <c r="H379" s="9"/>
+      <c r="A379" s="11"/>
+      <c r="B379" s="12"/>
+      <c r="C379" s="12"/>
+      <c r="D379" s="12"/>
+      <c r="E379" s="12"/>
+      <c r="F379" s="12"/>
+      <c r="G379" s="12"/>
+      <c r="H379" s="12"/>
       <c r="I379" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10961,14 +10988,14 @@
       <c r="N379" s="16"/>
     </row>
     <row r="380" spans="1:14">
-      <c r="A380" s="8"/>
-      <c r="B380" s="9"/>
-      <c r="C380" s="9"/>
-      <c r="D380" s="9"/>
-      <c r="E380" s="9"/>
-      <c r="F380" s="9"/>
-      <c r="G380" s="9"/>
-      <c r="H380" s="9"/>
+      <c r="A380" s="11"/>
+      <c r="B380" s="12"/>
+      <c r="C380" s="12"/>
+      <c r="D380" s="12"/>
+      <c r="E380" s="12"/>
+      <c r="F380" s="12"/>
+      <c r="G380" s="12"/>
+      <c r="H380" s="12"/>
       <c r="I380" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -10983,14 +11010,14 @@
       <c r="N380" s="16"/>
     </row>
     <row r="381" spans="1:14">
-      <c r="A381" s="8"/>
-      <c r="B381" s="9"/>
-      <c r="C381" s="9"/>
-      <c r="D381" s="9"/>
-      <c r="E381" s="9"/>
-      <c r="F381" s="9"/>
-      <c r="G381" s="9"/>
-      <c r="H381" s="9"/>
+      <c r="A381" s="11"/>
+      <c r="B381" s="12"/>
+      <c r="C381" s="12"/>
+      <c r="D381" s="12"/>
+      <c r="E381" s="12"/>
+      <c r="F381" s="12"/>
+      <c r="G381" s="12"/>
+      <c r="H381" s="12"/>
       <c r="I381" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11005,14 +11032,14 @@
       <c r="N381" s="16"/>
     </row>
     <row r="382" spans="1:14">
-      <c r="A382" s="8"/>
-      <c r="B382" s="9"/>
-      <c r="C382" s="9"/>
-      <c r="D382" s="9"/>
-      <c r="E382" s="9"/>
-      <c r="F382" s="9"/>
-      <c r="G382" s="9"/>
-      <c r="H382" s="9"/>
+      <c r="A382" s="11"/>
+      <c r="B382" s="12"/>
+      <c r="C382" s="12"/>
+      <c r="D382" s="12"/>
+      <c r="E382" s="12"/>
+      <c r="F382" s="12"/>
+      <c r="G382" s="12"/>
+      <c r="H382" s="12"/>
       <c r="I382" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11027,14 +11054,14 @@
       <c r="N382" s="16"/>
     </row>
     <row r="383" spans="1:14">
-      <c r="A383" s="8"/>
-      <c r="B383" s="9"/>
-      <c r="C383" s="9"/>
-      <c r="D383" s="9"/>
-      <c r="E383" s="9"/>
-      <c r="F383" s="9"/>
-      <c r="G383" s="9"/>
-      <c r="H383" s="9"/>
+      <c r="A383" s="11"/>
+      <c r="B383" s="12"/>
+      <c r="C383" s="12"/>
+      <c r="D383" s="12"/>
+      <c r="E383" s="12"/>
+      <c r="F383" s="12"/>
+      <c r="G383" s="12"/>
+      <c r="H383" s="12"/>
       <c r="I383" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11049,14 +11076,14 @@
       <c r="N383" s="16"/>
     </row>
     <row r="384" spans="1:14">
-      <c r="A384" s="8"/>
-      <c r="B384" s="9"/>
-      <c r="C384" s="9"/>
-      <c r="D384" s="9"/>
-      <c r="E384" s="9"/>
-      <c r="F384" s="9"/>
-      <c r="G384" s="9"/>
-      <c r="H384" s="9"/>
+      <c r="A384" s="11"/>
+      <c r="B384" s="12"/>
+      <c r="C384" s="12"/>
+      <c r="D384" s="12"/>
+      <c r="E384" s="12"/>
+      <c r="F384" s="12"/>
+      <c r="G384" s="12"/>
+      <c r="H384" s="12"/>
       <c r="I384" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11071,14 +11098,14 @@
       <c r="N384" s="16"/>
     </row>
     <row r="385" spans="1:14">
-      <c r="A385" s="8"/>
-      <c r="B385" s="9"/>
-      <c r="C385" s="9"/>
-      <c r="D385" s="9"/>
-      <c r="E385" s="9"/>
-      <c r="F385" s="9"/>
-      <c r="G385" s="9"/>
-      <c r="H385" s="9"/>
+      <c r="A385" s="11"/>
+      <c r="B385" s="12"/>
+      <c r="C385" s="12"/>
+      <c r="D385" s="12"/>
+      <c r="E385" s="12"/>
+      <c r="F385" s="12"/>
+      <c r="G385" s="12"/>
+      <c r="H385" s="12"/>
       <c r="I385" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11093,14 +11120,14 @@
       <c r="N385" s="16"/>
     </row>
     <row r="386" spans="1:14">
-      <c r="A386" s="8"/>
-      <c r="B386" s="9"/>
-      <c r="C386" s="9"/>
-      <c r="D386" s="9"/>
-      <c r="E386" s="9"/>
-      <c r="F386" s="9"/>
-      <c r="G386" s="9"/>
-      <c r="H386" s="9"/>
+      <c r="A386" s="11"/>
+      <c r="B386" s="12"/>
+      <c r="C386" s="12"/>
+      <c r="D386" s="12"/>
+      <c r="E386" s="12"/>
+      <c r="F386" s="12"/>
+      <c r="G386" s="12"/>
+      <c r="H386" s="12"/>
       <c r="I386" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11115,14 +11142,14 @@
       <c r="N386" s="16"/>
     </row>
     <row r="387" spans="1:14">
-      <c r="A387" s="8"/>
-      <c r="B387" s="9"/>
-      <c r="C387" s="9"/>
-      <c r="D387" s="9"/>
-      <c r="E387" s="9"/>
-      <c r="F387" s="9"/>
-      <c r="G387" s="9"/>
-      <c r="H387" s="9"/>
+      <c r="A387" s="11"/>
+      <c r="B387" s="12"/>
+      <c r="C387" s="12"/>
+      <c r="D387" s="12"/>
+      <c r="E387" s="12"/>
+      <c r="F387" s="12"/>
+      <c r="G387" s="12"/>
+      <c r="H387" s="12"/>
       <c r="I387" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11137,14 +11164,14 @@
       <c r="N387" s="16"/>
     </row>
     <row r="388" spans="1:14">
-      <c r="A388" s="8"/>
-      <c r="B388" s="9"/>
-      <c r="C388" s="9"/>
-      <c r="D388" s="9"/>
-      <c r="E388" s="9"/>
-      <c r="F388" s="9"/>
-      <c r="G388" s="9"/>
-      <c r="H388" s="9"/>
+      <c r="A388" s="11"/>
+      <c r="B388" s="12"/>
+      <c r="C388" s="12"/>
+      <c r="D388" s="12"/>
+      <c r="E388" s="12"/>
+      <c r="F388" s="12"/>
+      <c r="G388" s="12"/>
+      <c r="H388" s="12"/>
       <c r="I388" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11159,14 +11186,14 @@
       <c r="N388" s="16"/>
     </row>
     <row r="389" spans="1:14">
-      <c r="A389" s="8"/>
-      <c r="B389" s="9"/>
-      <c r="C389" s="9"/>
-      <c r="D389" s="9"/>
-      <c r="E389" s="9"/>
-      <c r="F389" s="9"/>
-      <c r="G389" s="9"/>
-      <c r="H389" s="9"/>
+      <c r="A389" s="11"/>
+      <c r="B389" s="12"/>
+      <c r="C389" s="12"/>
+      <c r="D389" s="12"/>
+      <c r="E389" s="12"/>
+      <c r="F389" s="12"/>
+      <c r="G389" s="12"/>
+      <c r="H389" s="12"/>
       <c r="I389" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -11181,14 +11208,14 @@
       <c r="N389" s="16"/>
     </row>
     <row r="390" spans="1:14">
-      <c r="A390" s="8"/>
-      <c r="B390" s="9"/>
-      <c r="C390" s="9"/>
-      <c r="D390" s="9"/>
-      <c r="E390" s="9"/>
-      <c r="F390" s="9"/>
-      <c r="G390" s="9"/>
-      <c r="H390" s="9"/>
+      <c r="A390" s="11"/>
+      <c r="B390" s="12"/>
+      <c r="C390" s="12"/>
+      <c r="D390" s="12"/>
+      <c r="E390" s="12"/>
+      <c r="F390" s="12"/>
+      <c r="G390" s="12"/>
+      <c r="H390" s="12"/>
       <c r="I390" s="13" t="str">
         <f t="shared" ref="I390:I453" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
@@ -11203,14 +11230,14 @@
       <c r="N390" s="16"/>
     </row>
     <row r="391" spans="1:14">
-      <c r="A391" s="8"/>
-      <c r="B391" s="9"/>
-      <c r="C391" s="9"/>
-      <c r="D391" s="9"/>
-      <c r="E391" s="9"/>
-      <c r="F391" s="9"/>
-      <c r="G391" s="9"/>
-      <c r="H391" s="9"/>
+      <c r="A391" s="11"/>
+      <c r="B391" s="12"/>
+      <c r="C391" s="12"/>
+      <c r="D391" s="12"/>
+      <c r="E391" s="12"/>
+      <c r="F391" s="12"/>
+      <c r="G391" s="12"/>
+      <c r="H391" s="12"/>
       <c r="I391" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11225,14 +11252,14 @@
       <c r="N391" s="16"/>
     </row>
     <row r="392" spans="1:14">
-      <c r="A392" s="8"/>
-      <c r="B392" s="9"/>
-      <c r="C392" s="9"/>
-      <c r="D392" s="9"/>
-      <c r="E392" s="9"/>
-      <c r="F392" s="9"/>
-      <c r="G392" s="9"/>
-      <c r="H392" s="9"/>
+      <c r="A392" s="11"/>
+      <c r="B392" s="12"/>
+      <c r="C392" s="12"/>
+      <c r="D392" s="12"/>
+      <c r="E392" s="12"/>
+      <c r="F392" s="12"/>
+      <c r="G392" s="12"/>
+      <c r="H392" s="12"/>
       <c r="I392" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11247,14 +11274,14 @@
       <c r="N392" s="16"/>
     </row>
     <row r="393" spans="1:14">
-      <c r="A393" s="8"/>
-      <c r="B393" s="9"/>
-      <c r="C393" s="9"/>
-      <c r="D393" s="9"/>
-      <c r="E393" s="9"/>
-      <c r="F393" s="9"/>
-      <c r="G393" s="9"/>
-      <c r="H393" s="9"/>
+      <c r="A393" s="11"/>
+      <c r="B393" s="12"/>
+      <c r="C393" s="12"/>
+      <c r="D393" s="12"/>
+      <c r="E393" s="12"/>
+      <c r="F393" s="12"/>
+      <c r="G393" s="12"/>
+      <c r="H393" s="12"/>
       <c r="I393" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11269,14 +11296,14 @@
       <c r="N393" s="16"/>
     </row>
     <row r="394" spans="1:14">
-      <c r="A394" s="8"/>
-      <c r="B394" s="9"/>
-      <c r="C394" s="9"/>
-      <c r="D394" s="9"/>
-      <c r="E394" s="9"/>
-      <c r="F394" s="9"/>
-      <c r="G394" s="9"/>
-      <c r="H394" s="9"/>
+      <c r="A394" s="11"/>
+      <c r="B394" s="12"/>
+      <c r="C394" s="12"/>
+      <c r="D394" s="12"/>
+      <c r="E394" s="12"/>
+      <c r="F394" s="12"/>
+      <c r="G394" s="12"/>
+      <c r="H394" s="12"/>
       <c r="I394" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11291,14 +11318,14 @@
       <c r="N394" s="16"/>
     </row>
     <row r="395" spans="1:14">
-      <c r="A395" s="8"/>
-      <c r="B395" s="9"/>
-      <c r="C395" s="9"/>
-      <c r="D395" s="9"/>
-      <c r="E395" s="9"/>
-      <c r="F395" s="9"/>
-      <c r="G395" s="9"/>
-      <c r="H395" s="9"/>
+      <c r="A395" s="11"/>
+      <c r="B395" s="12"/>
+      <c r="C395" s="12"/>
+      <c r="D395" s="12"/>
+      <c r="E395" s="12"/>
+      <c r="F395" s="12"/>
+      <c r="G395" s="12"/>
+      <c r="H395" s="12"/>
       <c r="I395" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11313,14 +11340,14 @@
       <c r="N395" s="16"/>
     </row>
     <row r="396" spans="1:14">
-      <c r="A396" s="8"/>
-      <c r="B396" s="9"/>
-      <c r="C396" s="9"/>
-      <c r="D396" s="9"/>
-      <c r="E396" s="9"/>
-      <c r="F396" s="9"/>
-      <c r="G396" s="9"/>
-      <c r="H396" s="9"/>
+      <c r="A396" s="11"/>
+      <c r="B396" s="12"/>
+      <c r="C396" s="12"/>
+      <c r="D396" s="12"/>
+      <c r="E396" s="12"/>
+      <c r="F396" s="12"/>
+      <c r="G396" s="12"/>
+      <c r="H396" s="12"/>
       <c r="I396" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11335,14 +11362,14 @@
       <c r="N396" s="16"/>
     </row>
     <row r="397" spans="1:14">
-      <c r="A397" s="8"/>
-      <c r="B397" s="9"/>
-      <c r="C397" s="9"/>
-      <c r="D397" s="9"/>
-      <c r="E397" s="9"/>
-      <c r="F397" s="9"/>
-      <c r="G397" s="9"/>
-      <c r="H397" s="9"/>
+      <c r="A397" s="11"/>
+      <c r="B397" s="12"/>
+      <c r="C397" s="12"/>
+      <c r="D397" s="12"/>
+      <c r="E397" s="12"/>
+      <c r="F397" s="12"/>
+      <c r="G397" s="12"/>
+      <c r="H397" s="12"/>
       <c r="I397" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11357,14 +11384,14 @@
       <c r="N397" s="16"/>
     </row>
     <row r="398" spans="1:14">
-      <c r="A398" s="8"/>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
+      <c r="A398" s="11"/>
+      <c r="B398" s="12"/>
+      <c r="C398" s="12"/>
+      <c r="D398" s="12"/>
+      <c r="E398" s="12"/>
+      <c r="F398" s="12"/>
+      <c r="G398" s="12"/>
+      <c r="H398" s="12"/>
       <c r="I398" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11379,14 +11406,14 @@
       <c r="N398" s="16"/>
     </row>
     <row r="399" spans="1:14">
-      <c r="A399" s="8"/>
-      <c r="B399" s="9"/>
-      <c r="C399" s="9"/>
-      <c r="D399" s="9"/>
-      <c r="E399" s="9"/>
-      <c r="F399" s="9"/>
-      <c r="G399" s="9"/>
-      <c r="H399" s="9"/>
+      <c r="A399" s="11"/>
+      <c r="B399" s="12"/>
+      <c r="C399" s="12"/>
+      <c r="D399" s="12"/>
+      <c r="E399" s="12"/>
+      <c r="F399" s="12"/>
+      <c r="G399" s="12"/>
+      <c r="H399" s="12"/>
       <c r="I399" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11401,14 +11428,14 @@
       <c r="N399" s="16"/>
     </row>
     <row r="400" spans="1:14">
-      <c r="A400" s="8"/>
-      <c r="B400" s="9"/>
-      <c r="C400" s="9"/>
-      <c r="D400" s="9"/>
-      <c r="E400" s="9"/>
-      <c r="F400" s="9"/>
-      <c r="G400" s="9"/>
-      <c r="H400" s="9"/>
+      <c r="A400" s="11"/>
+      <c r="B400" s="12"/>
+      <c r="C400" s="12"/>
+      <c r="D400" s="12"/>
+      <c r="E400" s="12"/>
+      <c r="F400" s="12"/>
+      <c r="G400" s="12"/>
+      <c r="H400" s="12"/>
       <c r="I400" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>
@@ -11423,14 +11450,14 @@
       <c r="N400" s="16"/>
     </row>
     <row r="401" spans="1:14">
-      <c r="A401" s="8"/>
-      <c r="B401" s="9"/>
-      <c r="C401" s="9"/>
-      <c r="D401" s="9"/>
-      <c r="E401" s="9"/>
-      <c r="F401" s="9"/>
-      <c r="G401" s="9"/>
-      <c r="H401" s="9"/>
+      <c r="A401" s="11"/>
+      <c r="B401" s="12"/>
+      <c r="C401" s="12"/>
+      <c r="D401" s="12"/>
+      <c r="E401" s="12"/>
+      <c r="F401" s="12"/>
+      <c r="G401" s="12"/>
+      <c r="H401" s="12"/>
       <c r="I401" s="13" t="str">
         <f t="shared" si="12"/>
         <v/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>Prepare for the CA and Practice.</t>
+  </si>
+  <si>
+    <t>Practice Coding.</t>
   </si>
 </sst>
 </file>
@@ -3706,26 +3709,50 @@
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="13" t="str">
+      <c r="A49" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B49" s="12">
+        <v>0</v>
+      </c>
+      <c r="C49" s="12">
+        <v>0</v>
+      </c>
+      <c r="D49" s="12">
+        <v>180</v>
+      </c>
+      <c r="E49" s="12">
+        <v>120</v>
+      </c>
+      <c r="F49" s="12">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12">
+        <v>0</v>
+      </c>
+      <c r="H49" s="12">
+        <v>240</v>
+      </c>
+      <c r="I49" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="13" t="str">
+        <v>540</v>
+      </c>
+      <c r="J49" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L49" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M49" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8400" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,24 @@
   </si>
   <si>
     <t>Practice Coding.</t>
+  </si>
+  <si>
+    <t>Practice.</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Due to unnecessary movement in the campus.</t>
+  </si>
+  <si>
+    <t>Tired due to travelling.</t>
+  </si>
+  <si>
+    <t>Travelling.</t>
+  </si>
+  <si>
+    <t>Take rest and complete the sleep schedule.</t>
   </si>
 </sst>
 </file>
@@ -3755,136 +3773,280 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="13" t="str">
+      <c r="A50" s="11">
+        <v>46291</v>
+      </c>
+      <c r="B50" s="12">
+        <v>480</v>
+      </c>
+      <c r="C50" s="12">
+        <v>0</v>
+      </c>
+      <c r="D50" s="12">
+        <v>60</v>
+      </c>
+      <c r="E50" s="12">
+        <v>120</v>
+      </c>
+      <c r="F50" s="12">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0</v>
+      </c>
+      <c r="H50" s="12">
+        <v>300</v>
+      </c>
+      <c r="I50" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J50" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="16"/>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="13" t="str">
+        <v>480</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L50" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M50" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N50" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" ht="28.8" spans="1:14">
+      <c r="A51" s="11">
+        <v>46292</v>
+      </c>
+      <c r="B51" s="12">
+        <v>0</v>
+      </c>
+      <c r="C51" s="12">
+        <v>0</v>
+      </c>
+      <c r="D51" s="12">
+        <v>60</v>
+      </c>
+      <c r="E51" s="12">
+        <v>0</v>
+      </c>
+      <c r="F51" s="12">
+        <v>0</v>
+      </c>
+      <c r="G51" s="12">
+        <v>0</v>
+      </c>
+      <c r="H51" s="12">
+        <v>240</v>
+      </c>
+      <c r="I51" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="13" t="str">
+        <v>300</v>
+      </c>
+      <c r="J51" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="16"/>
+        <v>1140</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M51" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N51" s="16" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="13" t="str">
+      <c r="A52" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="12">
+        <v>60</v>
+      </c>
+      <c r="C52" s="12">
+        <v>120</v>
+      </c>
+      <c r="D52" s="12">
+        <v>0</v>
+      </c>
+      <c r="E52" s="12">
+        <v>0</v>
+      </c>
+      <c r="F52" s="12">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12">
+        <v>0</v>
+      </c>
+      <c r="H52" s="12">
+        <v>360</v>
+      </c>
+      <c r="I52" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="13" t="str">
+        <v>540</v>
+      </c>
+      <c r="J52" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M52" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N52" s="16" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="13" t="str">
+      <c r="A53" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="12">
+        <v>120</v>
+      </c>
+      <c r="C53" s="12">
+        <v>0</v>
+      </c>
+      <c r="D53" s="12">
+        <v>0</v>
+      </c>
+      <c r="E53" s="12">
+        <v>0</v>
+      </c>
+      <c r="F53" s="12">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12">
+        <v>0</v>
+      </c>
+      <c r="H53" s="12">
+        <v>420</v>
+      </c>
+      <c r="I53" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="13" t="str">
+        <v>540</v>
+      </c>
+      <c r="J53" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L53" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N53" s="16" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="13" t="str">
+      <c r="A54" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="12">
+        <v>300</v>
+      </c>
+      <c r="C54" s="12">
+        <v>120</v>
+      </c>
+      <c r="D54" s="12">
+        <v>0</v>
+      </c>
+      <c r="E54" s="12">
+        <v>0</v>
+      </c>
+      <c r="F54" s="12">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0</v>
+      </c>
+      <c r="H54" s="12">
+        <v>360</v>
+      </c>
+      <c r="I54" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="13" t="str">
+        <v>780</v>
+      </c>
+      <c r="J54" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="16"/>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="13" t="str">
+        <v>660</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L54" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M54" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N54" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" ht="28.8" spans="1:14">
+      <c r="A55" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B55" s="12">
+        <v>360</v>
+      </c>
+      <c r="C55" s="12">
+        <v>0</v>
+      </c>
+      <c r="D55" s="12">
+        <v>0</v>
+      </c>
+      <c r="E55" s="12">
+        <v>0</v>
+      </c>
+      <c r="F55" s="12">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12">
+        <v>0</v>
+      </c>
+      <c r="H55" s="12">
+        <v>360</v>
+      </c>
+      <c r="I55" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="13" t="str">
+        <v>720</v>
+      </c>
+      <c r="J55" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L55" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N55" s="16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" tabRatio="500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>Take rest and complete the sleep schedule.</t>
+  </si>
+  <si>
+    <t>Enjoy and Spend more time with family.</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1624,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.57407407407407" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.3240740740741" customWidth="1"/>
+    <col min="1" max="1" width="11.787037037037" customWidth="1"/>
     <col min="2" max="2" width="10.8888888888889" customWidth="1"/>
     <col min="3" max="3" width="11.5555555555556" customWidth="1"/>
     <col min="4" max="6" width="11" customWidth="1"/>
@@ -1630,8 +1633,8 @@
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="13" max="13" width="12.787037037037" customWidth="1"/>
+    <col min="14" max="14" width="23.8981481481481" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:14">
@@ -3680,7 +3683,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" ht="28.8" spans="1:14">
       <c r="A48" s="11">
         <v>46289</v>
       </c>
@@ -4048,27 +4051,51 @@
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="13" t="str">
+    <row r="56" ht="28.8" spans="1:14">
+      <c r="A56" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B56" s="12">
+        <v>420</v>
+      </c>
+      <c r="C56" s="12">
+        <v>0</v>
+      </c>
+      <c r="D56" s="12">
+        <v>0</v>
+      </c>
+      <c r="E56" s="12">
+        <v>0</v>
+      </c>
+      <c r="F56" s="12">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12">
+        <v>0</v>
+      </c>
+      <c r="H56" s="12">
+        <v>300</v>
+      </c>
+      <c r="I56" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="13" t="str">
+        <v>720</v>
+      </c>
+      <c r="J56" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L56" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M56" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N56" s="16" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>Enjoy and Spend more time with family.</t>
+  </si>
+  <si>
+    <t>Do the tasks at home.</t>
   </si>
 </sst>
 </file>
@@ -1751,7 +1754,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" ht="41.4" spans="1:14">
+    <row r="6" ht="55.2" spans="1:14">
       <c r="A6" s="6">
         <v>46223</v>
       </c>
@@ -1935,7 +1938,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" ht="43.2" spans="1:14">
+    <row r="10" ht="57.6" spans="1:14">
       <c r="A10" s="11">
         <v>46250</v>
       </c>
@@ -2073,7 +2076,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" ht="43.2" spans="1:14">
+    <row r="13" ht="57.6" spans="1:14">
       <c r="A13" s="11">
         <v>46253</v>
       </c>
@@ -2349,7 +2352,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" ht="28.8" spans="1:14">
       <c r="A19" s="11">
         <v>46259</v>
       </c>
@@ -2579,7 +2582,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" ht="28.8" spans="1:14">
       <c r="A24" s="11">
         <v>46264</v>
       </c>
@@ -2901,7 +2904,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" ht="28.8" spans="1:14">
+    <row r="31" ht="43.2" spans="1:14">
       <c r="A31" s="11">
         <v>46272</v>
       </c>
@@ -3131,7 +3134,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" ht="28.8" spans="1:14">
+    <row r="36" ht="43.2" spans="1:14">
       <c r="A36" s="11">
         <v>46277</v>
       </c>
@@ -3361,7 +3364,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" ht="28.8" spans="1:14">
       <c r="A41" s="11">
         <v>46282</v>
       </c>
@@ -3545,7 +3548,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="45" ht="28.8" spans="1:14">
+    <row r="45" ht="43.2" spans="1:14">
       <c r="A45" s="11">
         <v>46286</v>
       </c>
@@ -4098,26 +4101,50 @@
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="13" t="str">
+      <c r="A57" s="11">
+        <v>46298</v>
+      </c>
+      <c r="B57" s="12">
+        <v>540</v>
+      </c>
+      <c r="C57" s="12">
+        <v>180</v>
+      </c>
+      <c r="D57" s="12">
+        <v>0</v>
+      </c>
+      <c r="E57" s="12">
+        <v>0</v>
+      </c>
+      <c r="F57" s="12">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12">
+        <v>0</v>
+      </c>
+      <c r="H57" s="12">
+        <v>360</v>
+      </c>
+      <c r="I57" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="13" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J57" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L57" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N57" s="16" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Do the tasks at home.</t>
+  </si>
+  <si>
+    <t>Preperation for the MTT and spending the time at home.</t>
   </si>
 </sst>
 </file>
@@ -4146,27 +4149,51 @@
         <v>104</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="13" t="str">
+    <row r="58" ht="28.8" spans="1:14">
+      <c r="A58" s="11">
+        <v>46299</v>
+      </c>
+      <c r="B58" s="12">
+        <v>360</v>
+      </c>
+      <c r="C58" s="12">
+        <v>240</v>
+      </c>
+      <c r="D58" s="12">
+        <v>60</v>
+      </c>
+      <c r="E58" s="12">
+        <v>0</v>
+      </c>
+      <c r="F58" s="12">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12">
+        <v>0</v>
+      </c>
+      <c r="H58" s="12">
+        <v>0</v>
+      </c>
+      <c r="I58" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="13" t="str">
+        <v>660</v>
+      </c>
+      <c r="J58" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="16"/>
+        <v>780</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L58" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M58" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N58" s="16" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>Preperation for the MTT and spending the time at home.</t>
+  </si>
+  <si>
+    <t>Prepare for the MTT.</t>
   </si>
 </sst>
 </file>
@@ -4196,48 +4199,96 @@
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="13" t="str">
+      <c r="A59" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B59" s="12">
+        <v>420</v>
+      </c>
+      <c r="C59" s="12">
+        <v>240</v>
+      </c>
+      <c r="D59" s="12">
+        <v>120</v>
+      </c>
+      <c r="E59" s="12">
+        <v>0</v>
+      </c>
+      <c r="F59" s="12">
+        <v>0</v>
+      </c>
+      <c r="G59" s="12">
+        <v>0</v>
+      </c>
+      <c r="H59" s="12">
+        <v>360</v>
+      </c>
+      <c r="I59" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="13" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J59" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L59" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M59" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N59" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="13" t="str">
+      <c r="A60" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B60" s="12">
+        <v>420</v>
+      </c>
+      <c r="C60" s="12">
+        <v>240</v>
+      </c>
+      <c r="D60" s="12">
+        <v>120</v>
+      </c>
+      <c r="E60" s="12">
+        <v>0</v>
+      </c>
+      <c r="F60" s="12">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <v>0</v>
+      </c>
+      <c r="H60" s="12">
+        <v>360</v>
+      </c>
+      <c r="I60" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="13" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J60" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N60" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>Prepare for the MTT.</t>
+  </si>
+  <si>
+    <t>Prepare for the MTT and making the Minor Project.</t>
   </si>
 </sst>
 </file>
@@ -4290,49 +4293,97 @@
         <v>106</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="13" t="str">
+    <row r="61" ht="28.8" spans="1:14">
+      <c r="A61" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B61" s="12">
+        <v>480</v>
+      </c>
+      <c r="C61" s="12">
+        <v>240</v>
+      </c>
+      <c r="D61" s="12">
+        <v>180</v>
+      </c>
+      <c r="E61" s="12">
+        <v>0</v>
+      </c>
+      <c r="F61" s="12">
+        <v>0</v>
+      </c>
+      <c r="G61" s="12">
+        <v>0</v>
+      </c>
+      <c r="H61" s="12">
+        <v>240</v>
+      </c>
+      <c r="I61" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="13" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J61" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="16"/>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="13" t="str">
+        <v>300</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L61" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M61" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N61" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="62" ht="28.8" spans="1:14">
+      <c r="A62" s="11">
+        <v>46303</v>
+      </c>
+      <c r="B62" s="12">
+        <v>480</v>
+      </c>
+      <c r="C62" s="12">
+        <v>120</v>
+      </c>
+      <c r="D62" s="12">
+        <v>240</v>
+      </c>
+      <c r="E62" s="12">
+        <v>0</v>
+      </c>
+      <c r="F62" s="12">
+        <v>0</v>
+      </c>
+      <c r="G62" s="12">
+        <v>0</v>
+      </c>
+      <c r="H62" s="12">
+        <v>240</v>
+      </c>
+      <c r="I62" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="13" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J62" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L62" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M62" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N62" s="16" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4386,70 +4386,142 @@
       </c>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="13" t="str">
+      <c r="A63" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B63" s="12">
+        <v>540</v>
+      </c>
+      <c r="C63" s="12">
+        <v>240</v>
+      </c>
+      <c r="D63" s="12">
+        <v>120</v>
+      </c>
+      <c r="E63" s="12">
+        <v>0</v>
+      </c>
+      <c r="F63" s="12">
+        <v>0</v>
+      </c>
+      <c r="G63" s="12">
+        <v>0</v>
+      </c>
+      <c r="H63" s="12">
+        <v>240</v>
+      </c>
+      <c r="I63" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="13" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J63" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="16"/>
+        <v>300</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L63" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M63" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N63" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="11"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="13" t="str">
+      <c r="A64" s="11">
+        <v>46305</v>
+      </c>
+      <c r="B64" s="12">
+        <v>120</v>
+      </c>
+      <c r="C64" s="12">
+        <v>120</v>
+      </c>
+      <c r="D64" s="12">
+        <v>0</v>
+      </c>
+      <c r="E64" s="12">
+        <v>0</v>
+      </c>
+      <c r="F64" s="12">
+        <v>0</v>
+      </c>
+      <c r="G64" s="12">
+        <v>0</v>
+      </c>
+      <c r="H64" s="12">
+        <v>720</v>
+      </c>
+      <c r="I64" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J64" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L64" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M64" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N64" s="16" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="13" t="str">
+      <c r="A65" s="11">
+        <v>46306</v>
+      </c>
+      <c r="B65" s="12">
+        <v>480</v>
+      </c>
+      <c r="C65" s="12">
+        <v>0</v>
+      </c>
+      <c r="D65" s="12">
+        <v>0</v>
+      </c>
+      <c r="E65" s="12">
+        <v>0</v>
+      </c>
+      <c r="F65" s="12">
+        <v>0</v>
+      </c>
+      <c r="G65" s="12">
+        <v>0</v>
+      </c>
+      <c r="H65" s="12">
+        <v>960</v>
+      </c>
+      <c r="I65" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="13" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J65" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L65" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N65" s="16" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4524,48 +4524,96 @@
       </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="13" t="str">
+      <c r="A66" s="11">
+        <v>46307</v>
+      </c>
+      <c r="B66" s="12">
+        <v>420</v>
+      </c>
+      <c r="C66" s="12">
+        <v>60</v>
+      </c>
+      <c r="D66" s="12">
+        <v>120</v>
+      </c>
+      <c r="E66" s="12">
+        <v>0</v>
+      </c>
+      <c r="F66" s="12">
+        <v>0</v>
+      </c>
+      <c r="G66" s="12">
+        <v>0</v>
+      </c>
+      <c r="H66" s="12">
+        <v>360</v>
+      </c>
+      <c r="I66" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J66" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L66" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M66" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="11"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="13" t="str">
+      <c r="A67" s="11">
+        <v>46308</v>
+      </c>
+      <c r="B67" s="12">
+        <v>420</v>
+      </c>
+      <c r="C67" s="12">
+        <v>60</v>
+      </c>
+      <c r="D67" s="12">
+        <v>120</v>
+      </c>
+      <c r="E67" s="12">
+        <v>0</v>
+      </c>
+      <c r="F67" s="12">
+        <v>0</v>
+      </c>
+      <c r="G67" s="12">
+        <v>0</v>
+      </c>
+      <c r="H67" s="12">
+        <v>360</v>
+      </c>
+      <c r="I67" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J67" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M67" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4616,48 +4616,96 @@
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="13" t="str">
+      <c r="A68" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B68" s="12">
+        <v>480</v>
+      </c>
+      <c r="C68" s="12">
+        <v>60</v>
+      </c>
+      <c r="D68" s="12">
+        <v>180</v>
+      </c>
+      <c r="E68" s="12">
+        <v>0</v>
+      </c>
+      <c r="F68" s="12">
+        <v>0</v>
+      </c>
+      <c r="G68" s="12">
+        <v>0</v>
+      </c>
+      <c r="H68" s="12">
+        <v>180</v>
+      </c>
+      <c r="I68" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="13" t="str">
+        <v>900</v>
+      </c>
+      <c r="J68" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-      <c r="N68" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L68" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M68" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N68" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="13" t="str">
+      <c r="A69" s="11">
+        <v>46310</v>
+      </c>
+      <c r="B69" s="12">
+        <v>480</v>
+      </c>
+      <c r="C69" s="12">
+        <v>0</v>
+      </c>
+      <c r="D69" s="12">
+        <v>180</v>
+      </c>
+      <c r="E69" s="12">
+        <v>0</v>
+      </c>
+      <c r="F69" s="12">
+        <v>0</v>
+      </c>
+      <c r="G69" s="12">
+        <v>0</v>
+      </c>
+      <c r="H69" s="12">
+        <v>240</v>
+      </c>
+      <c r="I69" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="13" t="str">
+        <v>900</v>
+      </c>
+      <c r="J69" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L69" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M69" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N69" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4708,26 +4708,50 @@
       </c>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="13" t="str">
+      <c r="A70" s="11">
+        <v>46311</v>
+      </c>
+      <c r="B70" s="12">
+        <v>540</v>
+      </c>
+      <c r="C70" s="12">
+        <v>60</v>
+      </c>
+      <c r="D70" s="12">
+        <v>180</v>
+      </c>
+      <c r="E70" s="12">
+        <v>0</v>
+      </c>
+      <c r="F70" s="12">
+        <v>0</v>
+      </c>
+      <c r="G70" s="12">
+        <v>0</v>
+      </c>
+      <c r="H70" s="12">
+        <v>240</v>
+      </c>
+      <c r="I70" s="13">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="13" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J70" s="13">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L70" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M70" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N70" s="16" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4753,27 +4753,51 @@
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="13" t="str">
+    <row r="71" ht="28.8" spans="1:14">
+      <c r="A71" s="11">
+        <v>46312</v>
+      </c>
+      <c r="B71" s="12">
+        <v>480</v>
+      </c>
+      <c r="C71" s="12">
+        <v>60</v>
+      </c>
+      <c r="D71" s="12">
+        <v>180</v>
+      </c>
+      <c r="E71" s="12">
+        <v>0</v>
+      </c>
+      <c r="F71" s="12">
+        <v>0</v>
+      </c>
+      <c r="G71" s="12">
+        <v>0</v>
+      </c>
+      <c r="H71" s="12">
+        <v>240</v>
+      </c>
+      <c r="I71" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="13" t="str">
+        <v>960</v>
+      </c>
+      <c r="J71" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L71" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M71" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N71" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4800,26 +4800,50 @@
       </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="13" t="str">
+      <c r="A72" s="11">
+        <v>46313</v>
+      </c>
+      <c r="B72" s="12">
+        <v>300</v>
+      </c>
+      <c r="C72" s="12">
+        <v>0</v>
+      </c>
+      <c r="D72" s="12">
+        <v>60</v>
+      </c>
+      <c r="E72" s="12">
+        <v>30</v>
+      </c>
+      <c r="F72" s="12">
+        <v>0</v>
+      </c>
+      <c r="G72" s="12">
+        <v>0</v>
+      </c>
+      <c r="H72" s="12">
+        <v>350</v>
+      </c>
+      <c r="I72" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="13" t="str">
+        <v>740</v>
+      </c>
+      <c r="J72" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="16"/>
+        <v>700</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L72" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M72" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -352,6 +352,15 @@
   </si>
   <si>
     <t>Prepare for the MTT and making the Minor Project.</t>
+  </si>
+  <si>
+    <t>Start Internship in Data Science domain.</t>
+  </si>
+  <si>
+    <t>Develop coding and learning skills.</t>
+  </si>
+  <si>
+    <t>Learning new concepts of C++.</t>
   </si>
 </sst>
 </file>
@@ -4822,15 +4831,15 @@
         <v>0</v>
       </c>
       <c r="H72" s="12">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="I72" s="13">
         <f t="shared" si="2"/>
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="J72" s="13">
         <f t="shared" si="3"/>
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="K72" s="14" t="s">
         <v>52</v>
@@ -4845,71 +4854,143 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="13" t="str">
+    <row r="73" ht="28.8" spans="1:14">
+      <c r="A73" s="11">
+        <v>46314</v>
+      </c>
+      <c r="B73" s="12">
+        <v>360</v>
+      </c>
+      <c r="C73" s="12">
+        <v>60</v>
+      </c>
+      <c r="D73" s="12">
+        <v>120</v>
+      </c>
+      <c r="E73" s="12">
+        <v>60</v>
+      </c>
+      <c r="F73" s="12">
+        <v>150</v>
+      </c>
+      <c r="G73" s="12">
+        <v>3</v>
+      </c>
+      <c r="H73" s="12">
+        <v>240</v>
+      </c>
+      <c r="I73" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="13" t="str">
+        <v>990</v>
+      </c>
+      <c r="J73" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="16"/>
-    </row>
-    <row r="74" spans="1:14">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="13" t="str">
+        <v>450</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L73" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M73" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N73" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" ht="28.8" spans="1:14">
+      <c r="A74" s="11">
+        <v>46315</v>
+      </c>
+      <c r="B74" s="12">
+        <v>420</v>
+      </c>
+      <c r="C74" s="12">
+        <v>0</v>
+      </c>
+      <c r="D74" s="12">
+        <v>120</v>
+      </c>
+      <c r="E74" s="12">
+        <v>60</v>
+      </c>
+      <c r="F74" s="12">
+        <v>0</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12">
+        <v>240</v>
+      </c>
+      <c r="I74" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="13" t="str">
+        <v>840</v>
+      </c>
+      <c r="J74" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="16"/>
-    </row>
-    <row r="75" spans="1:14">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="13" t="str">
+        <v>600</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L74" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M74" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N74" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" ht="28.8" spans="1:14">
+      <c r="A75" s="11">
+        <v>46316</v>
+      </c>
+      <c r="B75" s="12">
+        <v>360</v>
+      </c>
+      <c r="C75" s="12">
+        <v>60</v>
+      </c>
+      <c r="D75" s="12">
+        <v>120</v>
+      </c>
+      <c r="E75" s="12">
+        <v>30</v>
+      </c>
+      <c r="F75" s="12">
+        <v>200</v>
+      </c>
+      <c r="G75" s="12">
+        <v>4</v>
+      </c>
+      <c r="H75" s="12">
+        <v>300</v>
+      </c>
+      <c r="I75" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="13" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J75" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
-      <c r="M75" s="14"/>
-      <c r="N75" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L75" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M75" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N75" s="16" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -361,6 +361,15 @@
   </si>
   <si>
     <t>Learning new concepts of C++.</t>
+  </si>
+  <si>
+    <t>Learn new topic in SQL Database and practice it.</t>
+  </si>
+  <si>
+    <t>Practice some questions on Github.</t>
+  </si>
+  <si>
+    <t>Complete the assignment of the Domain Data Science.</t>
   </si>
 </sst>
 </file>
@@ -1645,7 +1654,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.57407407407407" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.787037037037" customWidth="1"/>
+    <col min="1" max="1" width="14.7037037037037" customWidth="1"/>
     <col min="2" max="2" width="10.8888888888889" customWidth="1"/>
     <col min="3" max="3" width="11.5555555555556" customWidth="1"/>
     <col min="4" max="6" width="11" customWidth="1"/>
@@ -4992,71 +5001,143 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="13" t="str">
+    <row r="76" ht="28.8" spans="1:14">
+      <c r="A76" s="11">
+        <v>46317</v>
+      </c>
+      <c r="B76" s="12">
+        <v>420</v>
+      </c>
+      <c r="C76" s="12">
+        <v>60</v>
+      </c>
+      <c r="D76" s="12">
+        <v>120</v>
+      </c>
+      <c r="E76" s="12">
+        <v>120</v>
+      </c>
+      <c r="F76" s="12">
+        <v>350</v>
+      </c>
+      <c r="G76" s="12">
+        <v>7</v>
+      </c>
+      <c r="H76" s="12">
+        <v>300</v>
+      </c>
+      <c r="I76" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="13" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J76" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="16"/>
-    </row>
-    <row r="77" spans="1:14">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="13" t="str">
+        <v>70</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L76" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M76" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N76" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="77" ht="28.8" spans="1:14">
+      <c r="A77" s="11">
+        <v>46318</v>
+      </c>
+      <c r="B77" s="12">
+        <v>360</v>
+      </c>
+      <c r="C77" s="12">
+        <v>60</v>
+      </c>
+      <c r="D77" s="12">
+        <v>120</v>
+      </c>
+      <c r="E77" s="12">
+        <v>120</v>
+      </c>
+      <c r="F77" s="12">
+        <v>300</v>
+      </c>
+      <c r="G77" s="12">
+        <v>6</v>
+      </c>
+      <c r="H77" s="12">
+        <v>300</v>
+      </c>
+      <c r="I77" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="13" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J77" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="16"/>
-    </row>
-    <row r="78" spans="1:14">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="13" t="str">
+        <v>180</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L77" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M77" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N77" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="78" ht="28.8" spans="1:14">
+      <c r="A78" s="11">
+        <v>46319</v>
+      </c>
+      <c r="B78" s="12">
+        <v>480</v>
+      </c>
+      <c r="C78" s="12">
+        <v>0</v>
+      </c>
+      <c r="D78" s="12">
+        <v>180</v>
+      </c>
+      <c r="E78" s="12">
+        <v>120</v>
+      </c>
+      <c r="F78" s="12">
+        <v>0</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12">
+        <v>300</v>
+      </c>
+      <c r="I78" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="13" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J78" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L78" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M78" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N78" s="16" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -370,6 +370,9 @@
   </si>
   <si>
     <t>Complete the assignment of the Domain Data Science.</t>
+  </si>
+  <si>
+    <t>Complete the assignment of Analytical Skills.</t>
   </si>
 </sst>
 </file>
@@ -5139,27 +5142,51 @@
         <v>113</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="13" t="str">
+    <row r="79" ht="28.8" spans="1:14">
+      <c r="A79" s="11">
+        <v>46320</v>
+      </c>
+      <c r="B79" s="12">
+        <v>540</v>
+      </c>
+      <c r="C79" s="12">
+        <v>0</v>
+      </c>
+      <c r="D79" s="12">
+        <v>180</v>
+      </c>
+      <c r="E79" s="12">
+        <v>120</v>
+      </c>
+      <c r="F79" s="12">
+        <v>0</v>
+      </c>
+      <c r="G79" s="12">
+        <v>0</v>
+      </c>
+      <c r="H79" s="12">
+        <v>360</v>
+      </c>
+      <c r="I79" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="13" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J79" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="16"/>
+        <v>240</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L79" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M79" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N79" s="16" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -373,6 +373,9 @@
   </si>
   <si>
     <t>Complete the assignment of Analytical Skills.</t>
+  </si>
+  <si>
+    <t>Learn new topics and practice it.</t>
   </si>
 </sst>
 </file>
@@ -5188,27 +5191,51 @@
         <v>114</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="13" t="str">
+    <row r="80" ht="28.8" spans="1:14">
+      <c r="A80" s="11">
+        <v>46321</v>
+      </c>
+      <c r="B80" s="12">
+        <v>360</v>
+      </c>
+      <c r="C80" s="12">
+        <v>0</v>
+      </c>
+      <c r="D80" s="12">
+        <v>120</v>
+      </c>
+      <c r="E80" s="12">
+        <v>120</v>
+      </c>
+      <c r="F80" s="12">
+        <v>0</v>
+      </c>
+      <c r="G80" s="12">
+        <v>0</v>
+      </c>
+      <c r="H80" s="12">
+        <v>300</v>
+      </c>
+      <c r="I80" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="13" t="str">
+        <v>900</v>
+      </c>
+      <c r="J80" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L80" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M80" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N80" s="16" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5237,27 +5237,51 @@
         <v>115</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
-      <c r="A81" s="11"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="13" t="str">
+    <row r="81" ht="43.2" spans="1:14">
+      <c r="A81" s="11">
+        <v>46322</v>
+      </c>
+      <c r="B81" s="12">
+        <v>180</v>
+      </c>
+      <c r="C81" s="12">
+        <v>60</v>
+      </c>
+      <c r="D81" s="12">
+        <v>60</v>
+      </c>
+      <c r="E81" s="12">
+        <v>120</v>
+      </c>
+      <c r="F81" s="12">
+        <v>350</v>
+      </c>
+      <c r="G81" s="12">
+        <v>7</v>
+      </c>
+      <c r="H81" s="12">
+        <v>300</v>
+      </c>
+      <c r="I81" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="13" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J81" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K81" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L81" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M81" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N81" s="16" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="11"/>

--- a/12618065.xlsx
+++ b/12618065.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="119">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -376,6 +376,15 @@
   </si>
   <si>
     <t>Learn new topics and practice it.</t>
+  </si>
+  <si>
+    <t>Practice SQL commands.</t>
+  </si>
+  <si>
+    <t>Prepare for the CA.</t>
+  </si>
+  <si>
+    <t>Complete the todays lecture of the Intership.</t>
   </si>
 </sst>
 </file>
@@ -5284,70 +5293,142 @@
       </c>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="11"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="13" t="str">
+      <c r="A82" s="11">
+        <v>46323</v>
+      </c>
+      <c r="B82" s="12">
+        <v>240</v>
+      </c>
+      <c r="C82" s="12">
+        <v>60</v>
+      </c>
+      <c r="D82" s="12">
+        <v>120</v>
+      </c>
+      <c r="E82" s="12">
+        <v>60</v>
+      </c>
+      <c r="F82" s="12">
+        <v>200</v>
+      </c>
+      <c r="G82" s="12">
+        <v>4</v>
+      </c>
+      <c r="H82" s="12">
+        <v>240</v>
+      </c>
+      <c r="I82" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="13" t="str">
+        <v>920</v>
+      </c>
+      <c r="J82" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
-      <c r="N82" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L82" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M82" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N82" s="16" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="13" t="str">
+      <c r="A83" s="11">
+        <v>46324</v>
+      </c>
+      <c r="B83" s="12">
+        <v>360</v>
+      </c>
+      <c r="C83" s="12">
+        <v>60</v>
+      </c>
+      <c r="D83" s="12">
+        <v>180</v>
+      </c>
+      <c r="E83" s="12">
+        <v>0</v>
+      </c>
+      <c r="F83" s="12">
+        <v>350</v>
+      </c>
+      <c r="G83" s="12">
+        <v>7</v>
+      </c>
+      <c r="H83" s="12">
+        <v>300</v>
+      </c>
+      <c r="I83" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="13" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J83" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
-      <c r="N83" s="16"/>
-    </row>
-    <row r="84" spans="1:14">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="13" t="str">
+        <v>190</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L83" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M83" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N83" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="84" ht="28.8" spans="1:14">
+      <c r="A84" s="11">
+        <v>46325</v>
+      </c>
+      <c r="B84" s="12">
+        <v>300</v>
+      </c>
+      <c r="C84" s="12">
+        <v>60</v>
+      </c>
+      <c r="D84" s="12">
+        <v>120</v>
+      </c>
+      <c r="E84" s="12">
+        <v>0</v>
+      </c>
+      <c r="F84" s="12">
+        <v>300</v>
+      </c>
+      <c r="G84" s="12">
+        <v>6</v>
+      </c>
+      <c r="H84" s="12">
+        <v>300</v>
+      </c>
+      <c r="I84" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="13" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J84" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
-      <c r="N84" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L84" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M84" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N84" s="16" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="11"/>
